--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.06</v>
+        <v>4.4</v>
       </c>
       <c r="F14" t="n">
-        <v>14.07</v>
+        <v>13.41</v>
       </c>
       <c r="G14" t="n">
-        <v>355.9</v>
+        <v>357.5</v>
       </c>
       <c r="H14" t="n">
-        <v>86.8</v>
+        <v>81.7</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-30.22</v>
+        <v>-10.12</v>
       </c>
       <c r="K14" t="n">
-        <v>-24.51</v>
+        <v>-290.26</v>
       </c>
       <c r="L14" t="n">
-        <v>38.91</v>
+        <v>290.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:30:11</t>
+          <t>04:31:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.56</v>
+        <v>3.83</v>
       </c>
       <c r="F15" t="n">
-        <v>13.92</v>
+        <v>14.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>82.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I15" t="n">
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>48.04</v>
+        <v>38.89</v>
       </c>
       <c r="K15" t="n">
-        <v>44.81</v>
+        <v>-160.93</v>
       </c>
       <c r="L15" t="n">
-        <v>65.69</v>
+        <v>165.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:32:00</t>
+          <t>04:33:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.45</v>
+        <v>3.73</v>
       </c>
       <c r="F16" t="n">
-        <v>13.77</v>
+        <v>14.26</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="H16" t="n">
-        <v>87.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-95.08</v>
+        <v>159.74</v>
       </c>
       <c r="K16" t="n">
-        <v>-23.83</v>
+        <v>166.07</v>
       </c>
       <c r="L16" t="n">
-        <v>98.02</v>
+        <v>230.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:37:06</t>
+          <t>04:38:21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.22</v>
+        <v>3.59</v>
       </c>
       <c r="F17" t="n">
-        <v>13.45</v>
+        <v>14.02</v>
       </c>
       <c r="G17" t="n">
-        <v>14.2</v>
+        <v>6.9</v>
       </c>
       <c r="H17" t="n">
-        <v>83.2</v>
+        <v>82</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-32.74</v>
+        <v>1.1</v>
       </c>
       <c r="K17" t="n">
-        <v>-357.55</v>
+        <v>-176.11</v>
       </c>
       <c r="L17" t="n">
-        <v>359.04</v>
+        <v>176.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:38:27</t>
+          <t>04:40:38</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.65</v>
+        <v>4.28</v>
       </c>
       <c r="F18" t="n">
-        <v>14.17</v>
+        <v>14.39</v>
       </c>
       <c r="G18" t="n">
-        <v>13.9</v>
+        <v>358.5</v>
       </c>
       <c r="H18" t="n">
-        <v>83</v>
+        <v>81.7</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>119.05</v>
+        <v>58.56</v>
       </c>
       <c r="K18" t="n">
-        <v>-85.26000000000001</v>
+        <v>-77.55</v>
       </c>
       <c r="L18" t="n">
-        <v>146.43</v>
+        <v>97.18000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:40:01</t>
+          <t>04:41:10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.4</v>
+        <v>4.53</v>
       </c>
       <c r="F19" t="n">
-        <v>14.27</v>
+        <v>13.62</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>2.3</v>
       </c>
       <c r="H19" t="n">
-        <v>84</v>
+        <v>88.7</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-417.48</v>
+        <v>29.7</v>
       </c>
       <c r="K19" t="n">
-        <v>-214.12</v>
+        <v>176.73</v>
       </c>
       <c r="L19" t="n">
-        <v>469.19</v>
+        <v>179.21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:45:41</t>
+          <t>04:44:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.94</v>
+        <v>4.61</v>
       </c>
       <c r="F20" t="n">
-        <v>13.59</v>
+        <v>13.66</v>
       </c>
       <c r="G20" t="n">
-        <v>359.1</v>
+        <v>24</v>
       </c>
       <c r="H20" t="n">
-        <v>84.3</v>
+        <v>85</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>127.66</v>
+        <v>-647.28</v>
       </c>
       <c r="K20" t="n">
-        <v>-360.74</v>
+        <v>60.58</v>
       </c>
       <c r="L20" t="n">
-        <v>382.67</v>
+        <v>650.11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:47:09</t>
+          <t>04:45:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.85</v>
+        <v>4.34</v>
       </c>
       <c r="F21" t="n">
-        <v>14.34</v>
+        <v>13.92</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9</v>
+        <v>10.6</v>
       </c>
       <c r="H21" t="n">
-        <v>83.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>44.75</v>
+        <v>29.42</v>
       </c>
       <c r="K21" t="n">
-        <v>65.34999999999999</v>
+        <v>-215.31</v>
       </c>
       <c r="L21" t="n">
-        <v>79.2</v>
+        <v>217.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:49:15</t>
+          <t>04:47:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.31</v>
+        <v>3.25</v>
       </c>
       <c r="F22" t="n">
-        <v>14.19</v>
+        <v>13.69</v>
       </c>
       <c r="G22" t="n">
-        <v>9.1</v>
+        <v>13.5</v>
       </c>
       <c r="H22" t="n">
-        <v>80.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-114</v>
+        <v>231.59</v>
       </c>
       <c r="K22" t="n">
-        <v>389.27</v>
+        <v>407.58</v>
       </c>
       <c r="L22" t="n">
-        <v>405.62</v>
+        <v>468.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:54:35</t>
+          <t>04:50:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.68</v>
+        <v>4.46</v>
       </c>
       <c r="F23" t="n">
-        <v>13.14</v>
+        <v>13.57</v>
       </c>
       <c r="G23" t="n">
-        <v>10.9</v>
+        <v>357.4</v>
       </c>
       <c r="H23" t="n">
-        <v>80.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-256.11</v>
+        <v>-401.32</v>
       </c>
       <c r="K23" t="n">
-        <v>70.88</v>
+        <v>-848.24</v>
       </c>
       <c r="L23" t="n">
-        <v>265.74</v>
+        <v>938.39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:57:14</t>
+          <t>04:53:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.11</v>
+        <v>4.47</v>
       </c>
       <c r="F24" t="n">
-        <v>13.57</v>
+        <v>13.73</v>
       </c>
       <c r="G24" t="n">
-        <v>357.2</v>
+        <v>359.4</v>
       </c>
       <c r="H24" t="n">
-        <v>87.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-50.04</v>
+        <v>-532.76</v>
       </c>
       <c r="K24" t="n">
-        <v>856.1900000000001</v>
+        <v>-1.7</v>
       </c>
       <c r="L24" t="n">
-        <v>857.65</v>
+        <v>532.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:58:40</t>
+          <t>04:54:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.9</v>
+        <v>4.24</v>
       </c>
       <c r="F25" t="n">
-        <v>14.35</v>
+        <v>14.64</v>
       </c>
       <c r="G25" t="n">
-        <v>10.3</v>
+        <v>13.1</v>
       </c>
       <c r="H25" t="n">
-        <v>76.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-144.49</v>
+        <v>243.07</v>
       </c>
       <c r="K25" t="n">
-        <v>270.64</v>
+        <v>20.51</v>
       </c>
       <c r="L25" t="n">
-        <v>306.79</v>
+        <v>243.94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:02:09</t>
+          <t>04:59:53</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.09</v>
+        <v>4.33</v>
       </c>
       <c r="F26" t="n">
-        <v>14.09</v>
+        <v>14.33</v>
       </c>
       <c r="G26" t="n">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="H26" t="n">
-        <v>83.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="I26" t="n">
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>917.42</v>
+        <v>-502.54</v>
       </c>
       <c r="K26" t="n">
-        <v>-105.1</v>
+        <v>-195.58</v>
       </c>
       <c r="L26" t="n">
-        <v>923.42</v>
+        <v>539.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:03:36</t>
+          <t>05:00:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.49</v>
+        <v>4.31</v>
       </c>
       <c r="F27" t="n">
-        <v>13.38</v>
+        <v>13.78</v>
       </c>
       <c r="G27" t="n">
-        <v>22.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>84</v>
+        <v>85.2</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>193.24</v>
+        <v>-219.51</v>
       </c>
       <c r="K27" t="n">
-        <v>303.17</v>
+        <v>1499.39</v>
       </c>
       <c r="L27" t="n">
-        <v>359.52</v>
+        <v>1515.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:04:59</t>
+          <t>05:02:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.76</v>
+        <v>4.48</v>
       </c>
       <c r="F28" t="n">
-        <v>13.99</v>
+        <v>13.92</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8</v>
+        <v>10.9</v>
       </c>
       <c r="H28" t="n">
-        <v>80.2</v>
+        <v>89.5</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-208.45</v>
+        <v>-119.76</v>
       </c>
       <c r="K28" t="n">
-        <v>331.03</v>
+        <v>-576.8</v>
       </c>
       <c r="L28" t="n">
-        <v>391.19</v>
+        <v>589.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:15:55</t>
+          <t>05:14:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.77</v>
+        <v>3.81</v>
       </c>
       <c r="F29" t="n">
-        <v>13.46</v>
+        <v>14.21</v>
       </c>
       <c r="G29" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>80.8</v>
+        <v>81.2</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-142.11</v>
+        <v>141.99</v>
       </c>
       <c r="K29" t="n">
-        <v>-53.6</v>
+        <v>10.22</v>
       </c>
       <c r="L29" t="n">
-        <v>151.88</v>
+        <v>142.36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:17:19</t>
+          <t>05:16:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.59</v>
+        <v>5.04</v>
       </c>
       <c r="F30" t="n">
-        <v>13.92</v>
+        <v>13.79</v>
       </c>
       <c r="G30" t="n">
-        <v>7.2</v>
+        <v>15.2</v>
       </c>
       <c r="H30" t="n">
-        <v>87.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>88.3</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-37.61</v>
+        <v>364.64</v>
       </c>
       <c r="L30" t="n">
-        <v>95.98</v>
+        <v>370.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:18:50</t>
+          <t>05:17:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.82</v>
+        <v>3.19</v>
       </c>
       <c r="F31" t="n">
-        <v>14.26</v>
+        <v>14.2</v>
       </c>
       <c r="G31" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H31" t="n">
-        <v>93.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>51.93</v>
+        <v>182.25</v>
       </c>
       <c r="K31" t="n">
-        <v>-111.22</v>
+        <v>157.41</v>
       </c>
       <c r="L31" t="n">
-        <v>122.74</v>
+        <v>240.82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:24:00</t>
+          <t>05:21:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.5</v>
+        <v>4.13</v>
       </c>
       <c r="F32" t="n">
-        <v>14.46</v>
+        <v>13.42</v>
       </c>
       <c r="G32" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="H32" t="n">
-        <v>83.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.98</v>
+        <v>-52.22</v>
       </c>
       <c r="K32" t="n">
-        <v>56.28</v>
+        <v>-418.73</v>
       </c>
       <c r="L32" t="n">
-        <v>56.29</v>
+        <v>421.97</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:26:32</t>
+          <t>05:23:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.39</v>
+        <v>4.47</v>
       </c>
       <c r="F33" t="n">
-        <v>13.85</v>
+        <v>14.99</v>
       </c>
       <c r="G33" t="n">
-        <v>14.7</v>
+        <v>6.1</v>
       </c>
       <c r="H33" t="n">
-        <v>92.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>274.99</v>
+        <v>171.08</v>
       </c>
       <c r="K33" t="n">
-        <v>170.61</v>
+        <v>71.83</v>
       </c>
       <c r="L33" t="n">
-        <v>323.62</v>
+        <v>185.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:28:30</t>
+          <t>05:26:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.84</v>
+        <v>4.74</v>
       </c>
       <c r="F34" t="n">
-        <v>13.91</v>
+        <v>13.95</v>
       </c>
       <c r="G34" t="n">
-        <v>7.5</v>
+        <v>13.3</v>
       </c>
       <c r="H34" t="n">
-        <v>84.8</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-173.95</v>
+        <v>-109.81</v>
       </c>
       <c r="K34" t="n">
-        <v>-144.79</v>
+        <v>31.11</v>
       </c>
       <c r="L34" t="n">
-        <v>226.32</v>
+        <v>114.13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:34:24</t>
+          <t>05:29:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="F35" t="n">
-        <v>12.83</v>
+        <v>14.33</v>
       </c>
       <c r="G35" t="n">
-        <v>354.8</v>
+        <v>14.7</v>
       </c>
       <c r="H35" t="n">
-        <v>87.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-360.68</v>
+        <v>154.67</v>
       </c>
       <c r="K35" t="n">
-        <v>-339.92</v>
+        <v>30.1</v>
       </c>
       <c r="L35" t="n">
-        <v>495.62</v>
+        <v>157.57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:35:26</t>
+          <t>05:30:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.61</v>
+        <v>4.59</v>
       </c>
       <c r="F36" t="n">
-        <v>14.27</v>
+        <v>13.61</v>
       </c>
       <c r="G36" t="n">
-        <v>14.8</v>
+        <v>356.4</v>
       </c>
       <c r="H36" t="n">
-        <v>90.3</v>
+        <v>83.5</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>36.53</v>
+        <v>51.59</v>
       </c>
       <c r="K36" t="n">
-        <v>13.21</v>
+        <v>-485.91</v>
       </c>
       <c r="L36" t="n">
-        <v>38.84</v>
+        <v>488.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:36:07</t>
+          <t>05:33:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="F37" t="n">
-        <v>13.28</v>
+        <v>13.68</v>
       </c>
       <c r="G37" t="n">
-        <v>355.6</v>
+        <v>12.7</v>
       </c>
       <c r="H37" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-66.7</v>
+        <v>-226.43</v>
       </c>
       <c r="K37" t="n">
-        <v>-51.31</v>
+        <v>-250.67</v>
       </c>
       <c r="L37" t="n">
-        <v>84.15000000000001</v>
+        <v>337.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:39:41</t>
+          <t>05:37:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.63</v>
+        <v>4.07</v>
       </c>
       <c r="F38" t="n">
-        <v>13.79</v>
+        <v>13.98</v>
       </c>
       <c r="G38" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="H38" t="n">
-        <v>93.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-37.2</v>
+        <v>-30.02</v>
       </c>
       <c r="K38" t="n">
-        <v>-27.29</v>
+        <v>188.66</v>
       </c>
       <c r="L38" t="n">
-        <v>46.14</v>
+        <v>191.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:41:54</t>
+          <t>05:39:35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="F39" t="n">
-        <v>14.28</v>
+        <v>14.39</v>
       </c>
       <c r="G39" t="n">
-        <v>20.1</v>
+        <v>13.6</v>
       </c>
       <c r="H39" t="n">
-        <v>90.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I39" t="n">
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-349.6</v>
+        <v>-452.16</v>
       </c>
       <c r="K39" t="n">
-        <v>38.7</v>
+        <v>7.21</v>
       </c>
       <c r="L39" t="n">
-        <v>351.74</v>
+        <v>452.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:43:09</t>
+          <t>05:40:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.06</v>
+        <v>4.76</v>
       </c>
       <c r="F40" t="n">
-        <v>13.93</v>
+        <v>13.65</v>
       </c>
       <c r="G40" t="n">
-        <v>18.1</v>
+        <v>355.7</v>
       </c>
       <c r="H40" t="n">
-        <v>83.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>134.97</v>
+        <v>-570.0700000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-275.1</v>
+        <v>383.81</v>
       </c>
       <c r="L40" t="n">
-        <v>306.42</v>
+        <v>687.24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:48:54</t>
+          <t>05:45:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="F41" t="n">
-        <v>13.98</v>
+        <v>14.47</v>
       </c>
       <c r="G41" t="n">
-        <v>11.9</v>
+        <v>7.8</v>
       </c>
       <c r="H41" t="n">
-        <v>85.7</v>
+        <v>83.7</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>29.44</v>
+        <v>-667.4400000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-373.27</v>
+        <v>-639.85</v>
       </c>
       <c r="L41" t="n">
-        <v>374.42</v>
+        <v>924.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:51:19</t>
+          <t>05:45:57</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.92</v>
+        <v>4.2</v>
       </c>
       <c r="F42" t="n">
-        <v>14.4</v>
+        <v>14.61</v>
       </c>
       <c r="G42" t="n">
-        <v>7.9</v>
+        <v>22.6</v>
       </c>
       <c r="H42" t="n">
-        <v>86.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>96.06999999999999</v>
+        <v>491.84</v>
       </c>
       <c r="K42" t="n">
-        <v>-439.5</v>
+        <v>299.04</v>
       </c>
       <c r="L42" t="n">
-        <v>449.88</v>
+        <v>575.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:52:53</t>
+          <t>05:48:11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.74</v>
+        <v>3.84</v>
       </c>
       <c r="F43" t="n">
-        <v>14.05</v>
+        <v>13.63</v>
       </c>
       <c r="G43" t="n">
-        <v>12.3</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>87.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>306.6</v>
+        <v>636.6</v>
       </c>
       <c r="K43" t="n">
-        <v>-280.2</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>415.35</v>
+        <v>644.37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:03:25</t>
+          <t>06:00:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.28</v>
+        <v>4.13</v>
       </c>
       <c r="F44" t="n">
-        <v>13.7</v>
+        <v>13.68</v>
       </c>
       <c r="G44" t="n">
-        <v>6.1</v>
+        <v>9</v>
       </c>
       <c r="H44" t="n">
-        <v>86.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-35.32</v>
+        <v>-203.61</v>
       </c>
       <c r="K44" t="n">
-        <v>32.73</v>
+        <v>-112.4</v>
       </c>
       <c r="L44" t="n">
-        <v>48.15</v>
+        <v>232.58</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:05:07</t>
+          <t>06:02:17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.72</v>
+        <v>4.27</v>
       </c>
       <c r="F45" t="n">
-        <v>13.54</v>
+        <v>14.1</v>
       </c>
       <c r="G45" t="n">
-        <v>8.300000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="H45" t="n">
-        <v>80.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>69.02</v>
+        <v>-74.8</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.71</v>
+        <v>109.86</v>
       </c>
       <c r="L45" t="n">
-        <v>69.18000000000001</v>
+        <v>132.91</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:07:32</t>
+          <t>06:03:09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.66</v>
+        <v>4.3</v>
       </c>
       <c r="F46" t="n">
-        <v>13.48</v>
+        <v>14.02</v>
       </c>
       <c r="G46" t="n">
-        <v>359.1</v>
+        <v>9.9</v>
       </c>
       <c r="H46" t="n">
-        <v>85.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>53.89</v>
+        <v>262.69</v>
       </c>
       <c r="K46" t="n">
-        <v>-15.66</v>
+        <v>-208.46</v>
       </c>
       <c r="L46" t="n">
-        <v>56.12</v>
+        <v>335.35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:10:53</t>
+          <t>06:08:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.38</v>
+        <v>5.21</v>
       </c>
       <c r="F47" t="n">
-        <v>13.91</v>
+        <v>13.83</v>
       </c>
       <c r="G47" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="H47" t="n">
-        <v>86.8</v>
+        <v>84.8</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-117.69</v>
+        <v>-203.56</v>
       </c>
       <c r="K47" t="n">
-        <v>115.91</v>
+        <v>134.56</v>
       </c>
       <c r="L47" t="n">
-        <v>165.18</v>
+        <v>244.01</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:12:58</t>
+          <t>06:10:14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.58</v>
+        <v>3.99</v>
       </c>
       <c r="F48" t="n">
-        <v>14.03</v>
+        <v>13.63</v>
       </c>
       <c r="G48" t="n">
-        <v>23.8</v>
+        <v>15.8</v>
       </c>
       <c r="H48" t="n">
-        <v>87.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-98.77</v>
+        <v>-281.37</v>
       </c>
       <c r="K48" t="n">
-        <v>-214.73</v>
+        <v>57.6</v>
       </c>
       <c r="L48" t="n">
-        <v>236.36</v>
+        <v>287.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:14:19</t>
+          <t>06:11:09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.47</v>
+        <v>4.54</v>
       </c>
       <c r="F49" t="n">
-        <v>13.9</v>
+        <v>14.65</v>
       </c>
       <c r="G49" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="H49" t="n">
-        <v>82.09999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>152.88</v>
+        <v>-35.45</v>
       </c>
       <c r="K49" t="n">
-        <v>-217.75</v>
+        <v>-149.77</v>
       </c>
       <c r="L49" t="n">
-        <v>266.05</v>
+        <v>153.91</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:17:42</t>
+          <t>06:15:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.62</v>
+        <v>4.07</v>
       </c>
       <c r="F50" t="n">
-        <v>13.95</v>
+        <v>13.58</v>
       </c>
       <c r="G50" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="H50" t="n">
-        <v>84.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>289.16</v>
+        <v>128.93</v>
       </c>
       <c r="K50" t="n">
-        <v>-107.65</v>
+        <v>50.56</v>
       </c>
       <c r="L50" t="n">
-        <v>308.55</v>
+        <v>138.49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:19:26</t>
+          <t>06:16:52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.01</v>
+        <v>4.44</v>
       </c>
       <c r="F51" t="n">
-        <v>14.33</v>
+        <v>13.84</v>
       </c>
       <c r="G51" t="n">
-        <v>12.6</v>
+        <v>9.4</v>
       </c>
       <c r="H51" t="n">
-        <v>79</v>
+        <v>82.2</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>71.91</v>
+        <v>591.42</v>
       </c>
       <c r="K51" t="n">
-        <v>-174.75</v>
+        <v>197.26</v>
       </c>
       <c r="L51" t="n">
-        <v>188.97</v>
+        <v>623.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:21:02</t>
+          <t>06:18:51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.77</v>
+        <v>4.52</v>
       </c>
       <c r="F52" t="n">
-        <v>13.91</v>
+        <v>14.04</v>
       </c>
       <c r="G52" t="n">
-        <v>359.7</v>
+        <v>17.9</v>
       </c>
       <c r="H52" t="n">
-        <v>83.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-17.1</v>
+        <v>-167.5</v>
       </c>
       <c r="K52" t="n">
-        <v>258.47</v>
+        <v>-550.63</v>
       </c>
       <c r="L52" t="n">
-        <v>259.04</v>
+        <v>575.54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:26:05</t>
+          <t>06:22:13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
       <c r="F53" t="n">
-        <v>13.71</v>
+        <v>14.12</v>
       </c>
       <c r="G53" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="H53" t="n">
-        <v>85.8</v>
+        <v>87.3</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-165.51</v>
+        <v>-899.16</v>
       </c>
       <c r="K53" t="n">
-        <v>-279.56</v>
+        <v>187.75</v>
       </c>
       <c r="L53" t="n">
-        <v>324.88</v>
+        <v>918.55</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:28:14</t>
+          <t>06:23:03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.73</v>
+        <v>6.47</v>
       </c>
       <c r="F54" t="n">
-        <v>13.58</v>
+        <v>13.65</v>
       </c>
       <c r="G54" t="n">
-        <v>6.1</v>
+        <v>354.3</v>
       </c>
       <c r="H54" t="n">
-        <v>89.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-17.61</v>
+        <v>552.64</v>
       </c>
       <c r="K54" t="n">
-        <v>29.48</v>
+        <v>619.1</v>
       </c>
       <c r="L54" t="n">
-        <v>34.34</v>
+        <v>829.88</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:30:38</t>
+          <t>06:25:16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.48</v>
+        <v>4.61</v>
       </c>
       <c r="F55" t="n">
         <v>14.13</v>
       </c>
       <c r="G55" t="n">
-        <v>12.8</v>
+        <v>26.4</v>
       </c>
       <c r="H55" t="n">
-        <v>92.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-119.42</v>
+        <v>-349.52</v>
       </c>
       <c r="K55" t="n">
-        <v>40.45</v>
+        <v>-133.42</v>
       </c>
       <c r="L55" t="n">
-        <v>126.08</v>
+        <v>374.12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:35:45</t>
+          <t>06:30:31</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.78</v>
+        <v>4.03</v>
       </c>
       <c r="F56" t="n">
-        <v>13.52</v>
+        <v>14.13</v>
       </c>
       <c r="G56" t="n">
-        <v>9.800000000000001</v>
+        <v>16.1</v>
       </c>
       <c r="H56" t="n">
-        <v>83.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I56" t="n">
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>176.22</v>
+        <v>633.91</v>
       </c>
       <c r="K56" t="n">
-        <v>182.78</v>
+        <v>-36.04</v>
       </c>
       <c r="L56" t="n">
-        <v>253.89</v>
+        <v>634.9299999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:37:28</t>
+          <t>06:31:26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.12</v>
+        <v>3.9</v>
       </c>
       <c r="F57" t="n">
-        <v>13.88</v>
+        <v>13.55</v>
       </c>
       <c r="G57" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="H57" t="n">
-        <v>92.7</v>
+        <v>84</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>380.01</v>
+        <v>453.45</v>
       </c>
       <c r="K57" t="n">
-        <v>-161.22</v>
+        <v>287.95</v>
       </c>
       <c r="L57" t="n">
-        <v>412.79</v>
+        <v>537.15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:39:20</t>
+          <t>06:32:47</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.72</v>
+        <v>4.6</v>
       </c>
       <c r="F58" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="G58" t="n">
-        <v>13.8</v>
+        <v>2.9</v>
       </c>
       <c r="H58" t="n">
-        <v>77.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>16.43</v>
+        <v>556.52</v>
       </c>
       <c r="K58" t="n">
-        <v>16.59</v>
+        <v>-208.25</v>
       </c>
       <c r="L58" t="n">
-        <v>23.34</v>
+        <v>594.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:52:40</t>
+          <t>06:44:22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.72</v>
+        <v>3.86</v>
       </c>
       <c r="F59" t="n">
-        <v>13.34</v>
+        <v>13.96</v>
       </c>
       <c r="G59" t="n">
-        <v>359</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>83.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-182.84</v>
+        <v>-172.07</v>
       </c>
       <c r="K59" t="n">
-        <v>50.88</v>
+        <v>255.69</v>
       </c>
       <c r="L59" t="n">
-        <v>189.79</v>
+        <v>308.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:54:15</t>
+          <t>06:45:53</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.16</v>
+        <v>4.45</v>
       </c>
       <c r="F60" t="n">
-        <v>13.6</v>
+        <v>14.73</v>
       </c>
       <c r="G60" t="n">
-        <v>347.7</v>
+        <v>11.3</v>
       </c>
       <c r="H60" t="n">
-        <v>86.5</v>
+        <v>82.2</v>
       </c>
       <c r="I60" t="n">
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-322.69</v>
+        <v>-202.1</v>
       </c>
       <c r="K60" t="n">
-        <v>-98.01000000000001</v>
+        <v>-151.66</v>
       </c>
       <c r="L60" t="n">
-        <v>337.24</v>
+        <v>252.67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:56:44</t>
+          <t>06:47:57</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.77</v>
+        <v>4.39</v>
       </c>
       <c r="F61" t="n">
-        <v>13.59</v>
+        <v>13.84</v>
       </c>
       <c r="G61" t="n">
-        <v>359.6</v>
+        <v>21.3</v>
       </c>
       <c r="H61" t="n">
-        <v>85.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>73.59999999999999</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-134.54</v>
+        <v>141.76</v>
       </c>
       <c r="L61" t="n">
-        <v>153.36</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:01:17</t>
+          <t>06:52:02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.39</v>
+        <v>5.17</v>
       </c>
       <c r="F62" t="n">
-        <v>13.17</v>
+        <v>14.2</v>
       </c>
       <c r="G62" t="n">
-        <v>11.3</v>
+        <v>0.9</v>
       </c>
       <c r="H62" t="n">
-        <v>83.8</v>
+        <v>84.8</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>1.41</v>
+        <v>-231.22</v>
       </c>
       <c r="K62" t="n">
-        <v>94.58</v>
+        <v>67.89</v>
       </c>
       <c r="L62" t="n">
-        <v>94.59</v>
+        <v>240.98</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:03:49</t>
+          <t>06:53:25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.94</v>
+        <v>5.25</v>
       </c>
       <c r="F63" t="n">
-        <v>13.65</v>
+        <v>13.88</v>
       </c>
       <c r="G63" t="n">
-        <v>2.4</v>
+        <v>21</v>
       </c>
       <c r="H63" t="n">
-        <v>83.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>-16.73</v>
+        <v>165.96</v>
       </c>
       <c r="K63" t="n">
-        <v>108.78</v>
+        <v>-111.27</v>
       </c>
       <c r="L63" t="n">
-        <v>110.06</v>
+        <v>199.81</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:04:54</t>
+          <t>06:54:29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.4</v>
+        <v>4.23</v>
       </c>
       <c r="F64" t="n">
-        <v>14.33</v>
+        <v>13.64</v>
       </c>
       <c r="G64" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="H64" t="n">
-        <v>83.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-261.31</v>
+        <v>-262.69</v>
       </c>
       <c r="K64" t="n">
-        <v>-49.53</v>
+        <v>217.68</v>
       </c>
       <c r="L64" t="n">
-        <v>265.97</v>
+        <v>341.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:10:55</t>
+          <t>06:58:45</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.29</v>
+        <v>4.88</v>
       </c>
       <c r="F65" t="n">
-        <v>13.95</v>
+        <v>13.41</v>
       </c>
       <c r="G65" t="n">
-        <v>12.2</v>
+        <v>6.2</v>
       </c>
       <c r="H65" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-142.52</v>
+        <v>571.58</v>
       </c>
       <c r="K65" t="n">
-        <v>79.39</v>
+        <v>40.77</v>
       </c>
       <c r="L65" t="n">
-        <v>163.14</v>
+        <v>573.03</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:13:19</t>
+          <t>07:00:28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.31</v>
+        <v>5.03</v>
       </c>
       <c r="F66" t="n">
-        <v>13.68</v>
+        <v>12.94</v>
       </c>
       <c r="G66" t="n">
-        <v>358.5</v>
+        <v>7.6</v>
       </c>
       <c r="H66" t="n">
-        <v>83.8</v>
+        <v>88.5</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-161.72</v>
+        <v>46.22</v>
       </c>
       <c r="K66" t="n">
-        <v>13.43</v>
+        <v>374.84</v>
       </c>
       <c r="L66" t="n">
-        <v>162.28</v>
+        <v>377.68</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:15:12</t>
+          <t>07:01:25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.92</v>
+        <v>4.52</v>
       </c>
       <c r="F67" t="n">
-        <v>14.15</v>
+        <v>13.63</v>
       </c>
       <c r="G67" t="n">
-        <v>11.2</v>
+        <v>20.8</v>
       </c>
       <c r="H67" t="n">
-        <v>86.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>191.12</v>
+        <v>-496.95</v>
       </c>
       <c r="K67" t="n">
-        <v>416.61</v>
+        <v>198.88</v>
       </c>
       <c r="L67" t="n">
-        <v>458.35</v>
+        <v>535.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:19:11</t>
+          <t>07:07:37</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.16</v>
+        <v>4.67</v>
       </c>
       <c r="F68" t="n">
-        <v>13.42</v>
+        <v>14.22</v>
       </c>
       <c r="G68" t="n">
-        <v>354.3</v>
+        <v>359</v>
       </c>
       <c r="H68" t="n">
-        <v>78.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>187.27</v>
+        <v>-494.63</v>
       </c>
       <c r="K68" t="n">
-        <v>-178.05</v>
+        <v>-88.76000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>258.4</v>
+        <v>502.53</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:21:14</t>
+          <t>07:08:37</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="F69" t="n">
-        <v>13.78</v>
+        <v>13.83</v>
       </c>
       <c r="G69" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="H69" t="n">
-        <v>85.5</v>
+        <v>89.3</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-540.02</v>
+        <v>-690.1</v>
       </c>
       <c r="K69" t="n">
-        <v>-203.58</v>
+        <v>56.27</v>
       </c>
       <c r="L69" t="n">
-        <v>577.12</v>
+        <v>692.39</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:23:42</t>
+          <t>07:10:21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.42</v>
+        <v>4.24</v>
       </c>
       <c r="F70" t="n">
-        <v>13.66</v>
+        <v>13.71</v>
       </c>
       <c r="G70" t="n">
-        <v>9.199999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="H70" t="n">
-        <v>81.7</v>
+        <v>84</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>15.2</v>
+        <v>279.84</v>
       </c>
       <c r="K70" t="n">
-        <v>-64.63</v>
+        <v>186.18</v>
       </c>
       <c r="L70" t="n">
-        <v>66.39</v>
+        <v>336.11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:27:42</t>
+          <t>07:14:31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.31</v>
+        <v>5.49</v>
       </c>
       <c r="F71" t="n">
-        <v>14.62</v>
+        <v>14.31</v>
       </c>
       <c r="G71" t="n">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
       <c r="H71" t="n">
-        <v>80.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>462.65</v>
+        <v>-1053.3</v>
       </c>
       <c r="K71" t="n">
-        <v>589.76</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>749.5700000000001</v>
+        <v>1055.58</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:29:21</t>
+          <t>07:16:46</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.66</v>
+        <v>4.87</v>
       </c>
       <c r="F72" t="n">
-        <v>14.54</v>
+        <v>13.13</v>
       </c>
       <c r="G72" t="n">
-        <v>17.9</v>
+        <v>23.5</v>
       </c>
       <c r="H72" t="n">
-        <v>81.2</v>
+        <v>90</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-411.03</v>
+        <v>-1094.58</v>
       </c>
       <c r="K72" t="n">
-        <v>-281.14</v>
+        <v>441.03</v>
       </c>
       <c r="L72" t="n">
-        <v>497.98</v>
+        <v>1180.09</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:30:06</t>
+          <t>07:19:29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.58</v>
+        <v>4.35</v>
       </c>
       <c r="F73" t="n">
-        <v>12.98</v>
+        <v>12.99</v>
       </c>
       <c r="G73" t="n">
-        <v>7.8</v>
+        <v>356.2</v>
       </c>
       <c r="H73" t="n">
-        <v>85.3</v>
+        <v>79.5</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-298.3</v>
+        <v>516.77</v>
       </c>
       <c r="K73" t="n">
-        <v>57.56</v>
+        <v>-40.48</v>
       </c>
       <c r="L73" t="n">
-        <v>303.81</v>
+        <v>518.35</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:42:50</t>
+          <t>07:29:21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.74</v>
+        <v>4.11</v>
       </c>
       <c r="F74" t="n">
-        <v>12.72</v>
+        <v>13.42</v>
       </c>
       <c r="G74" t="n">
-        <v>359.4</v>
+        <v>6.9</v>
       </c>
       <c r="H74" t="n">
-        <v>86.5</v>
+        <v>95.8</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>89.06999999999999</v>
+        <v>-203.83</v>
       </c>
       <c r="K74" t="n">
-        <v>-129.92</v>
+        <v>-60.77</v>
       </c>
       <c r="L74" t="n">
-        <v>157.52</v>
+        <v>212.69</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:44:35</t>
+          <t>07:30:36</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.58</v>
+        <v>3.51</v>
       </c>
       <c r="F75" t="n">
-        <v>13.7</v>
+        <v>14.21</v>
       </c>
       <c r="G75" t="n">
-        <v>25.3</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>81.2</v>
+        <v>89.8</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>122.32</v>
+        <v>20.16</v>
       </c>
       <c r="K75" t="n">
-        <v>-24.37</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>124.73</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:45:55</t>
+          <t>07:31:43</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.86</v>
+        <v>4.67</v>
       </c>
       <c r="F76" t="n">
-        <v>13.93</v>
+        <v>13.14</v>
       </c>
       <c r="G76" t="n">
-        <v>1.4</v>
+        <v>12.9</v>
       </c>
       <c r="H76" t="n">
-        <v>86</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>45.39</v>
+        <v>37.28</v>
       </c>
       <c r="K76" t="n">
-        <v>-217.86</v>
+        <v>-81.18000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>222.54</v>
+        <v>89.33</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:50:37</t>
+          <t>07:36:46</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.25</v>
+        <v>4.82</v>
       </c>
       <c r="F77" t="n">
-        <v>14.21</v>
+        <v>13.87</v>
       </c>
       <c r="G77" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="H77" t="n">
-        <v>78.8</v>
+        <v>80.3</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>156.88</v>
+        <v>314.24</v>
       </c>
       <c r="K77" t="n">
-        <v>49.16</v>
+        <v>-156.81</v>
       </c>
       <c r="L77" t="n">
-        <v>164.4</v>
+        <v>351.19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:52:13</t>
+          <t>07:39:09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.93</v>
+        <v>4.66</v>
       </c>
       <c r="F78" t="n">
-        <v>14.09</v>
+        <v>13.91</v>
       </c>
       <c r="G78" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-11.38</v>
+        <v>-117.23</v>
       </c>
       <c r="K78" t="n">
-        <v>-197.89</v>
+        <v>525.45</v>
       </c>
       <c r="L78" t="n">
-        <v>198.22</v>
+        <v>538.37</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:54:28</t>
+          <t>07:39:58</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.03</v>
+        <v>4.73</v>
       </c>
       <c r="F79" t="n">
-        <v>13.71</v>
+        <v>14.08</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1</v>
+        <v>7.8</v>
       </c>
       <c r="H79" t="n">
-        <v>87.5</v>
+        <v>88.3</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>73.95999999999999</v>
+        <v>-25.54</v>
       </c>
       <c r="K79" t="n">
-        <v>-84.19</v>
+        <v>-164.77</v>
       </c>
       <c r="L79" t="n">
-        <v>112.06</v>
+        <v>166.74</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:58:05</t>
+          <t>07:44:20</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.99</v>
+        <v>3.69</v>
       </c>
       <c r="F80" t="n">
-        <v>13.43</v>
+        <v>14.48</v>
       </c>
       <c r="G80" t="n">
-        <v>9.699999999999999</v>
+        <v>359.7</v>
       </c>
       <c r="H80" t="n">
-        <v>83.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>59</v>
+        <v>-477.73</v>
       </c>
       <c r="K80" t="n">
-        <v>-41.9</v>
+        <v>63.83</v>
       </c>
       <c r="L80" t="n">
-        <v>72.36</v>
+        <v>481.98</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:59:49</t>
+          <t>07:46:43</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.5</v>
+        <v>5.09</v>
       </c>
       <c r="F81" t="n">
-        <v>14.06</v>
+        <v>14.5</v>
       </c>
       <c r="G81" t="n">
-        <v>16.6</v>
+        <v>15.4</v>
       </c>
       <c r="H81" t="n">
-        <v>88.5</v>
+        <v>88.7</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.31</v>
+        <v>-429.63</v>
       </c>
       <c r="K81" t="n">
-        <v>-34.19</v>
+        <v>314.76</v>
       </c>
       <c r="L81" t="n">
-        <v>37.46</v>
+        <v>532.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:01:52</t>
+          <t>07:47:50</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.17</v>
+        <v>5.15</v>
       </c>
       <c r="F82" t="n">
-        <v>14.72</v>
+        <v>14.11</v>
       </c>
       <c r="G82" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="H82" t="n">
-        <v>87</v>
+        <v>81.8</v>
       </c>
       <c r="I82" t="n">
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-95.62</v>
+        <v>-92.26000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-74.86</v>
+        <v>910.03</v>
       </c>
       <c r="L82" t="n">
-        <v>121.44</v>
+        <v>914.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:06:17</t>
+          <t>07:52:39</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.43</v>
+        <v>5.7</v>
       </c>
       <c r="F83" t="n">
-        <v>13.4</v>
+        <v>14.5</v>
       </c>
       <c r="G83" t="n">
-        <v>11.2</v>
+        <v>14.5</v>
       </c>
       <c r="H83" t="n">
-        <v>76.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-224.72</v>
+        <v>-223.5</v>
       </c>
       <c r="K83" t="n">
-        <v>332.26</v>
+        <v>161.2</v>
       </c>
       <c r="L83" t="n">
-        <v>401.12</v>
+        <v>275.56</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:07:48</t>
+          <t>07:54:33</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.01</v>
+        <v>4.14</v>
       </c>
       <c r="F84" t="n">
-        <v>13.72</v>
+        <v>14.01</v>
       </c>
       <c r="G84" t="n">
-        <v>8.199999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="H84" t="n">
-        <v>86.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>13.54</v>
+        <v>-625.67</v>
       </c>
       <c r="K84" t="n">
-        <v>544.61</v>
+        <v>-502.84</v>
       </c>
       <c r="L84" t="n">
-        <v>544.78</v>
+        <v>802.6900000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:08:54</t>
+          <t>07:56:05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.13</v>
+        <v>4.97</v>
       </c>
       <c r="F85" t="n">
-        <v>13.2</v>
+        <v>13.73</v>
       </c>
       <c r="G85" t="n">
-        <v>356.6</v>
+        <v>4.4</v>
       </c>
       <c r="H85" t="n">
-        <v>83.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-326.73</v>
+        <v>-83.64</v>
       </c>
       <c r="K85" t="n">
-        <v>183.37</v>
+        <v>413.98</v>
       </c>
       <c r="L85" t="n">
-        <v>374.67</v>
+        <v>422.34</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:12:22</t>
+          <t>07:59:55</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.56</v>
+        <v>4.24</v>
       </c>
       <c r="F86" t="n">
-        <v>14.19</v>
+        <v>13.36</v>
       </c>
       <c r="G86" t="n">
-        <v>12.3</v>
+        <v>25.9</v>
       </c>
       <c r="H86" t="n">
-        <v>81.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-509.45</v>
+        <v>-100.67</v>
       </c>
       <c r="K86" t="n">
-        <v>149.95</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>531.0599999999999</v>
+        <v>135.39</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:14:11</t>
+          <t>08:01:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.68</v>
+        <v>4.43</v>
       </c>
       <c r="F87" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G87" t="n">
-        <v>358.9</v>
+        <v>358.2</v>
       </c>
       <c r="H87" t="n">
-        <v>78</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-61.34</v>
+        <v>-421.36</v>
       </c>
       <c r="K87" t="n">
-        <v>-154.1</v>
+        <v>93.02</v>
       </c>
       <c r="L87" t="n">
-        <v>165.86</v>
+        <v>431.51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:16:31</t>
+          <t>08:04:21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.84</v>
+        <v>4.59</v>
       </c>
       <c r="F88" t="n">
-        <v>13.65</v>
+        <v>13.87</v>
       </c>
       <c r="G88" t="n">
-        <v>19.2</v>
+        <v>11.8</v>
       </c>
       <c r="H88" t="n">
-        <v>76.2</v>
+        <v>79.2</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-420.4</v>
+        <v>483.38</v>
       </c>
       <c r="K88" t="n">
-        <v>320.44</v>
+        <v>621.62</v>
       </c>
       <c r="L88" t="n">
-        <v>528.6</v>
+        <v>787.4400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.12</v>
+        <v>-11.95</v>
       </c>
       <c r="K14" t="n">
-        <v>-290.26</v>
+        <v>-342.76</v>
       </c>
       <c r="L14" t="n">
-        <v>290.44</v>
+        <v>342.97</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>38.89</v>
+        <v>50.99</v>
       </c>
       <c r="K15" t="n">
-        <v>-160.93</v>
+        <v>-211</v>
       </c>
       <c r="L15" t="n">
-        <v>165.57</v>
+        <v>217.08</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>159.74</v>
+        <v>173.42</v>
       </c>
       <c r="K16" t="n">
-        <v>166.07</v>
+        <v>180.29</v>
       </c>
       <c r="L16" t="n">
-        <v>230.43</v>
+        <v>250.16</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="K17" t="n">
-        <v>-176.11</v>
+        <v>-246.08</v>
       </c>
       <c r="L17" t="n">
-        <v>176.11</v>
+        <v>246.08</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>58.56</v>
+        <v>111.5</v>
       </c>
       <c r="K18" t="n">
-        <v>-77.55</v>
+        <v>-147.67</v>
       </c>
       <c r="L18" t="n">
-        <v>97.18000000000001</v>
+        <v>185.03</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>29.7</v>
+        <v>49.57</v>
       </c>
       <c r="K19" t="n">
-        <v>176.73</v>
+        <v>294.92</v>
       </c>
       <c r="L19" t="n">
-        <v>179.21</v>
+        <v>299.06</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-647.28</v>
+        <v>-783.76</v>
       </c>
       <c r="K20" t="n">
-        <v>60.58</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>650.11</v>
+        <v>787.1900000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>29.42</v>
+        <v>46.79</v>
       </c>
       <c r="K21" t="n">
-        <v>-215.31</v>
+        <v>-342.4</v>
       </c>
       <c r="L21" t="n">
-        <v>217.31</v>
+        <v>345.58</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>231.59</v>
+        <v>244.59</v>
       </c>
       <c r="K22" t="n">
-        <v>407.58</v>
+        <v>430.47</v>
       </c>
       <c r="L22" t="n">
-        <v>468.78</v>
+        <v>495.11</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-401.32</v>
+        <v>-508.93</v>
       </c>
       <c r="K23" t="n">
-        <v>-848.24</v>
+        <v>-1075.68</v>
       </c>
       <c r="L23" t="n">
-        <v>938.39</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-532.76</v>
+        <v>-775.8</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.7</v>
+        <v>-2.48</v>
       </c>
       <c r="L24" t="n">
-        <v>532.76</v>
+        <v>775.8099999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>243.07</v>
+        <v>518.78</v>
       </c>
       <c r="K25" t="n">
-        <v>20.51</v>
+        <v>43.77</v>
       </c>
       <c r="L25" t="n">
-        <v>243.94</v>
+        <v>520.63</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-502.54</v>
+        <v>-805.7</v>
       </c>
       <c r="K26" t="n">
-        <v>-195.58</v>
+        <v>-313.57</v>
       </c>
       <c r="L26" t="n">
-        <v>539.25</v>
+        <v>864.5700000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-219.51</v>
+        <v>-278.85</v>
       </c>
       <c r="K27" t="n">
-        <v>1499.39</v>
+        <v>1904.66</v>
       </c>
       <c r="L27" t="n">
-        <v>1515.37</v>
+        <v>1924.96</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-119.76</v>
+        <v>-203.4</v>
       </c>
       <c r="K28" t="n">
-        <v>-576.8</v>
+        <v>-979.66</v>
       </c>
       <c r="L28" t="n">
-        <v>589.1</v>
+        <v>1000.55</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>141.99</v>
+        <v>191.44</v>
       </c>
       <c r="K29" t="n">
-        <v>10.22</v>
+        <v>13.78</v>
       </c>
       <c r="L29" t="n">
-        <v>142.36</v>
+        <v>191.93</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>68.34999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="K30" t="n">
-        <v>364.64</v>
+        <v>402.78</v>
       </c>
       <c r="L30" t="n">
-        <v>370.99</v>
+        <v>409.8</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>182.25</v>
+        <v>183.11</v>
       </c>
       <c r="K31" t="n">
-        <v>157.41</v>
+        <v>158.16</v>
       </c>
       <c r="L31" t="n">
-        <v>240.82</v>
+        <v>241.96</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-52.22</v>
+        <v>-53.76</v>
       </c>
       <c r="K32" t="n">
-        <v>-418.73</v>
+        <v>-431.06</v>
       </c>
       <c r="L32" t="n">
-        <v>421.97</v>
+        <v>434.4</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>171.08</v>
+        <v>277.14</v>
       </c>
       <c r="K33" t="n">
-        <v>71.83</v>
+        <v>116.37</v>
       </c>
       <c r="L33" t="n">
-        <v>185.55</v>
+        <v>300.58</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-109.81</v>
+        <v>-211.73</v>
       </c>
       <c r="K34" t="n">
-        <v>31.11</v>
+        <v>59.98</v>
       </c>
       <c r="L34" t="n">
-        <v>114.13</v>
+        <v>220.06</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>154.67</v>
+        <v>304.75</v>
       </c>
       <c r="K35" t="n">
-        <v>30.1</v>
+        <v>59.3</v>
       </c>
       <c r="L35" t="n">
-        <v>157.57</v>
+        <v>310.47</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>51.59</v>
+        <v>70.31</v>
       </c>
       <c r="K36" t="n">
-        <v>-485.91</v>
+        <v>-662.15</v>
       </c>
       <c r="L36" t="n">
-        <v>488.65</v>
+        <v>665.87</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-226.43</v>
+        <v>-295.73</v>
       </c>
       <c r="K37" t="n">
-        <v>-250.67</v>
+        <v>-327.39</v>
       </c>
       <c r="L37" t="n">
-        <v>337.8</v>
+        <v>441.18</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-30.02</v>
+        <v>-66.7</v>
       </c>
       <c r="K38" t="n">
-        <v>188.66</v>
+        <v>419.24</v>
       </c>
       <c r="L38" t="n">
-        <v>191.03</v>
+        <v>424.51</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-452.16</v>
+        <v>-616.5599999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>7.21</v>
+        <v>9.83</v>
       </c>
       <c r="L39" t="n">
-        <v>452.22</v>
+        <v>616.64</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-570.0700000000001</v>
+        <v>-768.14</v>
       </c>
       <c r="K40" t="n">
-        <v>383.81</v>
+        <v>517.17</v>
       </c>
       <c r="L40" t="n">
-        <v>687.24</v>
+        <v>926.02</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-667.4400000000001</v>
+        <v>-928.2</v>
       </c>
       <c r="K41" t="n">
-        <v>-639.85</v>
+        <v>-889.83</v>
       </c>
       <c r="L41" t="n">
-        <v>924.6</v>
+        <v>1285.83</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>491.84</v>
+        <v>734.98</v>
       </c>
       <c r="K42" t="n">
-        <v>299.04</v>
+        <v>446.87</v>
       </c>
       <c r="L42" t="n">
-        <v>575.61</v>
+        <v>860.17</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>636.6</v>
+        <v>966.11</v>
       </c>
       <c r="K43" t="n">
-        <v>99.73999999999999</v>
+        <v>151.36</v>
       </c>
       <c r="L43" t="n">
-        <v>644.37</v>
+        <v>977.9</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-203.61</v>
+        <v>-231.18</v>
       </c>
       <c r="K44" t="n">
-        <v>-112.4</v>
+        <v>-127.63</v>
       </c>
       <c r="L44" t="n">
-        <v>232.58</v>
+        <v>264.07</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-74.8</v>
+        <v>-125.67</v>
       </c>
       <c r="K45" t="n">
-        <v>109.86</v>
+        <v>184.58</v>
       </c>
       <c r="L45" t="n">
-        <v>132.91</v>
+        <v>223.3</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>262.69</v>
+        <v>308</v>
       </c>
       <c r="K46" t="n">
-        <v>-208.46</v>
+        <v>-244.41</v>
       </c>
       <c r="L46" t="n">
-        <v>335.35</v>
+        <v>393.19</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-203.56</v>
+        <v>-317.26</v>
       </c>
       <c r="K47" t="n">
-        <v>134.56</v>
+        <v>209.73</v>
       </c>
       <c r="L47" t="n">
-        <v>244.01</v>
+        <v>380.32</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-281.37</v>
+        <v>-341.79</v>
       </c>
       <c r="K48" t="n">
-        <v>57.6</v>
+        <v>69.97</v>
       </c>
       <c r="L48" t="n">
-        <v>287.2</v>
+        <v>348.87</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-35.45</v>
+        <v>-56.25</v>
       </c>
       <c r="K49" t="n">
-        <v>-149.77</v>
+        <v>-237.61</v>
       </c>
       <c r="L49" t="n">
-        <v>153.91</v>
+        <v>244.17</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>128.93</v>
+        <v>294.17</v>
       </c>
       <c r="K50" t="n">
-        <v>50.56</v>
+        <v>115.35</v>
       </c>
       <c r="L50" t="n">
-        <v>138.49</v>
+        <v>315.97</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>591.42</v>
+        <v>680.39</v>
       </c>
       <c r="K51" t="n">
-        <v>197.26</v>
+        <v>226.93</v>
       </c>
       <c r="L51" t="n">
-        <v>623.45</v>
+        <v>717.24</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-167.5</v>
+        <v>-217.36</v>
       </c>
       <c r="K52" t="n">
-        <v>-550.63</v>
+        <v>-714.54</v>
       </c>
       <c r="L52" t="n">
-        <v>575.54</v>
+        <v>746.86</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-899.16</v>
+        <v>-1150.32</v>
       </c>
       <c r="K53" t="n">
-        <v>187.75</v>
+        <v>240.19</v>
       </c>
       <c r="L53" t="n">
-        <v>918.55</v>
+        <v>1175.12</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>552.64</v>
+        <v>887.72</v>
       </c>
       <c r="K54" t="n">
-        <v>619.1</v>
+        <v>994.48</v>
       </c>
       <c r="L54" t="n">
-        <v>829.88</v>
+        <v>1333.05</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-349.52</v>
+        <v>-649.2</v>
       </c>
       <c r="K55" t="n">
-        <v>-133.42</v>
+        <v>-247.83</v>
       </c>
       <c r="L55" t="n">
-        <v>374.12</v>
+        <v>694.9</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>633.91</v>
+        <v>955.16</v>
       </c>
       <c r="K56" t="n">
-        <v>-36.04</v>
+        <v>-54.31</v>
       </c>
       <c r="L56" t="n">
-        <v>634.9299999999999</v>
+        <v>956.7</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>453.45</v>
+        <v>751.96</v>
       </c>
       <c r="K57" t="n">
-        <v>287.95</v>
+        <v>477.51</v>
       </c>
       <c r="L57" t="n">
-        <v>537.15</v>
+        <v>890.76</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>556.52</v>
+        <v>970.79</v>
       </c>
       <c r="K58" t="n">
-        <v>-208.25</v>
+        <v>-363.27</v>
       </c>
       <c r="L58" t="n">
-        <v>594.2</v>
+        <v>1036.53</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-172.07</v>
+        <v>-192.4</v>
       </c>
       <c r="K59" t="n">
-        <v>255.69</v>
+        <v>285.9</v>
       </c>
       <c r="L59" t="n">
-        <v>308.2</v>
+        <v>344.61</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-202.1</v>
+        <v>-245.19</v>
       </c>
       <c r="K60" t="n">
-        <v>-151.66</v>
+        <v>-183.99</v>
       </c>
       <c r="L60" t="n">
-        <v>252.67</v>
+        <v>306.55</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>74.18000000000001</v>
+        <v>114.82</v>
       </c>
       <c r="K61" t="n">
-        <v>141.76</v>
+        <v>219.42</v>
       </c>
       <c r="L61" t="n">
-        <v>159.99</v>
+        <v>247.65</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-231.22</v>
+        <v>-347.43</v>
       </c>
       <c r="K62" t="n">
-        <v>67.89</v>
+        <v>102.01</v>
       </c>
       <c r="L62" t="n">
-        <v>240.98</v>
+        <v>362.09</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>165.96</v>
+        <v>280.84</v>
       </c>
       <c r="K63" t="n">
-        <v>-111.27</v>
+        <v>-188.28</v>
       </c>
       <c r="L63" t="n">
-        <v>199.81</v>
+        <v>338.11</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-262.69</v>
+        <v>-326.74</v>
       </c>
       <c r="K64" t="n">
-        <v>217.68</v>
+        <v>270.75</v>
       </c>
       <c r="L64" t="n">
-        <v>341.16</v>
+        <v>424.34</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>571.58</v>
+        <v>718.1</v>
       </c>
       <c r="K65" t="n">
-        <v>40.77</v>
+        <v>51.23</v>
       </c>
       <c r="L65" t="n">
-        <v>573.03</v>
+        <v>719.92</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>46.22</v>
+        <v>63.83</v>
       </c>
       <c r="K66" t="n">
-        <v>374.84</v>
+        <v>517.64</v>
       </c>
       <c r="L66" t="n">
-        <v>377.68</v>
+        <v>521.5599999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-496.95</v>
+        <v>-597.95</v>
       </c>
       <c r="K67" t="n">
-        <v>198.88</v>
+        <v>239.3</v>
       </c>
       <c r="L67" t="n">
-        <v>535.27</v>
+        <v>644.0599999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-494.63</v>
+        <v>-808.78</v>
       </c>
       <c r="K68" t="n">
-        <v>-88.76000000000001</v>
+        <v>-145.14</v>
       </c>
       <c r="L68" t="n">
-        <v>502.53</v>
+        <v>821.7</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-690.1</v>
+        <v>-943.36</v>
       </c>
       <c r="K69" t="n">
-        <v>56.27</v>
+        <v>76.92</v>
       </c>
       <c r="L69" t="n">
-        <v>692.39</v>
+        <v>946.49</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>279.84</v>
+        <v>496.95</v>
       </c>
       <c r="K70" t="n">
-        <v>186.18</v>
+        <v>330.64</v>
       </c>
       <c r="L70" t="n">
-        <v>336.11</v>
+        <v>596.89</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-1053.3</v>
+        <v>-1672.28</v>
       </c>
       <c r="K71" t="n">
-        <v>69.34999999999999</v>
+        <v>110.11</v>
       </c>
       <c r="L71" t="n">
-        <v>1055.58</v>
+        <v>1675.91</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-1094.58</v>
+        <v>-1405.93</v>
       </c>
       <c r="K72" t="n">
-        <v>441.03</v>
+        <v>566.47</v>
       </c>
       <c r="L72" t="n">
-        <v>1180.09</v>
+        <v>1515.76</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>516.77</v>
+        <v>797.61</v>
       </c>
       <c r="K73" t="n">
-        <v>-40.48</v>
+        <v>-62.47</v>
       </c>
       <c r="L73" t="n">
-        <v>518.35</v>
+        <v>800.05</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-203.83</v>
+        <v>-266.74</v>
       </c>
       <c r="K74" t="n">
-        <v>-60.77</v>
+        <v>-79.52</v>
       </c>
       <c r="L74" t="n">
-        <v>212.69</v>
+        <v>278.34</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>20.16</v>
+        <v>29.68</v>
       </c>
       <c r="K75" t="n">
-        <v>87.81999999999999</v>
+        <v>129.29</v>
       </c>
       <c r="L75" t="n">
-        <v>90.09999999999999</v>
+        <v>132.65</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>37.28</v>
+        <v>82.02</v>
       </c>
       <c r="K76" t="n">
-        <v>-81.18000000000001</v>
+        <v>-178.58</v>
       </c>
       <c r="L76" t="n">
-        <v>89.33</v>
+        <v>196.51</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>314.24</v>
+        <v>367.27</v>
       </c>
       <c r="K77" t="n">
-        <v>-156.81</v>
+        <v>-183.27</v>
       </c>
       <c r="L77" t="n">
-        <v>351.19</v>
+        <v>410.45</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-117.23</v>
+        <v>-127.35</v>
       </c>
       <c r="K78" t="n">
-        <v>525.45</v>
+        <v>570.8</v>
       </c>
       <c r="L78" t="n">
-        <v>538.37</v>
+        <v>584.83</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-25.54</v>
+        <v>-45.04</v>
       </c>
       <c r="K79" t="n">
-        <v>-164.77</v>
+        <v>-290.56</v>
       </c>
       <c r="L79" t="n">
-        <v>166.74</v>
+        <v>294.03</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-477.73</v>
+        <v>-584.61</v>
       </c>
       <c r="K80" t="n">
-        <v>63.83</v>
+        <v>78.11</v>
       </c>
       <c r="L80" t="n">
-        <v>481.98</v>
+        <v>589.8</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-429.63</v>
+        <v>-547.5700000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>314.76</v>
+        <v>401.17</v>
       </c>
       <c r="L81" t="n">
-        <v>532.6</v>
+        <v>678.8</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-92.26000000000001</v>
+        <v>-106.43</v>
       </c>
       <c r="K82" t="n">
-        <v>910.03</v>
+        <v>1049.72</v>
       </c>
       <c r="L82" t="n">
-        <v>914.7</v>
+        <v>1055.1</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-223.5</v>
+        <v>-472.04</v>
       </c>
       <c r="K83" t="n">
-        <v>161.2</v>
+        <v>340.47</v>
       </c>
       <c r="L83" t="n">
-        <v>275.56</v>
+        <v>582.02</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-625.67</v>
+        <v>-808.92</v>
       </c>
       <c r="K84" t="n">
-        <v>-502.84</v>
+        <v>-650.11</v>
       </c>
       <c r="L84" t="n">
-        <v>802.6900000000001</v>
+        <v>1037.78</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-83.64</v>
+        <v>-147.57</v>
       </c>
       <c r="K85" t="n">
-        <v>413.98</v>
+        <v>730.46</v>
       </c>
       <c r="L85" t="n">
-        <v>422.34</v>
+        <v>745.22</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-100.67</v>
+        <v>-353.1</v>
       </c>
       <c r="K86" t="n">
-        <v>90.54000000000001</v>
+        <v>317.57</v>
       </c>
       <c r="L86" t="n">
-        <v>135.39</v>
+        <v>474.9</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-421.36</v>
+        <v>-767.48</v>
       </c>
       <c r="K87" t="n">
-        <v>93.02</v>
+        <v>169.42</v>
       </c>
       <c r="L87" t="n">
-        <v>431.51</v>
+        <v>785.96</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>483.38</v>
+        <v>733.75</v>
       </c>
       <c r="K88" t="n">
-        <v>621.62</v>
+        <v>943.59</v>
       </c>
       <c r="L88" t="n">
-        <v>787.4400000000001</v>
+        <v>1195.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.95</v>
+        <v>-7.52</v>
       </c>
       <c r="K14" t="n">
-        <v>-342.76</v>
+        <v>-215.58</v>
       </c>
       <c r="L14" t="n">
-        <v>342.97</v>
+        <v>215.71</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>50.99</v>
+        <v>32.92</v>
       </c>
       <c r="K15" t="n">
-        <v>-211</v>
+        <v>-136.24</v>
       </c>
       <c r="L15" t="n">
-        <v>217.08</v>
+        <v>140.16</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>173.42</v>
+        <v>118.62</v>
       </c>
       <c r="K16" t="n">
-        <v>180.29</v>
+        <v>123.32</v>
       </c>
       <c r="L16" t="n">
-        <v>250.16</v>
+        <v>171.11</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>1.54</v>
+        <v>0.92</v>
       </c>
       <c r="K17" t="n">
-        <v>-246.08</v>
+        <v>-146.49</v>
       </c>
       <c r="L17" t="n">
-        <v>246.08</v>
+        <v>146.49</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>111.5</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-147.67</v>
+        <v>-96.22</v>
       </c>
       <c r="L18" t="n">
-        <v>185.03</v>
+        <v>120.57</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>49.57</v>
+        <v>28.23</v>
       </c>
       <c r="K19" t="n">
-        <v>294.92</v>
+        <v>167.93</v>
       </c>
       <c r="L19" t="n">
-        <v>299.06</v>
+        <v>170.29</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-783.76</v>
+        <v>-408.63</v>
       </c>
       <c r="K20" t="n">
-        <v>73.34999999999999</v>
+        <v>38.24</v>
       </c>
       <c r="L20" t="n">
-        <v>787.1900000000001</v>
+        <v>410.41</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>46.79</v>
+        <v>26.69</v>
       </c>
       <c r="K21" t="n">
-        <v>-342.4</v>
+        <v>-195.29</v>
       </c>
       <c r="L21" t="n">
-        <v>345.58</v>
+        <v>197.11</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>244.59</v>
+        <v>142.58</v>
       </c>
       <c r="K22" t="n">
-        <v>430.47</v>
+        <v>250.94</v>
       </c>
       <c r="L22" t="n">
-        <v>495.11</v>
+        <v>288.62</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-508.93</v>
+        <v>-235.42</v>
       </c>
       <c r="K23" t="n">
-        <v>-1075.68</v>
+        <v>-497.58</v>
       </c>
       <c r="L23" t="n">
-        <v>1190</v>
+        <v>550.47</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-775.8</v>
+        <v>-368.03</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.48</v>
+        <v>-1.18</v>
       </c>
       <c r="L24" t="n">
-        <v>775.8099999999999</v>
+        <v>368.03</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>518.78</v>
+        <v>230.83</v>
       </c>
       <c r="K25" t="n">
-        <v>43.77</v>
+        <v>19.48</v>
       </c>
       <c r="L25" t="n">
-        <v>520.63</v>
+        <v>231.65</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-805.7</v>
+        <v>-355.16</v>
       </c>
       <c r="K26" t="n">
-        <v>-313.57</v>
+        <v>-138.22</v>
       </c>
       <c r="L26" t="n">
-        <v>864.5700000000001</v>
+        <v>381.11</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-278.85</v>
+        <v>-114.41</v>
       </c>
       <c r="K27" t="n">
-        <v>1904.66</v>
+        <v>781.48</v>
       </c>
       <c r="L27" t="n">
-        <v>1924.96</v>
+        <v>789.8099999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-203.4</v>
+        <v>-82.95</v>
       </c>
       <c r="K28" t="n">
-        <v>-979.66</v>
+        <v>-399.52</v>
       </c>
       <c r="L28" t="n">
-        <v>1000.55</v>
+        <v>408.04</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>191.44</v>
+        <v>126.92</v>
       </c>
       <c r="K29" t="n">
-        <v>13.78</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>191.93</v>
+        <v>127.25</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>75.5</v>
+        <v>50.32</v>
       </c>
       <c r="K30" t="n">
-        <v>402.78</v>
+        <v>268.46</v>
       </c>
       <c r="L30" t="n">
-        <v>409.8</v>
+        <v>273.14</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>183.11</v>
+        <v>123.48</v>
       </c>
       <c r="K31" t="n">
-        <v>158.16</v>
+        <v>106.65</v>
       </c>
       <c r="L31" t="n">
-        <v>241.96</v>
+        <v>163.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-53.76</v>
+        <v>-35.27</v>
       </c>
       <c r="K32" t="n">
-        <v>-431.06</v>
+        <v>-282.79</v>
       </c>
       <c r="L32" t="n">
-        <v>434.4</v>
+        <v>284.98</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>277.14</v>
+        <v>157.81</v>
       </c>
       <c r="K33" t="n">
-        <v>116.37</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>300.58</v>
+        <v>171.16</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-211.73</v>
+        <v>-133.11</v>
       </c>
       <c r="K34" t="n">
-        <v>59.98</v>
+        <v>37.71</v>
       </c>
       <c r="L34" t="n">
-        <v>220.06</v>
+        <v>138.35</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>304.75</v>
+        <v>156.22</v>
       </c>
       <c r="K35" t="n">
-        <v>59.3</v>
+        <v>30.4</v>
       </c>
       <c r="L35" t="n">
-        <v>310.47</v>
+        <v>159.15</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>70.31</v>
+        <v>35</v>
       </c>
       <c r="K36" t="n">
-        <v>-662.15</v>
+        <v>-329.61</v>
       </c>
       <c r="L36" t="n">
-        <v>665.87</v>
+        <v>331.46</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-295.73</v>
+        <v>-165.83</v>
       </c>
       <c r="K37" t="n">
-        <v>-327.39</v>
+        <v>-183.58</v>
       </c>
       <c r="L37" t="n">
-        <v>441.18</v>
+        <v>247.39</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-66.7</v>
+        <v>-31.32</v>
       </c>
       <c r="K38" t="n">
-        <v>419.24</v>
+        <v>196.85</v>
       </c>
       <c r="L38" t="n">
-        <v>424.51</v>
+        <v>199.33</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-616.5599999999999</v>
+        <v>-308.14</v>
       </c>
       <c r="K39" t="n">
-        <v>9.83</v>
+        <v>4.91</v>
       </c>
       <c r="L39" t="n">
-        <v>616.64</v>
+        <v>308.18</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-768.14</v>
+        <v>-372.67</v>
       </c>
       <c r="K40" t="n">
-        <v>517.17</v>
+        <v>250.91</v>
       </c>
       <c r="L40" t="n">
-        <v>926.02</v>
+        <v>449.26</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-928.2</v>
+        <v>-390.25</v>
       </c>
       <c r="K41" t="n">
-        <v>-889.83</v>
+        <v>-374.12</v>
       </c>
       <c r="L41" t="n">
-        <v>1285.83</v>
+        <v>540.61</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>734.98</v>
+        <v>334.11</v>
       </c>
       <c r="K42" t="n">
-        <v>446.87</v>
+        <v>203.14</v>
       </c>
       <c r="L42" t="n">
-        <v>860.17</v>
+        <v>391.01</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>966.11</v>
+        <v>402.56</v>
       </c>
       <c r="K43" t="n">
-        <v>151.36</v>
+        <v>63.07</v>
       </c>
       <c r="L43" t="n">
-        <v>977.9</v>
+        <v>407.47</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-231.18</v>
+        <v>-159.38</v>
       </c>
       <c r="K44" t="n">
-        <v>-127.63</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>264.07</v>
+        <v>182.06</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-125.67</v>
+        <v>-75.81</v>
       </c>
       <c r="K45" t="n">
-        <v>184.58</v>
+        <v>111.35</v>
       </c>
       <c r="L45" t="n">
-        <v>223.3</v>
+        <v>134.71</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>308</v>
+        <v>185.57</v>
       </c>
       <c r="K46" t="n">
-        <v>-244.41</v>
+        <v>-147.26</v>
       </c>
       <c r="L46" t="n">
-        <v>393.19</v>
+        <v>236.9</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-317.26</v>
+        <v>-182.4</v>
       </c>
       <c r="K47" t="n">
-        <v>209.73</v>
+        <v>120.58</v>
       </c>
       <c r="L47" t="n">
-        <v>380.32</v>
+        <v>218.65</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-341.79</v>
+        <v>-208.32</v>
       </c>
       <c r="K48" t="n">
-        <v>69.97</v>
+        <v>42.65</v>
       </c>
       <c r="L48" t="n">
-        <v>348.87</v>
+        <v>212.64</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-56.25</v>
+        <v>-36.38</v>
       </c>
       <c r="K49" t="n">
-        <v>-237.61</v>
+        <v>-153.68</v>
       </c>
       <c r="L49" t="n">
-        <v>244.17</v>
+        <v>157.93</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>294.17</v>
+        <v>149.21</v>
       </c>
       <c r="K50" t="n">
-        <v>115.35</v>
+        <v>58.51</v>
       </c>
       <c r="L50" t="n">
-        <v>315.97</v>
+        <v>160.27</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>680.39</v>
+        <v>375.94</v>
       </c>
       <c r="K51" t="n">
-        <v>226.93</v>
+        <v>125.39</v>
       </c>
       <c r="L51" t="n">
-        <v>717.24</v>
+        <v>396.3</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-217.36</v>
+        <v>-108.46</v>
       </c>
       <c r="K52" t="n">
-        <v>-714.54</v>
+        <v>-356.55</v>
       </c>
       <c r="L52" t="n">
-        <v>746.86</v>
+        <v>372.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-1150.32</v>
+        <v>-522.6799999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>240.19</v>
+        <v>109.14</v>
       </c>
       <c r="L53" t="n">
-        <v>1175.12</v>
+        <v>533.95</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>887.72</v>
+        <v>384.29</v>
       </c>
       <c r="K54" t="n">
-        <v>994.48</v>
+        <v>430.5</v>
       </c>
       <c r="L54" t="n">
-        <v>1333.05</v>
+        <v>577.0700000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-649.2</v>
+        <v>-285.89</v>
       </c>
       <c r="K55" t="n">
-        <v>-247.83</v>
+        <v>-109.14</v>
       </c>
       <c r="L55" t="n">
-        <v>694.9</v>
+        <v>306.01</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>955.16</v>
+        <v>414.41</v>
       </c>
       <c r="K56" t="n">
-        <v>-54.31</v>
+        <v>-23.56</v>
       </c>
       <c r="L56" t="n">
-        <v>956.7</v>
+        <v>415.08</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>751.96</v>
+        <v>312.66</v>
       </c>
       <c r="K57" t="n">
-        <v>477.51</v>
+        <v>198.55</v>
       </c>
       <c r="L57" t="n">
-        <v>890.76</v>
+        <v>370.38</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>970.79</v>
+        <v>392.1</v>
       </c>
       <c r="K58" t="n">
-        <v>-363.27</v>
+        <v>-146.72</v>
       </c>
       <c r="L58" t="n">
-        <v>1036.53</v>
+        <v>418.65</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-192.4</v>
+        <v>-118.34</v>
       </c>
       <c r="K59" t="n">
-        <v>285.9</v>
+        <v>175.85</v>
       </c>
       <c r="L59" t="n">
-        <v>344.61</v>
+        <v>211.96</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-245.19</v>
+        <v>-157.87</v>
       </c>
       <c r="K60" t="n">
-        <v>-183.99</v>
+        <v>-118.46</v>
       </c>
       <c r="L60" t="n">
-        <v>306.55</v>
+        <v>197.37</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>114.82</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>219.42</v>
+        <v>131.73</v>
       </c>
       <c r="L61" t="n">
-        <v>247.65</v>
+        <v>148.67</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-347.43</v>
+        <v>-204.82</v>
       </c>
       <c r="K62" t="n">
-        <v>102.01</v>
+        <v>60.14</v>
       </c>
       <c r="L62" t="n">
-        <v>362.09</v>
+        <v>213.46</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>280.84</v>
+        <v>161.29</v>
       </c>
       <c r="K63" t="n">
-        <v>-188.28</v>
+        <v>-108.13</v>
       </c>
       <c r="L63" t="n">
-        <v>338.11</v>
+        <v>194.18</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-326.74</v>
+        <v>-187.85</v>
       </c>
       <c r="K64" t="n">
-        <v>270.75</v>
+        <v>155.66</v>
       </c>
       <c r="L64" t="n">
-        <v>424.34</v>
+        <v>243.96</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>718.1</v>
+        <v>380.78</v>
       </c>
       <c r="K65" t="n">
-        <v>51.23</v>
+        <v>27.16</v>
       </c>
       <c r="L65" t="n">
-        <v>719.92</v>
+        <v>381.75</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>63.83</v>
+        <v>35.62</v>
       </c>
       <c r="K66" t="n">
-        <v>517.64</v>
+        <v>288.83</v>
       </c>
       <c r="L66" t="n">
-        <v>521.5599999999999</v>
+        <v>291.02</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-597.95</v>
+        <v>-329.46</v>
       </c>
       <c r="K67" t="n">
-        <v>239.3</v>
+        <v>131.85</v>
       </c>
       <c r="L67" t="n">
-        <v>644.0599999999999</v>
+        <v>354.86</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-808.78</v>
+        <v>-355.86</v>
       </c>
       <c r="K68" t="n">
-        <v>-145.14</v>
+        <v>-63.86</v>
       </c>
       <c r="L68" t="n">
-        <v>821.7</v>
+        <v>361.55</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-943.36</v>
+        <v>-436.84</v>
       </c>
       <c r="K69" t="n">
-        <v>76.92</v>
+        <v>35.62</v>
       </c>
       <c r="L69" t="n">
-        <v>946.49</v>
+        <v>438.29</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>496.95</v>
+        <v>226.23</v>
       </c>
       <c r="K70" t="n">
-        <v>330.64</v>
+        <v>150.52</v>
       </c>
       <c r="L70" t="n">
-        <v>596.89</v>
+        <v>271.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-1672.28</v>
+        <v>-654.75</v>
       </c>
       <c r="K71" t="n">
-        <v>110.11</v>
+        <v>43.11</v>
       </c>
       <c r="L71" t="n">
-        <v>1675.91</v>
+        <v>656.16</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-1405.93</v>
+        <v>-635.36</v>
       </c>
       <c r="K72" t="n">
-        <v>566.47</v>
+        <v>256</v>
       </c>
       <c r="L72" t="n">
-        <v>1515.76</v>
+        <v>685</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>797.61</v>
+        <v>371.28</v>
       </c>
       <c r="K73" t="n">
-        <v>-62.47</v>
+        <v>-29.08</v>
       </c>
       <c r="L73" t="n">
-        <v>800.05</v>
+        <v>372.42</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-266.74</v>
+        <v>-162.05</v>
       </c>
       <c r="K74" t="n">
-        <v>-79.52</v>
+        <v>-48.31</v>
       </c>
       <c r="L74" t="n">
-        <v>278.34</v>
+        <v>169.1</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>29.68</v>
+        <v>21.17</v>
       </c>
       <c r="K75" t="n">
-        <v>129.29</v>
+        <v>92.22</v>
       </c>
       <c r="L75" t="n">
-        <v>132.65</v>
+        <v>94.62</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>82.02</v>
+        <v>48.7</v>
       </c>
       <c r="K76" t="n">
-        <v>-178.58</v>
+        <v>-106.04</v>
       </c>
       <c r="L76" t="n">
-        <v>196.51</v>
+        <v>116.69</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>367.27</v>
+        <v>237</v>
       </c>
       <c r="K77" t="n">
-        <v>-183.27</v>
+        <v>-118.26</v>
       </c>
       <c r="L77" t="n">
-        <v>410.45</v>
+        <v>264.87</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-127.35</v>
+        <v>-77.95</v>
       </c>
       <c r="K78" t="n">
-        <v>570.8</v>
+        <v>349.38</v>
       </c>
       <c r="L78" t="n">
-        <v>584.83</v>
+        <v>357.97</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-45.04</v>
+        <v>-25.65</v>
       </c>
       <c r="K79" t="n">
-        <v>-290.56</v>
+        <v>-165.43</v>
       </c>
       <c r="L79" t="n">
-        <v>294.03</v>
+        <v>167.41</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-584.61</v>
+        <v>-301.47</v>
       </c>
       <c r="K80" t="n">
-        <v>78.11</v>
+        <v>40.28</v>
       </c>
       <c r="L80" t="n">
-        <v>589.8</v>
+        <v>304.15</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-547.5700000000001</v>
+        <v>-296.53</v>
       </c>
       <c r="K81" t="n">
-        <v>401.17</v>
+        <v>217.24</v>
       </c>
       <c r="L81" t="n">
-        <v>678.8</v>
+        <v>367.59</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-106.43</v>
+        <v>-56.02</v>
       </c>
       <c r="K82" t="n">
-        <v>1049.72</v>
+        <v>552.58</v>
       </c>
       <c r="L82" t="n">
-        <v>1055.1</v>
+        <v>555.41</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-472.04</v>
+        <v>-230.15</v>
       </c>
       <c r="K83" t="n">
-        <v>340.47</v>
+        <v>166</v>
       </c>
       <c r="L83" t="n">
-        <v>582.02</v>
+        <v>283.77</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-808.92</v>
+        <v>-369.72</v>
       </c>
       <c r="K84" t="n">
-        <v>-650.11</v>
+        <v>-297.14</v>
       </c>
       <c r="L84" t="n">
-        <v>1037.78</v>
+        <v>474.32</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-147.57</v>
+        <v>-65.95</v>
       </c>
       <c r="K85" t="n">
-        <v>730.46</v>
+        <v>326.44</v>
       </c>
       <c r="L85" t="n">
-        <v>745.22</v>
+        <v>333.04</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-353.1</v>
+        <v>-152.17</v>
       </c>
       <c r="K86" t="n">
-        <v>317.57</v>
+        <v>136.85</v>
       </c>
       <c r="L86" t="n">
-        <v>474.9</v>
+        <v>204.66</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-767.48</v>
+        <v>-328.87</v>
       </c>
       <c r="K87" t="n">
-        <v>169.42</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>785.96</v>
+        <v>336.79</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>733.75</v>
+        <v>303.46</v>
       </c>
       <c r="K88" t="n">
-        <v>943.59</v>
+        <v>390.24</v>
       </c>
       <c r="L88" t="n">
-        <v>1195.31</v>
+        <v>494.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.52</v>
+        <v>-8.15</v>
       </c>
       <c r="K14" t="n">
-        <v>-215.58</v>
+        <v>-233.58</v>
       </c>
       <c r="L14" t="n">
-        <v>215.71</v>
+        <v>233.72</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>32.92</v>
+        <v>35.57</v>
       </c>
       <c r="K15" t="n">
-        <v>-136.24</v>
+        <v>-147.18</v>
       </c>
       <c r="L15" t="n">
-        <v>140.16</v>
+        <v>151.41</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>118.62</v>
+        <v>126.49</v>
       </c>
       <c r="K16" t="n">
-        <v>123.32</v>
+        <v>131.51</v>
       </c>
       <c r="L16" t="n">
-        <v>171.11</v>
+        <v>182.47</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>-146.49</v>
+        <v>-162.66</v>
       </c>
       <c r="L17" t="n">
-        <v>146.49</v>
+        <v>162.66</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>72.65000000000001</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-96.22</v>
+        <v>-104.02</v>
       </c>
       <c r="L18" t="n">
-        <v>120.57</v>
+        <v>130.34</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>28.23</v>
+        <v>31.4</v>
       </c>
       <c r="K19" t="n">
-        <v>167.93</v>
+        <v>186.81</v>
       </c>
       <c r="L19" t="n">
-        <v>170.29</v>
+        <v>189.43</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-408.63</v>
+        <v>-466.93</v>
       </c>
       <c r="K20" t="n">
-        <v>38.24</v>
+        <v>43.7</v>
       </c>
       <c r="L20" t="n">
-        <v>410.41</v>
+        <v>468.97</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>26.69</v>
+        <v>30.09</v>
       </c>
       <c r="K21" t="n">
-        <v>-195.29</v>
+        <v>-220.24</v>
       </c>
       <c r="L21" t="n">
-        <v>197.11</v>
+        <v>222.28</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>142.58</v>
+        <v>161.64</v>
       </c>
       <c r="K22" t="n">
-        <v>250.94</v>
+        <v>284.48</v>
       </c>
       <c r="L22" t="n">
-        <v>288.62</v>
+        <v>327.19</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-235.42</v>
+        <v>-276.75</v>
       </c>
       <c r="K23" t="n">
-        <v>-497.58</v>
+        <v>-584.95</v>
       </c>
       <c r="L23" t="n">
-        <v>550.47</v>
+        <v>647.12</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-368.03</v>
+        <v>-432.88</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.18</v>
+        <v>-1.38</v>
       </c>
       <c r="L24" t="n">
-        <v>368.03</v>
+        <v>432.88</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>230.83</v>
+        <v>273.31</v>
       </c>
       <c r="K25" t="n">
-        <v>19.48</v>
+        <v>23.06</v>
       </c>
       <c r="L25" t="n">
-        <v>231.65</v>
+        <v>274.28</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-355.16</v>
+        <v>-422.2</v>
       </c>
       <c r="K26" t="n">
-        <v>-138.22</v>
+        <v>-164.32</v>
       </c>
       <c r="L26" t="n">
-        <v>381.11</v>
+        <v>453.05</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-114.41</v>
+        <v>-138.85</v>
       </c>
       <c r="K27" t="n">
-        <v>781.48</v>
+        <v>948.4400000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>789.8099999999999</v>
+        <v>958.55</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-82.95</v>
+        <v>-101.51</v>
       </c>
       <c r="K28" t="n">
-        <v>-399.52</v>
+        <v>-488.92</v>
       </c>
       <c r="L28" t="n">
-        <v>408.04</v>
+        <v>499.34</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>126.92</v>
+        <v>135.4</v>
       </c>
       <c r="K29" t="n">
-        <v>9.140000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="L29" t="n">
-        <v>127.25</v>
+        <v>135.75</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>50.32</v>
+        <v>54.63</v>
       </c>
       <c r="K30" t="n">
-        <v>268.46</v>
+        <v>291.44</v>
       </c>
       <c r="L30" t="n">
-        <v>273.14</v>
+        <v>296.51</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>123.48</v>
+        <v>131.02</v>
       </c>
       <c r="K31" t="n">
-        <v>106.65</v>
+        <v>113.17</v>
       </c>
       <c r="L31" t="n">
-        <v>163.16</v>
+        <v>173.13</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-35.27</v>
+        <v>-38.26</v>
       </c>
       <c r="K32" t="n">
-        <v>-282.79</v>
+        <v>-306.76</v>
       </c>
       <c r="L32" t="n">
-        <v>284.98</v>
+        <v>309.14</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>157.81</v>
+        <v>174.5</v>
       </c>
       <c r="K33" t="n">
-        <v>66.26000000000001</v>
+        <v>73.27</v>
       </c>
       <c r="L33" t="n">
-        <v>171.16</v>
+        <v>189.26</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-133.11</v>
+        <v>-145.37</v>
       </c>
       <c r="K34" t="n">
-        <v>37.71</v>
+        <v>41.18</v>
       </c>
       <c r="L34" t="n">
-        <v>138.35</v>
+        <v>151.09</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>156.22</v>
+        <v>180.31</v>
       </c>
       <c r="K35" t="n">
-        <v>30.4</v>
+        <v>35.09</v>
       </c>
       <c r="L35" t="n">
-        <v>159.15</v>
+        <v>183.69</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>35</v>
+        <v>40.23</v>
       </c>
       <c r="K36" t="n">
-        <v>-329.61</v>
+        <v>-378.88</v>
       </c>
       <c r="L36" t="n">
-        <v>331.46</v>
+        <v>381.01</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-165.83</v>
+        <v>-187</v>
       </c>
       <c r="K37" t="n">
-        <v>-183.58</v>
+        <v>-207.02</v>
       </c>
       <c r="L37" t="n">
-        <v>247.39</v>
+        <v>278.97</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-31.32</v>
+        <v>-36.59</v>
       </c>
       <c r="K38" t="n">
-        <v>196.85</v>
+        <v>230.01</v>
       </c>
       <c r="L38" t="n">
-        <v>199.33</v>
+        <v>232.9</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-308.14</v>
+        <v>-357.5</v>
       </c>
       <c r="K39" t="n">
-        <v>4.91</v>
+        <v>5.7</v>
       </c>
       <c r="L39" t="n">
-        <v>308.18</v>
+        <v>357.55</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-372.67</v>
+        <v>-435.76</v>
       </c>
       <c r="K40" t="n">
-        <v>250.91</v>
+        <v>293.38</v>
       </c>
       <c r="L40" t="n">
-        <v>449.26</v>
+        <v>525.3200000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-390.25</v>
+        <v>-470.46</v>
       </c>
       <c r="K41" t="n">
-        <v>-374.12</v>
+        <v>-451.01</v>
       </c>
       <c r="L41" t="n">
-        <v>540.61</v>
+        <v>651.73</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>334.11</v>
+        <v>400.08</v>
       </c>
       <c r="K42" t="n">
-        <v>203.14</v>
+        <v>243.25</v>
       </c>
       <c r="L42" t="n">
-        <v>391.01</v>
+        <v>468.22</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>402.56</v>
+        <v>480.51</v>
       </c>
       <c r="K43" t="n">
-        <v>63.07</v>
+        <v>75.28</v>
       </c>
       <c r="L43" t="n">
-        <v>407.47</v>
+        <v>486.37</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-159.38</v>
+        <v>-170.83</v>
       </c>
       <c r="K44" t="n">
-        <v>-87.98999999999999</v>
+        <v>-94.31</v>
       </c>
       <c r="L44" t="n">
-        <v>182.06</v>
+        <v>195.13</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-75.81</v>
+        <v>-83.18000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>111.35</v>
+        <v>122.17</v>
       </c>
       <c r="L45" t="n">
-        <v>134.71</v>
+        <v>147.79</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>185.57</v>
+        <v>203.72</v>
       </c>
       <c r="K46" t="n">
-        <v>-147.26</v>
+        <v>-161.67</v>
       </c>
       <c r="L46" t="n">
-        <v>236.9</v>
+        <v>260.08</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-182.4</v>
+        <v>-201.72</v>
       </c>
       <c r="K47" t="n">
-        <v>120.58</v>
+        <v>133.35</v>
       </c>
       <c r="L47" t="n">
-        <v>218.65</v>
+        <v>241.81</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-208.32</v>
+        <v>-229.48</v>
       </c>
       <c r="K48" t="n">
-        <v>42.65</v>
+        <v>46.98</v>
       </c>
       <c r="L48" t="n">
-        <v>212.64</v>
+        <v>234.24</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-36.38</v>
+        <v>-39.48</v>
       </c>
       <c r="K49" t="n">
-        <v>-153.68</v>
+        <v>-166.78</v>
       </c>
       <c r="L49" t="n">
-        <v>157.93</v>
+        <v>171.39</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>149.21</v>
+        <v>172.43</v>
       </c>
       <c r="K50" t="n">
-        <v>58.51</v>
+        <v>67.61</v>
       </c>
       <c r="L50" t="n">
-        <v>160.27</v>
+        <v>185.21</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>375.94</v>
+        <v>424.38</v>
       </c>
       <c r="K51" t="n">
-        <v>125.39</v>
+        <v>141.54</v>
       </c>
       <c r="L51" t="n">
-        <v>396.3</v>
+        <v>447.36</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-108.46</v>
+        <v>-126.25</v>
       </c>
       <c r="K52" t="n">
-        <v>-356.55</v>
+        <v>-415.03</v>
       </c>
       <c r="L52" t="n">
-        <v>372.69</v>
+        <v>433.81</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-522.6799999999999</v>
+        <v>-618.62</v>
       </c>
       <c r="K53" t="n">
-        <v>109.14</v>
+        <v>129.17</v>
       </c>
       <c r="L53" t="n">
-        <v>533.95</v>
+        <v>631.96</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>384.29</v>
+        <v>448.36</v>
       </c>
       <c r="K54" t="n">
-        <v>430.5</v>
+        <v>502.28</v>
       </c>
       <c r="L54" t="n">
-        <v>577.0700000000001</v>
+        <v>673.28</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-285.89</v>
+        <v>-339.39</v>
       </c>
       <c r="K55" t="n">
-        <v>-109.14</v>
+        <v>-129.56</v>
       </c>
       <c r="L55" t="n">
-        <v>306.01</v>
+        <v>363.28</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>414.41</v>
+        <v>492.29</v>
       </c>
       <c r="K56" t="n">
-        <v>-23.56</v>
+        <v>-27.99</v>
       </c>
       <c r="L56" t="n">
-        <v>415.08</v>
+        <v>493.09</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>312.66</v>
+        <v>376.22</v>
       </c>
       <c r="K57" t="n">
-        <v>198.55</v>
+        <v>238.9</v>
       </c>
       <c r="L57" t="n">
-        <v>370.38</v>
+        <v>445.66</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>392.1</v>
+        <v>477.84</v>
       </c>
       <c r="K58" t="n">
-        <v>-146.72</v>
+        <v>-178.8</v>
       </c>
       <c r="L58" t="n">
-        <v>418.65</v>
+        <v>510.19</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-118.34</v>
+        <v>-128.6</v>
       </c>
       <c r="K59" t="n">
-        <v>175.85</v>
+        <v>191.1</v>
       </c>
       <c r="L59" t="n">
-        <v>211.96</v>
+        <v>230.34</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-157.87</v>
+        <v>-170.59</v>
       </c>
       <c r="K60" t="n">
-        <v>-118.46</v>
+        <v>-128.01</v>
       </c>
       <c r="L60" t="n">
-        <v>197.37</v>
+        <v>213.27</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>68.93000000000001</v>
+        <v>75.56</v>
       </c>
       <c r="K61" t="n">
-        <v>131.73</v>
+        <v>144.4</v>
       </c>
       <c r="L61" t="n">
-        <v>148.67</v>
+        <v>162.97</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-204.82</v>
+        <v>-225.52</v>
       </c>
       <c r="K62" t="n">
-        <v>60.14</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>213.46</v>
+        <v>235.04</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>161.29</v>
+        <v>177.51</v>
       </c>
       <c r="K63" t="n">
-        <v>-108.13</v>
+        <v>-119.01</v>
       </c>
       <c r="L63" t="n">
-        <v>194.18</v>
+        <v>213.71</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-187.85</v>
+        <v>-208.69</v>
       </c>
       <c r="K64" t="n">
-        <v>155.66</v>
+        <v>172.93</v>
       </c>
       <c r="L64" t="n">
-        <v>243.96</v>
+        <v>271.03</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>380.78</v>
+        <v>433.88</v>
       </c>
       <c r="K65" t="n">
-        <v>27.16</v>
+        <v>30.95</v>
       </c>
       <c r="L65" t="n">
-        <v>381.75</v>
+        <v>434.98</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>35.62</v>
+        <v>40.36</v>
       </c>
       <c r="K66" t="n">
-        <v>288.83</v>
+        <v>327.32</v>
       </c>
       <c r="L66" t="n">
-        <v>291.02</v>
+        <v>329.8</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-329.46</v>
+        <v>-376.27</v>
       </c>
       <c r="K67" t="n">
-        <v>131.85</v>
+        <v>150.58</v>
       </c>
       <c r="L67" t="n">
-        <v>354.86</v>
+        <v>405.28</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-355.86</v>
+        <v>-423.05</v>
       </c>
       <c r="K68" t="n">
-        <v>-63.86</v>
+        <v>-75.92</v>
       </c>
       <c r="L68" t="n">
-        <v>361.55</v>
+        <v>429.81</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-436.84</v>
+        <v>-516.78</v>
       </c>
       <c r="K69" t="n">
-        <v>35.62</v>
+        <v>42.14</v>
       </c>
       <c r="L69" t="n">
-        <v>438.29</v>
+        <v>518.49</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>226.23</v>
+        <v>266.5</v>
       </c>
       <c r="K70" t="n">
-        <v>150.52</v>
+        <v>177.31</v>
       </c>
       <c r="L70" t="n">
-        <v>271.73</v>
+        <v>320.1</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-654.75</v>
+        <v>-782.95</v>
       </c>
       <c r="K71" t="n">
-        <v>43.11</v>
+        <v>51.55</v>
       </c>
       <c r="L71" t="n">
-        <v>656.16</v>
+        <v>784.64</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-635.36</v>
+        <v>-763.71</v>
       </c>
       <c r="K72" t="n">
-        <v>256</v>
+        <v>307.71</v>
       </c>
       <c r="L72" t="n">
-        <v>685</v>
+        <v>823.37</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>371.28</v>
+        <v>438.25</v>
       </c>
       <c r="K73" t="n">
-        <v>-29.08</v>
+        <v>-34.33</v>
       </c>
       <c r="L73" t="n">
-        <v>372.42</v>
+        <v>439.59</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-162.05</v>
+        <v>-179.44</v>
       </c>
       <c r="K74" t="n">
-        <v>-48.31</v>
+        <v>-53.5</v>
       </c>
       <c r="L74" t="n">
-        <v>169.1</v>
+        <v>187.24</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>21.17</v>
+        <v>22.49</v>
       </c>
       <c r="K75" t="n">
-        <v>92.22</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>94.62</v>
+        <v>100.51</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>48.7</v>
+        <v>53.39</v>
       </c>
       <c r="K76" t="n">
-        <v>-106.04</v>
+        <v>-116.25</v>
       </c>
       <c r="L76" t="n">
-        <v>116.69</v>
+        <v>127.93</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>237</v>
+        <v>255.21</v>
       </c>
       <c r="K77" t="n">
-        <v>-118.26</v>
+        <v>-127.35</v>
       </c>
       <c r="L77" t="n">
-        <v>264.87</v>
+        <v>285.22</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-77.95</v>
+        <v>-85.41</v>
       </c>
       <c r="K78" t="n">
-        <v>349.38</v>
+        <v>382.82</v>
       </c>
       <c r="L78" t="n">
-        <v>357.97</v>
+        <v>392.23</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-25.65</v>
+        <v>-28.48</v>
       </c>
       <c r="K79" t="n">
-        <v>-165.43</v>
+        <v>-183.72</v>
       </c>
       <c r="L79" t="n">
-        <v>167.41</v>
+        <v>185.92</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-301.47</v>
+        <v>-345.9</v>
       </c>
       <c r="K80" t="n">
-        <v>40.28</v>
+        <v>46.21</v>
       </c>
       <c r="L80" t="n">
-        <v>304.15</v>
+        <v>348.97</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-296.53</v>
+        <v>-337.63</v>
       </c>
       <c r="K81" t="n">
-        <v>217.24</v>
+        <v>247.36</v>
       </c>
       <c r="L81" t="n">
-        <v>367.59</v>
+        <v>418.54</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-56.02</v>
+        <v>-63.48</v>
       </c>
       <c r="K82" t="n">
-        <v>552.58</v>
+        <v>626.13</v>
       </c>
       <c r="L82" t="n">
-        <v>555.41</v>
+        <v>629.34</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-230.15</v>
+        <v>-265.11</v>
       </c>
       <c r="K83" t="n">
-        <v>166</v>
+        <v>191.22</v>
       </c>
       <c r="L83" t="n">
-        <v>283.77</v>
+        <v>326.88</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-369.72</v>
+        <v>-432.98</v>
       </c>
       <c r="K84" t="n">
-        <v>-297.14</v>
+        <v>-347.97</v>
       </c>
       <c r="L84" t="n">
-        <v>474.32</v>
+        <v>555.48</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-65.95</v>
+        <v>-78.31999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>326.44</v>
+        <v>387.68</v>
       </c>
       <c r="L85" t="n">
-        <v>333.04</v>
+        <v>395.52</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-152.17</v>
+        <v>-184.03</v>
       </c>
       <c r="K86" t="n">
-        <v>136.85</v>
+        <v>165.51</v>
       </c>
       <c r="L86" t="n">
-        <v>204.66</v>
+        <v>247.51</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-328.87</v>
+        <v>-401.81</v>
       </c>
       <c r="K87" t="n">
-        <v>72.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="L87" t="n">
-        <v>336.79</v>
+        <v>411.49</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>303.46</v>
+        <v>365.49</v>
       </c>
       <c r="K88" t="n">
-        <v>390.24</v>
+        <v>470.01</v>
       </c>
       <c r="L88" t="n">
-        <v>494.34</v>
+        <v>595.39</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.15</v>
+        <v>-3.43</v>
       </c>
       <c r="K14" t="n">
-        <v>-233.58</v>
+        <v>-98.45</v>
       </c>
       <c r="L14" t="n">
-        <v>233.72</v>
+        <v>98.51000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>35.57</v>
+        <v>16.8</v>
       </c>
       <c r="K15" t="n">
-        <v>-147.18</v>
+        <v>-69.5</v>
       </c>
       <c r="L15" t="n">
-        <v>151.41</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>126.49</v>
+        <v>61.09</v>
       </c>
       <c r="K16" t="n">
-        <v>131.51</v>
+        <v>63.51</v>
       </c>
       <c r="L16" t="n">
-        <v>182.47</v>
+        <v>88.13</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>0.51</v>
       </c>
       <c r="K17" t="n">
-        <v>-162.66</v>
+        <v>-81.54000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>162.66</v>
+        <v>81.55</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>78.54000000000001</v>
+        <v>34.83</v>
       </c>
       <c r="K18" t="n">
-        <v>-104.02</v>
+        <v>-46.13</v>
       </c>
       <c r="L18" t="n">
-        <v>130.34</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>31.4</v>
+        <v>13.41</v>
       </c>
       <c r="K19" t="n">
-        <v>186.81</v>
+        <v>79.81</v>
       </c>
       <c r="L19" t="n">
-        <v>189.43</v>
+        <v>80.93000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-466.93</v>
+        <v>-224.1</v>
       </c>
       <c r="K20" t="n">
-        <v>43.7</v>
+        <v>20.97</v>
       </c>
       <c r="L20" t="n">
-        <v>468.97</v>
+        <v>225.08</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>30.09</v>
+        <v>14.61</v>
       </c>
       <c r="K21" t="n">
-        <v>-220.24</v>
+        <v>-106.93</v>
       </c>
       <c r="L21" t="n">
-        <v>222.28</v>
+        <v>107.92</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>161.64</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>284.48</v>
+        <v>146.69</v>
       </c>
       <c r="L22" t="n">
-        <v>327.19</v>
+        <v>168.71</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-276.75</v>
+        <v>-126.1</v>
       </c>
       <c r="K23" t="n">
-        <v>-584.95</v>
+        <v>-266.52</v>
       </c>
       <c r="L23" t="n">
-        <v>647.12</v>
+        <v>294.84</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-432.88</v>
+        <v>-196.91</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.38</v>
+        <v>-0.63</v>
       </c>
       <c r="L24" t="n">
-        <v>432.88</v>
+        <v>196.91</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>273.31</v>
+        <v>129.29</v>
       </c>
       <c r="K25" t="n">
-        <v>23.06</v>
+        <v>10.91</v>
       </c>
       <c r="L25" t="n">
-        <v>274.28</v>
+        <v>129.75</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-422.2</v>
+        <v>-226.61</v>
       </c>
       <c r="K26" t="n">
-        <v>-164.32</v>
+        <v>-88.19</v>
       </c>
       <c r="L26" t="n">
-        <v>453.05</v>
+        <v>243.17</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-138.85</v>
+        <v>-74.59</v>
       </c>
       <c r="K27" t="n">
-        <v>948.4400000000001</v>
+        <v>509.5</v>
       </c>
       <c r="L27" t="n">
-        <v>958.55</v>
+        <v>514.9299999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-101.51</v>
+        <v>-54.14</v>
       </c>
       <c r="K28" t="n">
-        <v>-488.92</v>
+        <v>-260.78</v>
       </c>
       <c r="L28" t="n">
-        <v>499.34</v>
+        <v>266.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>135.4</v>
+        <v>64.22</v>
       </c>
       <c r="K29" t="n">
-        <v>9.75</v>
+        <v>4.62</v>
       </c>
       <c r="L29" t="n">
-        <v>135.75</v>
+        <v>64.39</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>54.63</v>
+        <v>21.85</v>
       </c>
       <c r="K30" t="n">
-        <v>291.44</v>
+        <v>116.55</v>
       </c>
       <c r="L30" t="n">
-        <v>296.51</v>
+        <v>118.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>131.02</v>
+        <v>72.05</v>
       </c>
       <c r="K31" t="n">
-        <v>113.17</v>
+        <v>62.23</v>
       </c>
       <c r="L31" t="n">
-        <v>173.13</v>
+        <v>95.20999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-38.26</v>
+        <v>-17.38</v>
       </c>
       <c r="K32" t="n">
-        <v>-306.76</v>
+        <v>-139.34</v>
       </c>
       <c r="L32" t="n">
-        <v>309.14</v>
+        <v>140.42</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>174.5</v>
+        <v>75.2</v>
       </c>
       <c r="K33" t="n">
-        <v>73.27</v>
+        <v>31.58</v>
       </c>
       <c r="L33" t="n">
-        <v>189.26</v>
+        <v>81.56</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-145.37</v>
+        <v>-60.33</v>
       </c>
       <c r="K34" t="n">
-        <v>41.18</v>
+        <v>17.09</v>
       </c>
       <c r="L34" t="n">
-        <v>151.09</v>
+        <v>62.71</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>180.31</v>
+        <v>89.81</v>
       </c>
       <c r="K35" t="n">
-        <v>35.09</v>
+        <v>17.48</v>
       </c>
       <c r="L35" t="n">
-        <v>183.69</v>
+        <v>91.48999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>40.23</v>
+        <v>19.32</v>
       </c>
       <c r="K36" t="n">
-        <v>-378.88</v>
+        <v>-181.99</v>
       </c>
       <c r="L36" t="n">
-        <v>381.01</v>
+        <v>183.02</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-187</v>
+        <v>-92.08</v>
       </c>
       <c r="K37" t="n">
-        <v>-207.02</v>
+        <v>-101.94</v>
       </c>
       <c r="L37" t="n">
-        <v>278.97</v>
+        <v>137.37</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-36.59</v>
+        <v>-17.85</v>
       </c>
       <c r="K38" t="n">
-        <v>230.01</v>
+        <v>112.18</v>
       </c>
       <c r="L38" t="n">
-        <v>232.9</v>
+        <v>113.59</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-357.5</v>
+        <v>-182.16</v>
       </c>
       <c r="K39" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="L39" t="n">
-        <v>357.55</v>
+        <v>182.18</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-435.76</v>
+        <v>-189.68</v>
       </c>
       <c r="K40" t="n">
-        <v>293.38</v>
+        <v>127.71</v>
       </c>
       <c r="L40" t="n">
-        <v>525.3200000000001</v>
+        <v>228.67</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-470.46</v>
+        <v>-253.28</v>
       </c>
       <c r="K41" t="n">
-        <v>-451.01</v>
+        <v>-242.81</v>
       </c>
       <c r="L41" t="n">
-        <v>651.73</v>
+        <v>350.86</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>400.08</v>
+        <v>215.95</v>
       </c>
       <c r="K42" t="n">
-        <v>243.25</v>
+        <v>131.3</v>
       </c>
       <c r="L42" t="n">
-        <v>468.22</v>
+        <v>252.73</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>480.51</v>
+        <v>263.79</v>
       </c>
       <c r="K43" t="n">
-        <v>75.28</v>
+        <v>41.33</v>
       </c>
       <c r="L43" t="n">
-        <v>486.37</v>
+        <v>267</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-170.83</v>
+        <v>-75.77</v>
       </c>
       <c r="K44" t="n">
-        <v>-94.31</v>
+        <v>-41.83</v>
       </c>
       <c r="L44" t="n">
-        <v>195.13</v>
+        <v>86.55</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-83.18000000000001</v>
+        <v>-35.91</v>
       </c>
       <c r="K45" t="n">
-        <v>122.17</v>
+        <v>52.74</v>
       </c>
       <c r="L45" t="n">
-        <v>147.79</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>203.72</v>
+        <v>87.45</v>
       </c>
       <c r="K46" t="n">
-        <v>-161.67</v>
+        <v>-69.40000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>260.08</v>
+        <v>111.64</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-201.72</v>
+        <v>-85.28</v>
       </c>
       <c r="K47" t="n">
-        <v>133.35</v>
+        <v>56.37</v>
       </c>
       <c r="L47" t="n">
-        <v>241.81</v>
+        <v>102.23</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-229.48</v>
+        <v>-106.73</v>
       </c>
       <c r="K48" t="n">
-        <v>46.98</v>
+        <v>21.85</v>
       </c>
       <c r="L48" t="n">
-        <v>234.24</v>
+        <v>108.94</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-39.48</v>
+        <v>-16.84</v>
       </c>
       <c r="K49" t="n">
-        <v>-166.78</v>
+        <v>-71.15000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>171.39</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>172.43</v>
+        <v>84.78</v>
       </c>
       <c r="K50" t="n">
-        <v>67.61</v>
+        <v>33.24</v>
       </c>
       <c r="L50" t="n">
-        <v>185.21</v>
+        <v>91.06999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>424.38</v>
+        <v>205.14</v>
       </c>
       <c r="K51" t="n">
-        <v>141.54</v>
+        <v>68.42</v>
       </c>
       <c r="L51" t="n">
-        <v>447.36</v>
+        <v>216.25</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-126.25</v>
+        <v>-60.82</v>
       </c>
       <c r="K52" t="n">
-        <v>-415.03</v>
+        <v>-199.93</v>
       </c>
       <c r="L52" t="n">
-        <v>433.81</v>
+        <v>208.98</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-618.62</v>
+        <v>-290.1</v>
       </c>
       <c r="K53" t="n">
-        <v>129.17</v>
+        <v>60.57</v>
       </c>
       <c r="L53" t="n">
-        <v>631.96</v>
+        <v>296.36</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>448.36</v>
+        <v>212.31</v>
       </c>
       <c r="K54" t="n">
-        <v>502.28</v>
+        <v>237.84</v>
       </c>
       <c r="L54" t="n">
-        <v>673.28</v>
+        <v>318.81</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-339.39</v>
+        <v>-150.91</v>
       </c>
       <c r="K55" t="n">
-        <v>-129.56</v>
+        <v>-57.61</v>
       </c>
       <c r="L55" t="n">
-        <v>363.28</v>
+        <v>161.53</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>492.29</v>
+        <v>267.79</v>
       </c>
       <c r="K56" t="n">
-        <v>-27.99</v>
+        <v>-15.23</v>
       </c>
       <c r="L56" t="n">
-        <v>493.09</v>
+        <v>268.23</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>376.22</v>
+        <v>205.92</v>
       </c>
       <c r="K57" t="n">
-        <v>238.9</v>
+        <v>130.76</v>
       </c>
       <c r="L57" t="n">
-        <v>445.66</v>
+        <v>243.94</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>477.84</v>
+        <v>253.65</v>
       </c>
       <c r="K58" t="n">
-        <v>-178.8</v>
+        <v>-94.92</v>
       </c>
       <c r="L58" t="n">
-        <v>510.19</v>
+        <v>270.83</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-128.6</v>
+        <v>-60.33</v>
       </c>
       <c r="K59" t="n">
-        <v>191.1</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>230.34</v>
+        <v>108.06</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-170.59</v>
+        <v>-71.26000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-128.01</v>
+        <v>-53.47</v>
       </c>
       <c r="L60" t="n">
-        <v>213.27</v>
+        <v>89.09</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>75.56</v>
+        <v>31.9</v>
       </c>
       <c r="K61" t="n">
-        <v>144.4</v>
+        <v>60.97</v>
       </c>
       <c r="L61" t="n">
-        <v>162.97</v>
+        <v>68.81</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-225.52</v>
+        <v>-95.19</v>
       </c>
       <c r="K62" t="n">
-        <v>66.20999999999999</v>
+        <v>27.95</v>
       </c>
       <c r="L62" t="n">
-        <v>235.04</v>
+        <v>99.20999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>177.51</v>
+        <v>75.16</v>
       </c>
       <c r="K63" t="n">
-        <v>-119.01</v>
+        <v>-50.39</v>
       </c>
       <c r="L63" t="n">
-        <v>213.71</v>
+        <v>90.48999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-208.69</v>
+        <v>-93.28</v>
       </c>
       <c r="K64" t="n">
-        <v>172.93</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>271.03</v>
+        <v>121.14</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>433.88</v>
+        <v>207.16</v>
       </c>
       <c r="K65" t="n">
-        <v>30.95</v>
+        <v>14.78</v>
       </c>
       <c r="L65" t="n">
-        <v>434.98</v>
+        <v>207.69</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>40.36</v>
+        <v>19.28</v>
       </c>
       <c r="K66" t="n">
-        <v>327.32</v>
+        <v>156.35</v>
       </c>
       <c r="L66" t="n">
-        <v>329.8</v>
+        <v>157.53</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-376.27</v>
+        <v>-181.26</v>
       </c>
       <c r="K67" t="n">
-        <v>150.58</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>405.28</v>
+        <v>195.24</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-423.05</v>
+        <v>-186.33</v>
       </c>
       <c r="K68" t="n">
-        <v>-75.92</v>
+        <v>-33.44</v>
       </c>
       <c r="L68" t="n">
-        <v>429.81</v>
+        <v>189.31</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-516.78</v>
+        <v>-236.64</v>
       </c>
       <c r="K69" t="n">
-        <v>42.14</v>
+        <v>19.29</v>
       </c>
       <c r="L69" t="n">
-        <v>518.49</v>
+        <v>237.42</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>266.5</v>
+        <v>126.07</v>
       </c>
       <c r="K70" t="n">
-        <v>177.31</v>
+        <v>83.88</v>
       </c>
       <c r="L70" t="n">
-        <v>320.1</v>
+        <v>151.42</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-782.95</v>
+        <v>-423.14</v>
       </c>
       <c r="K71" t="n">
-        <v>51.55</v>
+        <v>27.86</v>
       </c>
       <c r="L71" t="n">
-        <v>784.64</v>
+        <v>424.06</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-763.71</v>
+        <v>-404.81</v>
       </c>
       <c r="K72" t="n">
-        <v>307.71</v>
+        <v>163.1</v>
       </c>
       <c r="L72" t="n">
-        <v>823.37</v>
+        <v>436.43</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>438.25</v>
+        <v>235.03</v>
       </c>
       <c r="K73" t="n">
-        <v>-34.33</v>
+        <v>-18.41</v>
       </c>
       <c r="L73" t="n">
-        <v>439.59</v>
+        <v>235.74</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-179.44</v>
+        <v>-79.90000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-53.5</v>
+        <v>-23.82</v>
       </c>
       <c r="L74" t="n">
-        <v>187.24</v>
+        <v>83.38</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>22.49</v>
+        <v>11.45</v>
       </c>
       <c r="K75" t="n">
-        <v>97.95999999999999</v>
+        <v>49.88</v>
       </c>
       <c r="L75" t="n">
-        <v>100.51</v>
+        <v>51.17</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>53.39</v>
+        <v>21.48</v>
       </c>
       <c r="K76" t="n">
-        <v>-116.25</v>
+        <v>-46.77</v>
       </c>
       <c r="L76" t="n">
-        <v>127.93</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>255.21</v>
+        <v>106.13</v>
       </c>
       <c r="K77" t="n">
-        <v>-127.35</v>
+        <v>-52.96</v>
       </c>
       <c r="L77" t="n">
-        <v>285.22</v>
+        <v>118.61</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-85.41</v>
+        <v>-35.83</v>
       </c>
       <c r="K78" t="n">
-        <v>382.82</v>
+        <v>160.61</v>
       </c>
       <c r="L78" t="n">
-        <v>392.23</v>
+        <v>164.55</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-28.48</v>
+        <v>-11.84</v>
       </c>
       <c r="K79" t="n">
-        <v>-183.72</v>
+        <v>-76.34999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>185.92</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-345.9</v>
+        <v>-173.53</v>
       </c>
       <c r="K80" t="n">
-        <v>46.21</v>
+        <v>23.18</v>
       </c>
       <c r="L80" t="n">
-        <v>348.97</v>
+        <v>175.07</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-337.63</v>
+        <v>-161.3</v>
       </c>
       <c r="K81" t="n">
-        <v>247.36</v>
+        <v>118.17</v>
       </c>
       <c r="L81" t="n">
-        <v>418.54</v>
+        <v>199.96</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-63.48</v>
+        <v>-30.33</v>
       </c>
       <c r="K82" t="n">
-        <v>626.13</v>
+        <v>299.18</v>
       </c>
       <c r="L82" t="n">
-        <v>629.34</v>
+        <v>300.71</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-265.11</v>
+        <v>-121.6</v>
       </c>
       <c r="K83" t="n">
-        <v>191.22</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>326.88</v>
+        <v>149.94</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-432.98</v>
+        <v>-208.5</v>
       </c>
       <c r="K84" t="n">
-        <v>-347.97</v>
+        <v>-167.57</v>
       </c>
       <c r="L84" t="n">
-        <v>555.48</v>
+        <v>267.49</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-78.31999999999999</v>
+        <v>-34.55</v>
       </c>
       <c r="K85" t="n">
-        <v>387.68</v>
+        <v>171.03</v>
       </c>
       <c r="L85" t="n">
-        <v>395.52</v>
+        <v>174.48</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-184.03</v>
+        <v>-43.36</v>
       </c>
       <c r="K86" t="n">
-        <v>165.51</v>
+        <v>38.99</v>
       </c>
       <c r="L86" t="n">
-        <v>247.51</v>
+        <v>58.31</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-401.81</v>
+        <v>-214.76</v>
       </c>
       <c r="K87" t="n">
-        <v>88.7</v>
+        <v>47.41</v>
       </c>
       <c r="L87" t="n">
-        <v>411.49</v>
+        <v>219.93</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>365.49</v>
+        <v>194.09</v>
       </c>
       <c r="K88" t="n">
-        <v>470.01</v>
+        <v>249.6</v>
       </c>
       <c r="L88" t="n">
-        <v>595.39</v>
+        <v>316.18</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.43</v>
+        <v>-3.26</v>
       </c>
       <c r="K14" t="n">
-        <v>-98.45</v>
+        <v>-93.43000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>98.51000000000001</v>
+        <v>93.48</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>16.8</v>
+        <v>16.79</v>
       </c>
       <c r="K15" t="n">
-        <v>-69.5</v>
+        <v>-69.45999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>71.5</v>
+        <v>71.45999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>61.09</v>
+        <v>59.33</v>
       </c>
       <c r="K16" t="n">
-        <v>63.51</v>
+        <v>61.68</v>
       </c>
       <c r="L16" t="n">
-        <v>88.13</v>
+        <v>85.59</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="K17" t="n">
-        <v>-81.54000000000001</v>
+        <v>-82.54000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>81.55</v>
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>34.83</v>
+        <v>36.43</v>
       </c>
       <c r="K18" t="n">
-        <v>-46.13</v>
+        <v>-48.25</v>
       </c>
       <c r="L18" t="n">
-        <v>57.8</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>13.41</v>
+        <v>13.43</v>
       </c>
       <c r="K19" t="n">
-        <v>79.81</v>
+        <v>79.92</v>
       </c>
       <c r="L19" t="n">
-        <v>80.93000000000001</v>
+        <v>81.04000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-224.1</v>
+        <v>-212.77</v>
       </c>
       <c r="K20" t="n">
-        <v>20.97</v>
+        <v>19.91</v>
       </c>
       <c r="L20" t="n">
-        <v>225.08</v>
+        <v>213.7</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>14.61</v>
+        <v>15.01</v>
       </c>
       <c r="K21" t="n">
-        <v>-106.93</v>
+        <v>-109.87</v>
       </c>
       <c r="L21" t="n">
-        <v>107.92</v>
+        <v>110.9</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>83.34999999999999</v>
+        <v>80.48</v>
       </c>
       <c r="K22" t="n">
-        <v>146.69</v>
+        <v>141.65</v>
       </c>
       <c r="L22" t="n">
-        <v>168.71</v>
+        <v>162.92</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-126.1</v>
+        <v>-121.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-266.52</v>
+        <v>-257.61</v>
       </c>
       <c r="L23" t="n">
-        <v>294.84</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-196.91</v>
+        <v>-197.99</v>
       </c>
       <c r="K24" t="n">
         <v>-0.63</v>
       </c>
       <c r="L24" t="n">
-        <v>196.91</v>
+        <v>197.99</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>129.29</v>
+        <v>138.61</v>
       </c>
       <c r="K25" t="n">
-        <v>10.91</v>
+        <v>11.69</v>
       </c>
       <c r="L25" t="n">
-        <v>129.75</v>
+        <v>139.1</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-226.61</v>
+        <v>-242.99</v>
       </c>
       <c r="K26" t="n">
-        <v>-88.19</v>
+        <v>-94.56999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>243.17</v>
+        <v>260.74</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-74.59</v>
+        <v>-74.44</v>
       </c>
       <c r="K27" t="n">
-        <v>509.5</v>
+        <v>508.46</v>
       </c>
       <c r="L27" t="n">
-        <v>514.9299999999999</v>
+        <v>513.88</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-54.14</v>
+        <v>-59.49</v>
       </c>
       <c r="K28" t="n">
-        <v>-260.78</v>
+        <v>-286.51</v>
       </c>
       <c r="L28" t="n">
-        <v>266.35</v>
+        <v>292.62</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>64.22</v>
+        <v>64.78</v>
       </c>
       <c r="K29" t="n">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
       <c r="L29" t="n">
-        <v>64.39</v>
+        <v>64.94</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>21.85</v>
+        <v>19.03</v>
       </c>
       <c r="K30" t="n">
-        <v>116.55</v>
+        <v>101.53</v>
       </c>
       <c r="L30" t="n">
-        <v>118.58</v>
+        <v>103.29</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>72.05</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>62.23</v>
+        <v>60.67</v>
       </c>
       <c r="L31" t="n">
-        <v>95.20999999999999</v>
+        <v>92.81</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-17.38</v>
+        <v>-16.2</v>
       </c>
       <c r="K32" t="n">
-        <v>-139.34</v>
+        <v>-129.87</v>
       </c>
       <c r="L32" t="n">
-        <v>140.42</v>
+        <v>130.88</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>75.2</v>
+        <v>75</v>
       </c>
       <c r="K33" t="n">
-        <v>31.58</v>
+        <v>31.49</v>
       </c>
       <c r="L33" t="n">
-        <v>81.56</v>
+        <v>81.34</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-60.33</v>
+        <v>-62.01</v>
       </c>
       <c r="K34" t="n">
-        <v>17.09</v>
+        <v>17.57</v>
       </c>
       <c r="L34" t="n">
-        <v>62.71</v>
+        <v>64.45</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>89.81</v>
+        <v>95.25</v>
       </c>
       <c r="K35" t="n">
-        <v>17.48</v>
+        <v>18.53</v>
       </c>
       <c r="L35" t="n">
-        <v>91.48999999999999</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>19.32</v>
+        <v>18.75</v>
       </c>
       <c r="K36" t="n">
-        <v>-181.99</v>
+        <v>-176.61</v>
       </c>
       <c r="L36" t="n">
-        <v>183.02</v>
+        <v>177.6</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-92.08</v>
+        <v>-91.15000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-101.94</v>
+        <v>-100.91</v>
       </c>
       <c r="L37" t="n">
-        <v>137.37</v>
+        <v>135.98</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-17.85</v>
+        <v>-19.34</v>
       </c>
       <c r="K38" t="n">
-        <v>112.18</v>
+        <v>121.54</v>
       </c>
       <c r="L38" t="n">
-        <v>113.59</v>
+        <v>123.07</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-182.16</v>
+        <v>-182.19</v>
       </c>
       <c r="K39" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="L39" t="n">
-        <v>182.18</v>
+        <v>182.21</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-189.68</v>
+        <v>-196.45</v>
       </c>
       <c r="K40" t="n">
-        <v>127.71</v>
+        <v>132.27</v>
       </c>
       <c r="L40" t="n">
-        <v>228.67</v>
+        <v>236.83</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-253.28</v>
+        <v>-259.64</v>
       </c>
       <c r="K41" t="n">
-        <v>-242.81</v>
+        <v>-248.9</v>
       </c>
       <c r="L41" t="n">
-        <v>350.86</v>
+        <v>359.67</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>215.95</v>
+        <v>227.63</v>
       </c>
       <c r="K42" t="n">
-        <v>131.3</v>
+        <v>138.4</v>
       </c>
       <c r="L42" t="n">
-        <v>252.73</v>
+        <v>266.4</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>263.79</v>
+        <v>271.66</v>
       </c>
       <c r="K43" t="n">
-        <v>41.33</v>
+        <v>42.56</v>
       </c>
       <c r="L43" t="n">
-        <v>267</v>
+        <v>274.97</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-75.77</v>
+        <v>-73.3</v>
       </c>
       <c r="K44" t="n">
-        <v>-41.83</v>
+        <v>-40.46</v>
       </c>
       <c r="L44" t="n">
-        <v>86.55</v>
+        <v>83.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-35.91</v>
+        <v>-36.64</v>
       </c>
       <c r="K45" t="n">
-        <v>52.74</v>
+        <v>53.81</v>
       </c>
       <c r="L45" t="n">
-        <v>63.8</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>87.45</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-69.40000000000001</v>
+        <v>-65.7</v>
       </c>
       <c r="L46" t="n">
-        <v>111.64</v>
+        <v>105.69</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-85.28</v>
+        <v>-77.25</v>
       </c>
       <c r="K47" t="n">
-        <v>56.37</v>
+        <v>51.07</v>
       </c>
       <c r="L47" t="n">
-        <v>102.23</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-106.73</v>
+        <v>-103.46</v>
       </c>
       <c r="K48" t="n">
-        <v>21.85</v>
+        <v>21.18</v>
       </c>
       <c r="L48" t="n">
-        <v>108.94</v>
+        <v>105.61</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-16.84</v>
+        <v>-16.99</v>
       </c>
       <c r="K49" t="n">
-        <v>-71.15000000000001</v>
+        <v>-71.79000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>73.12</v>
+        <v>73.77</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>84.78</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>33.24</v>
+        <v>35.85</v>
       </c>
       <c r="L50" t="n">
-        <v>91.06999999999999</v>
+        <v>98.20999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>205.14</v>
+        <v>195.31</v>
       </c>
       <c r="K51" t="n">
-        <v>68.42</v>
+        <v>65.14</v>
       </c>
       <c r="L51" t="n">
-        <v>216.25</v>
+        <v>205.89</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-60.82</v>
+        <v>-58.6</v>
       </c>
       <c r="K52" t="n">
-        <v>-199.93</v>
+        <v>-192.65</v>
       </c>
       <c r="L52" t="n">
-        <v>208.98</v>
+        <v>201.36</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-290.1</v>
+        <v>-281.14</v>
       </c>
       <c r="K53" t="n">
-        <v>60.57</v>
+        <v>58.7</v>
       </c>
       <c r="L53" t="n">
-        <v>296.36</v>
+        <v>287.2</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>212.31</v>
+        <v>229.99</v>
       </c>
       <c r="K54" t="n">
-        <v>237.84</v>
+        <v>257.65</v>
       </c>
       <c r="L54" t="n">
-        <v>318.81</v>
+        <v>345.36</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-150.91</v>
+        <v>-160.71</v>
       </c>
       <c r="K55" t="n">
-        <v>-57.61</v>
+        <v>-61.35</v>
       </c>
       <c r="L55" t="n">
-        <v>161.53</v>
+        <v>172.02</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>267.79</v>
+        <v>279.91</v>
       </c>
       <c r="K56" t="n">
-        <v>-15.23</v>
+        <v>-15.91</v>
       </c>
       <c r="L56" t="n">
-        <v>268.23</v>
+        <v>280.36</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>205.92</v>
+        <v>217.25</v>
       </c>
       <c r="K57" t="n">
-        <v>130.76</v>
+        <v>137.96</v>
       </c>
       <c r="L57" t="n">
-        <v>243.94</v>
+        <v>257.35</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>253.65</v>
+        <v>285.24</v>
       </c>
       <c r="K58" t="n">
-        <v>-94.92</v>
+        <v>-106.74</v>
       </c>
       <c r="L58" t="n">
-        <v>270.83</v>
+        <v>304.56</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-60.33</v>
+        <v>-57.61</v>
       </c>
       <c r="K59" t="n">
-        <v>89.65000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>108.06</v>
+        <v>103.18</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-71.26000000000001</v>
+        <v>-68.18000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-53.47</v>
+        <v>-51.17</v>
       </c>
       <c r="L60" t="n">
-        <v>89.09</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
       <c r="K61" t="n">
-        <v>60.97</v>
+        <v>60.92</v>
       </c>
       <c r="L61" t="n">
-        <v>68.81</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-95.19</v>
+        <v>-86.34</v>
       </c>
       <c r="K62" t="n">
-        <v>27.95</v>
+        <v>25.35</v>
       </c>
       <c r="L62" t="n">
-        <v>99.20999999999999</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>75.16</v>
+        <v>68.52</v>
       </c>
       <c r="K63" t="n">
-        <v>-50.39</v>
+        <v>-45.94</v>
       </c>
       <c r="L63" t="n">
-        <v>90.48999999999999</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-93.28</v>
+        <v>-88.94</v>
       </c>
       <c r="K64" t="n">
-        <v>77.29000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="L64" t="n">
-        <v>121.14</v>
+        <v>115.51</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>207.16</v>
+        <v>197.26</v>
       </c>
       <c r="K65" t="n">
-        <v>14.78</v>
+        <v>14.07</v>
       </c>
       <c r="L65" t="n">
-        <v>207.69</v>
+        <v>197.76</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>19.28</v>
+        <v>18.89</v>
       </c>
       <c r="K66" t="n">
-        <v>156.35</v>
+        <v>153.2</v>
       </c>
       <c r="L66" t="n">
-        <v>157.53</v>
+        <v>154.36</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-181.26</v>
+        <v>-173.84</v>
       </c>
       <c r="K67" t="n">
-        <v>72.54000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>195.24</v>
+        <v>187.25</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-186.33</v>
+        <v>-195.63</v>
       </c>
       <c r="K68" t="n">
-        <v>-33.44</v>
+        <v>-35.11</v>
       </c>
       <c r="L68" t="n">
-        <v>189.31</v>
+        <v>198.76</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-236.64</v>
+        <v>-233.42</v>
       </c>
       <c r="K69" t="n">
-        <v>19.29</v>
+        <v>19.03</v>
       </c>
       <c r="L69" t="n">
-        <v>237.42</v>
+        <v>234.2</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>126.07</v>
+        <v>131.38</v>
       </c>
       <c r="K70" t="n">
-        <v>83.88</v>
+        <v>87.41</v>
       </c>
       <c r="L70" t="n">
-        <v>151.42</v>
+        <v>157.8</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-423.14</v>
+        <v>-483.33</v>
       </c>
       <c r="K71" t="n">
-        <v>27.86</v>
+        <v>31.82</v>
       </c>
       <c r="L71" t="n">
-        <v>424.06</v>
+        <v>484.37</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-404.81</v>
+        <v>-440.44</v>
       </c>
       <c r="K72" t="n">
-        <v>163.1</v>
+        <v>177.46</v>
       </c>
       <c r="L72" t="n">
-        <v>436.43</v>
+        <v>474.85</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>235.03</v>
+        <v>252.78</v>
       </c>
       <c r="K73" t="n">
-        <v>-18.41</v>
+        <v>-19.8</v>
       </c>
       <c r="L73" t="n">
-        <v>235.74</v>
+        <v>253.56</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-79.90000000000001</v>
+        <v>-78.09999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>-23.82</v>
+        <v>-23.28</v>
       </c>
       <c r="L74" t="n">
-        <v>83.38</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>11.45</v>
+        <v>11.99</v>
       </c>
       <c r="K75" t="n">
-        <v>49.88</v>
+        <v>52.24</v>
       </c>
       <c r="L75" t="n">
-        <v>51.17</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>21.48</v>
+        <v>22.38</v>
       </c>
       <c r="K76" t="n">
-        <v>-46.77</v>
+        <v>-48.74</v>
       </c>
       <c r="L76" t="n">
-        <v>51.46</v>
+        <v>53.63</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>106.13</v>
+        <v>98.19</v>
       </c>
       <c r="K77" t="n">
-        <v>-52.96</v>
+        <v>-49</v>
       </c>
       <c r="L77" t="n">
-        <v>118.61</v>
+        <v>109.73</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-35.83</v>
+        <v>-32.73</v>
       </c>
       <c r="K78" t="n">
-        <v>160.61</v>
+        <v>146.72</v>
       </c>
       <c r="L78" t="n">
-        <v>164.55</v>
+        <v>150.33</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-11.84</v>
+        <v>-11.88</v>
       </c>
       <c r="K79" t="n">
-        <v>-76.34999999999999</v>
+        <v>-76.63</v>
       </c>
       <c r="L79" t="n">
-        <v>77.26000000000001</v>
+        <v>77.54000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-173.53</v>
+        <v>-168.12</v>
       </c>
       <c r="K80" t="n">
-        <v>23.18</v>
+        <v>22.46</v>
       </c>
       <c r="L80" t="n">
-        <v>175.07</v>
+        <v>169.61</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-161.3</v>
+        <v>-153.97</v>
       </c>
       <c r="K81" t="n">
-        <v>118.17</v>
+        <v>112.8</v>
       </c>
       <c r="L81" t="n">
-        <v>199.96</v>
+        <v>190.87</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-30.33</v>
+        <v>-27.99</v>
       </c>
       <c r="K82" t="n">
-        <v>299.18</v>
+        <v>276.06</v>
       </c>
       <c r="L82" t="n">
-        <v>300.71</v>
+        <v>277.48</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-121.6</v>
+        <v>-139.56</v>
       </c>
       <c r="K83" t="n">
-        <v>87.70999999999999</v>
+        <v>100.66</v>
       </c>
       <c r="L83" t="n">
-        <v>149.94</v>
+        <v>172.07</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-208.5</v>
+        <v>-202.28</v>
       </c>
       <c r="K84" t="n">
-        <v>-167.57</v>
+        <v>-162.57</v>
       </c>
       <c r="L84" t="n">
-        <v>267.49</v>
+        <v>259.51</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-34.55</v>
+        <v>-37.67</v>
       </c>
       <c r="K85" t="n">
-        <v>171.03</v>
+        <v>186.48</v>
       </c>
       <c r="L85" t="n">
-        <v>174.48</v>
+        <v>190.25</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-43.36</v>
+        <v>-44.71</v>
       </c>
       <c r="K86" t="n">
-        <v>38.99</v>
+        <v>40.21</v>
       </c>
       <c r="L86" t="n">
-        <v>58.31</v>
+        <v>60.13</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-214.76</v>
+        <v>-238.76</v>
       </c>
       <c r="K87" t="n">
-        <v>47.41</v>
+        <v>52.71</v>
       </c>
       <c r="L87" t="n">
-        <v>219.93</v>
+        <v>244.51</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>194.09</v>
+        <v>211.47</v>
       </c>
       <c r="K88" t="n">
-        <v>249.6</v>
+        <v>271.94</v>
       </c>
       <c r="L88" t="n">
-        <v>316.18</v>
+        <v>344.49</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.26</v>
+        <v>-3.18</v>
       </c>
       <c r="K14" t="n">
-        <v>-93.43000000000001</v>
+        <v>-91.29000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>93.48</v>
+        <v>91.34</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>16.79</v>
+        <v>17.1</v>
       </c>
       <c r="K15" t="n">
-        <v>-69.45999999999999</v>
+        <v>-70.73999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>71.45999999999999</v>
+        <v>72.78</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>59.33</v>
+        <v>58.3</v>
       </c>
       <c r="K16" t="n">
-        <v>61.68</v>
+        <v>60.61</v>
       </c>
       <c r="L16" t="n">
-        <v>85.59</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="K17" t="n">
-        <v>-82.54000000000001</v>
+        <v>-84.62</v>
       </c>
       <c r="L17" t="n">
-        <v>82.54000000000001</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>36.43</v>
+        <v>39.38</v>
       </c>
       <c r="K18" t="n">
-        <v>-48.25</v>
+        <v>-52.15</v>
       </c>
       <c r="L18" t="n">
-        <v>60.45</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>13.43</v>
+        <v>13.98</v>
       </c>
       <c r="K19" t="n">
-        <v>79.92</v>
+        <v>83.19</v>
       </c>
       <c r="L19" t="n">
-        <v>81.04000000000001</v>
+        <v>84.34999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-212.77</v>
+        <v>-203.12</v>
       </c>
       <c r="K20" t="n">
-        <v>19.91</v>
+        <v>19.01</v>
       </c>
       <c r="L20" t="n">
-        <v>213.7</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>15.01</v>
+        <v>15.65</v>
       </c>
       <c r="K21" t="n">
-        <v>-109.87</v>
+        <v>-114.53</v>
       </c>
       <c r="L21" t="n">
-        <v>110.9</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>80.48</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>141.65</v>
+        <v>135.89</v>
       </c>
       <c r="L22" t="n">
-        <v>162.92</v>
+        <v>156.3</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-121.88</v>
+        <v>-115.83</v>
       </c>
       <c r="K23" t="n">
-        <v>-257.61</v>
+        <v>-244.82</v>
       </c>
       <c r="L23" t="n">
-        <v>284.99</v>
+        <v>270.84</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-197.99</v>
+        <v>-197.31</v>
       </c>
       <c r="K24" t="n">
         <v>-0.63</v>
       </c>
       <c r="L24" t="n">
-        <v>197.99</v>
+        <v>197.31</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>138.61</v>
+        <v>148.24</v>
       </c>
       <c r="K25" t="n">
-        <v>11.69</v>
+        <v>12.51</v>
       </c>
       <c r="L25" t="n">
-        <v>139.1</v>
+        <v>148.77</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-242.99</v>
+        <v>-249.19</v>
       </c>
       <c r="K26" t="n">
-        <v>-94.56999999999999</v>
+        <v>-96.98</v>
       </c>
       <c r="L26" t="n">
-        <v>260.74</v>
+        <v>267.39</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-74.44</v>
+        <v>-70.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>508.46</v>
+        <v>478.85</v>
       </c>
       <c r="L27" t="n">
-        <v>513.88</v>
+        <v>483.95</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-59.49</v>
+        <v>-61.05</v>
       </c>
       <c r="K28" t="n">
-        <v>-286.51</v>
+        <v>-294.02</v>
       </c>
       <c r="L28" t="n">
-        <v>292.62</v>
+        <v>300.29</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>64.78</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>4.66</v>
+        <v>4.79</v>
       </c>
       <c r="L29" t="n">
-        <v>64.94</v>
+        <v>66.77</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>19.03</v>
+        <v>18.22</v>
       </c>
       <c r="K30" t="n">
-        <v>101.53</v>
+        <v>97.22</v>
       </c>
       <c r="L30" t="n">
-        <v>103.29</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>70.23999999999999</v>
+        <v>68.17</v>
       </c>
       <c r="K31" t="n">
-        <v>60.67</v>
+        <v>58.88</v>
       </c>
       <c r="L31" t="n">
-        <v>92.81</v>
+        <v>90.08</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-16.2</v>
+        <v>-15.35</v>
       </c>
       <c r="K32" t="n">
-        <v>-129.87</v>
+        <v>-123.05</v>
       </c>
       <c r="L32" t="n">
-        <v>130.88</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>75</v>
+        <v>77.61</v>
       </c>
       <c r="K33" t="n">
-        <v>31.49</v>
+        <v>32.59</v>
       </c>
       <c r="L33" t="n">
-        <v>81.34</v>
+        <v>84.17</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-62.01</v>
+        <v>-66.63</v>
       </c>
       <c r="K34" t="n">
-        <v>17.57</v>
+        <v>18.87</v>
       </c>
       <c r="L34" t="n">
-        <v>64.45</v>
+        <v>69.25</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>95.25</v>
+        <v>102.07</v>
       </c>
       <c r="K35" t="n">
-        <v>18.53</v>
+        <v>19.86</v>
       </c>
       <c r="L35" t="n">
-        <v>97.03</v>
+        <v>103.99</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>18.75</v>
+        <v>18.38</v>
       </c>
       <c r="K36" t="n">
-        <v>-176.61</v>
+        <v>-173.09</v>
       </c>
       <c r="L36" t="n">
-        <v>177.6</v>
+        <v>174.06</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-91.15000000000001</v>
+        <v>-90.93000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-100.91</v>
+        <v>-100.67</v>
       </c>
       <c r="L37" t="n">
-        <v>135.98</v>
+        <v>135.66</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-19.34</v>
+        <v>-20.92</v>
       </c>
       <c r="K38" t="n">
-        <v>121.54</v>
+        <v>131.49</v>
       </c>
       <c r="L38" t="n">
-        <v>123.07</v>
+        <v>133.15</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-182.19</v>
+        <v>-181.34</v>
       </c>
       <c r="K39" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="L39" t="n">
-        <v>182.21</v>
+        <v>181.36</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-196.45</v>
+        <v>-192.46</v>
       </c>
       <c r="K40" t="n">
-        <v>132.27</v>
+        <v>129.58</v>
       </c>
       <c r="L40" t="n">
-        <v>236.83</v>
+        <v>232.01</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-259.64</v>
+        <v>-252.89</v>
       </c>
       <c r="K41" t="n">
-        <v>-248.9</v>
+        <v>-242.43</v>
       </c>
       <c r="L41" t="n">
-        <v>359.67</v>
+        <v>350.32</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>227.63</v>
+        <v>229.71</v>
       </c>
       <c r="K42" t="n">
-        <v>138.4</v>
+        <v>139.67</v>
       </c>
       <c r="L42" t="n">
-        <v>266.4</v>
+        <v>268.84</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>271.66</v>
+        <v>271.67</v>
       </c>
       <c r="K43" t="n">
         <v>42.56</v>
       </c>
       <c r="L43" t="n">
-        <v>274.97</v>
+        <v>274.98</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-73.3</v>
+        <v>-72.64</v>
       </c>
       <c r="K44" t="n">
-        <v>-40.46</v>
+        <v>-40.1</v>
       </c>
       <c r="L44" t="n">
-        <v>83.72</v>
+        <v>82.97</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-36.64</v>
+        <v>-38.64</v>
       </c>
       <c r="K45" t="n">
-        <v>53.81</v>
+        <v>56.74</v>
       </c>
       <c r="L45" t="n">
-        <v>65.09999999999999</v>
+        <v>68.65000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>82.79000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-65.7</v>
+        <v>-63.8</v>
       </c>
       <c r="L46" t="n">
-        <v>105.69</v>
+        <v>102.64</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-77.25</v>
+        <v>-79.20999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>51.07</v>
+        <v>52.36</v>
       </c>
       <c r="L47" t="n">
-        <v>92.59999999999999</v>
+        <v>94.95</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-103.46</v>
+        <v>-102.32</v>
       </c>
       <c r="K48" t="n">
-        <v>21.18</v>
+        <v>20.95</v>
       </c>
       <c r="L48" t="n">
-        <v>105.61</v>
+        <v>104.44</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-16.99</v>
+        <v>-17.83</v>
       </c>
       <c r="K49" t="n">
-        <v>-71.79000000000001</v>
+        <v>-75.33</v>
       </c>
       <c r="L49" t="n">
-        <v>73.77</v>
+        <v>77.41</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>91.43000000000001</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>35.85</v>
+        <v>39.14</v>
       </c>
       <c r="L50" t="n">
-        <v>98.20999999999999</v>
+        <v>107.22</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>195.31</v>
+        <v>186.79</v>
       </c>
       <c r="K51" t="n">
-        <v>65.14</v>
+        <v>62.3</v>
       </c>
       <c r="L51" t="n">
-        <v>205.89</v>
+        <v>196.91</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-58.6</v>
+        <v>-56.91</v>
       </c>
       <c r="K52" t="n">
-        <v>-192.65</v>
+        <v>-187.09</v>
       </c>
       <c r="L52" t="n">
-        <v>201.36</v>
+        <v>195.56</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-281.14</v>
+        <v>-268.45</v>
       </c>
       <c r="K53" t="n">
-        <v>58.7</v>
+        <v>56.05</v>
       </c>
       <c r="L53" t="n">
-        <v>287.2</v>
+        <v>274.24</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>229.99</v>
+        <v>230.33</v>
       </c>
       <c r="K54" t="n">
-        <v>257.65</v>
+        <v>258.03</v>
       </c>
       <c r="L54" t="n">
-        <v>345.36</v>
+        <v>345.88</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-160.71</v>
+        <v>-168.2</v>
       </c>
       <c r="K55" t="n">
-        <v>-61.35</v>
+        <v>-64.20999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>172.02</v>
+        <v>180.04</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>279.91</v>
+        <v>282.03</v>
       </c>
       <c r="K56" t="n">
-        <v>-15.91</v>
+        <v>-16.03</v>
       </c>
       <c r="L56" t="n">
-        <v>280.36</v>
+        <v>282.48</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>217.25</v>
+        <v>222.57</v>
       </c>
       <c r="K57" t="n">
-        <v>137.96</v>
+        <v>141.33</v>
       </c>
       <c r="L57" t="n">
-        <v>257.35</v>
+        <v>263.65</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>285.24</v>
+        <v>294.46</v>
       </c>
       <c r="K58" t="n">
-        <v>-106.74</v>
+        <v>-110.19</v>
       </c>
       <c r="L58" t="n">
-        <v>304.56</v>
+        <v>314.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-57.61</v>
+        <v>-55.72</v>
       </c>
       <c r="K59" t="n">
-        <v>85.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="L59" t="n">
-        <v>103.18</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-68.18000000000001</v>
+        <v>-67.38</v>
       </c>
       <c r="K60" t="n">
-        <v>-51.17</v>
+        <v>-50.56</v>
       </c>
       <c r="L60" t="n">
-        <v>85.25</v>
+        <v>84.23999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>31.88</v>
+        <v>32.99</v>
       </c>
       <c r="K61" t="n">
-        <v>60.92</v>
+        <v>63.05</v>
       </c>
       <c r="L61" t="n">
-        <v>68.75</v>
+        <v>71.16</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-86.34</v>
+        <v>-88.02</v>
       </c>
       <c r="K62" t="n">
-        <v>25.35</v>
+        <v>25.84</v>
       </c>
       <c r="L62" t="n">
-        <v>89.98</v>
+        <v>91.73</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>68.52</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-45.94</v>
+        <v>-47.76</v>
       </c>
       <c r="L63" t="n">
-        <v>82.5</v>
+        <v>85.76000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-88.94</v>
+        <v>-86.92</v>
       </c>
       <c r="K64" t="n">
-        <v>73.7</v>
+        <v>72.03</v>
       </c>
       <c r="L64" t="n">
-        <v>115.51</v>
+        <v>112.89</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>197.26</v>
+        <v>190.51</v>
       </c>
       <c r="K65" t="n">
-        <v>14.07</v>
+        <v>13.59</v>
       </c>
       <c r="L65" t="n">
-        <v>197.76</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>18.89</v>
+        <v>18.9</v>
       </c>
       <c r="K66" t="n">
-        <v>153.2</v>
+        <v>153.23</v>
       </c>
       <c r="L66" t="n">
-        <v>154.36</v>
+        <v>154.39</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-173.84</v>
+        <v>-167.89</v>
       </c>
       <c r="K67" t="n">
-        <v>69.56999999999999</v>
+        <v>67.19</v>
       </c>
       <c r="L67" t="n">
-        <v>187.25</v>
+        <v>180.83</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-195.63</v>
+        <v>-198.71</v>
       </c>
       <c r="K68" t="n">
-        <v>-35.11</v>
+        <v>-35.66</v>
       </c>
       <c r="L68" t="n">
-        <v>198.76</v>
+        <v>201.88</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-233.42</v>
+        <v>-227.5</v>
       </c>
       <c r="K69" t="n">
-        <v>19.03</v>
+        <v>18.55</v>
       </c>
       <c r="L69" t="n">
-        <v>234.2</v>
+        <v>228.26</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>131.38</v>
+        <v>136.45</v>
       </c>
       <c r="K70" t="n">
-        <v>87.41</v>
+        <v>90.78</v>
       </c>
       <c r="L70" t="n">
-        <v>157.8</v>
+        <v>163.89</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-483.33</v>
+        <v>-479.06</v>
       </c>
       <c r="K71" t="n">
-        <v>31.82</v>
+        <v>31.54</v>
       </c>
       <c r="L71" t="n">
-        <v>484.37</v>
+        <v>480.1</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-440.44</v>
+        <v>-423.87</v>
       </c>
       <c r="K72" t="n">
-        <v>177.46</v>
+        <v>170.78</v>
       </c>
       <c r="L72" t="n">
-        <v>474.85</v>
+        <v>456.98</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>252.78</v>
+        <v>259.18</v>
       </c>
       <c r="K73" t="n">
-        <v>-19.8</v>
+        <v>-20.3</v>
       </c>
       <c r="L73" t="n">
-        <v>253.56</v>
+        <v>259.97</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-78.09999999999999</v>
+        <v>-78.27</v>
       </c>
       <c r="K74" t="n">
-        <v>-23.28</v>
+        <v>-23.34</v>
       </c>
       <c r="L74" t="n">
-        <v>81.5</v>
+        <v>81.68000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>11.99</v>
+        <v>12.71</v>
       </c>
       <c r="K75" t="n">
-        <v>52.24</v>
+        <v>55.37</v>
       </c>
       <c r="L75" t="n">
-        <v>53.59</v>
+        <v>56.81</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>22.38</v>
+        <v>24.35</v>
       </c>
       <c r="K76" t="n">
-        <v>-48.74</v>
+        <v>-53.01</v>
       </c>
       <c r="L76" t="n">
-        <v>53.63</v>
+        <v>58.34</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>98.19</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-49</v>
+        <v>-47.65</v>
       </c>
       <c r="L77" t="n">
-        <v>109.73</v>
+        <v>106.72</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-32.73</v>
+        <v>-30.76</v>
       </c>
       <c r="K78" t="n">
-        <v>146.72</v>
+        <v>137.86</v>
       </c>
       <c r="L78" t="n">
-        <v>150.33</v>
+        <v>141.24</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-11.88</v>
+        <v>-12.46</v>
       </c>
       <c r="K79" t="n">
-        <v>-76.63</v>
+        <v>-80.34999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>77.54000000000001</v>
+        <v>81.31</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-168.12</v>
+        <v>-162.89</v>
       </c>
       <c r="K80" t="n">
-        <v>22.46</v>
+        <v>21.76</v>
       </c>
       <c r="L80" t="n">
-        <v>169.61</v>
+        <v>164.33</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-153.97</v>
+        <v>-149.46</v>
       </c>
       <c r="K81" t="n">
-        <v>112.8</v>
+        <v>109.5</v>
       </c>
       <c r="L81" t="n">
-        <v>190.87</v>
+        <v>185.27</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-27.99</v>
+        <v>-26.06</v>
       </c>
       <c r="K82" t="n">
-        <v>276.06</v>
+        <v>257.01</v>
       </c>
       <c r="L82" t="n">
-        <v>277.48</v>
+        <v>258.33</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-139.56</v>
+        <v>-150.26</v>
       </c>
       <c r="K83" t="n">
-        <v>100.66</v>
+        <v>108.38</v>
       </c>
       <c r="L83" t="n">
-        <v>172.07</v>
+        <v>185.27</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-202.28</v>
+        <v>-193.65</v>
       </c>
       <c r="K84" t="n">
-        <v>-162.57</v>
+        <v>-155.63</v>
       </c>
       <c r="L84" t="n">
-        <v>259.51</v>
+        <v>248.44</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-37.67</v>
+        <v>-38.94</v>
       </c>
       <c r="K85" t="n">
-        <v>186.48</v>
+        <v>192.76</v>
       </c>
       <c r="L85" t="n">
-        <v>190.25</v>
+        <v>196.66</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-44.71</v>
+        <v>-48.49</v>
       </c>
       <c r="K86" t="n">
-        <v>40.21</v>
+        <v>43.61</v>
       </c>
       <c r="L86" t="n">
-        <v>60.13</v>
+        <v>65.20999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-238.76</v>
+        <v>-250.29</v>
       </c>
       <c r="K87" t="n">
-        <v>52.71</v>
+        <v>55.25</v>
       </c>
       <c r="L87" t="n">
-        <v>244.51</v>
+        <v>256.31</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>211.47</v>
+        <v>210.97</v>
       </c>
       <c r="K88" t="n">
-        <v>271.94</v>
+        <v>271.3</v>
       </c>
       <c r="L88" t="n">
-        <v>344.49</v>
+        <v>343.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4</v>
+        <v>3.92</v>
       </c>
       <c r="F14" t="n">
-        <v>13.41</v>
+        <v>12.24</v>
       </c>
       <c r="G14" t="n">
-        <v>357.5</v>
+        <v>23.1</v>
       </c>
       <c r="H14" t="n">
-        <v>81.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.18</v>
+        <v>19.53</v>
       </c>
       <c r="K14" t="n">
-        <v>-91.29000000000001</v>
+        <v>-74.67</v>
       </c>
       <c r="L14" t="n">
-        <v>91.34</v>
+        <v>77.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:31:02</t>
+          <t>04:29:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="F15" t="n">
-        <v>14.62</v>
+        <v>10.8</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>10.9</v>
       </c>
       <c r="H15" t="n">
-        <v>87.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>17.1</v>
+        <v>66.11</v>
       </c>
       <c r="K15" t="n">
-        <v>-70.73999999999999</v>
+        <v>-59.87</v>
       </c>
       <c r="L15" t="n">
-        <v>72.78</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:33:31</t>
+          <t>04:30:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.73</v>
+        <v>3.79</v>
       </c>
       <c r="F16" t="n">
-        <v>14.26</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="H16" t="n">
-        <v>85.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>58.3</v>
+        <v>0.79</v>
       </c>
       <c r="K16" t="n">
-        <v>60.61</v>
+        <v>-72.2</v>
       </c>
       <c r="L16" t="n">
-        <v>84.09999999999999</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:38:21</t>
+          <t>04:35:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.59</v>
+        <v>4.26</v>
       </c>
       <c r="F17" t="n">
-        <v>14.02</v>
+        <v>10.72</v>
       </c>
       <c r="G17" t="n">
-        <v>6.9</v>
+        <v>22.8</v>
       </c>
       <c r="H17" t="n">
-        <v>82</v>
+        <v>89.7</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>0.53</v>
+        <v>-26.3</v>
       </c>
       <c r="K17" t="n">
-        <v>-84.62</v>
+        <v>93.92</v>
       </c>
       <c r="L17" t="n">
-        <v>84.62</v>
+        <v>97.53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:40:38</t>
+          <t>04:37:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="F18" t="n">
-        <v>14.39</v>
+        <v>13.89</v>
       </c>
       <c r="G18" t="n">
-        <v>358.5</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>39.38</v>
+        <v>14.05</v>
       </c>
       <c r="K18" t="n">
-        <v>-52.15</v>
+        <v>86.77</v>
       </c>
       <c r="L18" t="n">
-        <v>65.34999999999999</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:41:10</t>
+          <t>04:38:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.53</v>
+        <v>4.58</v>
       </c>
       <c r="F19" t="n">
-        <v>13.62</v>
+        <v>13.13</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>88.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>13.98</v>
+        <v>13.83</v>
       </c>
       <c r="K19" t="n">
-        <v>83.19</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>84.34999999999999</v>
+        <v>90.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:44:32</t>
+          <t>04:42:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.61</v>
+        <v>4.33</v>
       </c>
       <c r="F20" t="n">
-        <v>13.66</v>
+        <v>12.37</v>
       </c>
       <c r="G20" t="n">
-        <v>24</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>85</v>
+        <v>85.7</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-203.12</v>
+        <v>26.78</v>
       </c>
       <c r="K20" t="n">
-        <v>19.01</v>
+        <v>-123.19</v>
       </c>
       <c r="L20" t="n">
-        <v>204</v>
+        <v>126.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:45:49</t>
+          <t>04:43:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.34</v>
+        <v>3.24</v>
       </c>
       <c r="F21" t="n">
-        <v>13.92</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6</v>
+        <v>13.8</v>
       </c>
       <c r="H21" t="n">
-        <v>84.8</v>
+        <v>82.7</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>15.65</v>
+        <v>147.83</v>
       </c>
       <c r="K21" t="n">
-        <v>-114.53</v>
+        <v>82.67</v>
       </c>
       <c r="L21" t="n">
-        <v>115.6</v>
+        <v>169.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:47:40</t>
+          <t>04:45:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="F22" t="n">
-        <v>13.69</v>
+        <v>11.98</v>
       </c>
       <c r="G22" t="n">
-        <v>13.5</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
-        <v>85.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>77.20999999999999</v>
+        <v>-85.72</v>
       </c>
       <c r="K22" t="n">
-        <v>135.89</v>
+        <v>-176.11</v>
       </c>
       <c r="L22" t="n">
-        <v>156.3</v>
+        <v>195.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:50:58</t>
+          <t>04:50:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1006,31 +1006,31 @@
         <v>4.46</v>
       </c>
       <c r="F23" t="n">
-        <v>13.57</v>
+        <v>14.23</v>
       </c>
       <c r="G23" t="n">
-        <v>357.4</v>
+        <v>18.4</v>
       </c>
       <c r="H23" t="n">
-        <v>84.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-115.83</v>
+        <v>-11.5</v>
       </c>
       <c r="K23" t="n">
-        <v>-244.82</v>
+        <v>179.32</v>
       </c>
       <c r="L23" t="n">
-        <v>270.84</v>
+        <v>179.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:53:27</t>
+          <t>04:52:48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.47</v>
+        <v>3.79</v>
       </c>
       <c r="F24" t="n">
-        <v>13.73</v>
+        <v>10.94</v>
       </c>
       <c r="G24" t="n">
-        <v>359.4</v>
+        <v>23.5</v>
       </c>
       <c r="H24" t="n">
-        <v>87.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>-197.31</v>
+        <v>152.03</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.63</v>
+        <v>61.69</v>
       </c>
       <c r="L24" t="n">
-        <v>197.31</v>
+        <v>164.07</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:54:17</t>
+          <t>04:54:29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.24</v>
+        <v>4.31</v>
       </c>
       <c r="F25" t="n">
-        <v>14.64</v>
+        <v>9.49</v>
       </c>
       <c r="G25" t="n">
-        <v>13.1</v>
+        <v>357.1</v>
       </c>
       <c r="H25" t="n">
-        <v>84.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>148.24</v>
+        <v>-111.86</v>
       </c>
       <c r="K25" t="n">
-        <v>12.51</v>
+        <v>143.37</v>
       </c>
       <c r="L25" t="n">
-        <v>148.77</v>
+        <v>181.85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>04:59:53</t>
+          <t>04:59:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.33</v>
+        <v>5.19</v>
       </c>
       <c r="F26" t="n">
-        <v>14.33</v>
+        <v>15.16</v>
       </c>
       <c r="G26" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="H26" t="n">
-        <v>78.5</v>
+        <v>84.8</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>-249.19</v>
+        <v>-86.20999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-96.98</v>
+        <v>644.37</v>
       </c>
       <c r="L26" t="n">
-        <v>267.39</v>
+        <v>650.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:00:43</t>
+          <t>04:59:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.31</v>
+        <v>4.47</v>
       </c>
       <c r="F27" t="n">
-        <v>13.78</v>
+        <v>15.1</v>
       </c>
       <c r="G27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H27" t="n">
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="I27" t="n">
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-70.09999999999999</v>
+        <v>-271.14</v>
       </c>
       <c r="K27" t="n">
-        <v>478.85</v>
+        <v>-296.13</v>
       </c>
       <c r="L27" t="n">
-        <v>483.95</v>
+        <v>401.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:02:59</t>
+          <t>05:01:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.48</v>
+        <v>4.31</v>
       </c>
       <c r="F28" t="n">
-        <v>13.92</v>
+        <v>14.08</v>
       </c>
       <c r="G28" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>89.5</v>
+        <v>81.2</v>
       </c>
       <c r="I28" t="n">
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-61.05</v>
+        <v>-76.27</v>
       </c>
       <c r="K28" t="n">
-        <v>-294.02</v>
+        <v>324.27</v>
       </c>
       <c r="L28" t="n">
-        <v>300.29</v>
+        <v>333.12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:14:15</t>
+          <t>05:14:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.81</v>
+        <v>4.21</v>
       </c>
       <c r="F29" t="n">
-        <v>14.21</v>
+        <v>13.67</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="H29" t="n">
-        <v>81.2</v>
+        <v>88</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>66.59999999999999</v>
+        <v>20.61</v>
       </c>
       <c r="K29" t="n">
-        <v>4.79</v>
+        <v>111.99</v>
       </c>
       <c r="L29" t="n">
-        <v>66.77</v>
+        <v>113.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:16:36</t>
+          <t>05:16:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.04</v>
+        <v>3.18</v>
       </c>
       <c r="F30" t="n">
-        <v>13.79</v>
+        <v>6.46</v>
       </c>
       <c r="G30" t="n">
-        <v>15.2</v>
+        <v>9.4</v>
       </c>
       <c r="H30" t="n">
-        <v>86.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>18.22</v>
+        <v>11.79</v>
       </c>
       <c r="K30" t="n">
-        <v>97.22</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>98.91</v>
+        <v>77.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:17:27</t>
+          <t>05:17:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.19</v>
+        <v>4.73</v>
       </c>
       <c r="F31" t="n">
-        <v>14.2</v>
+        <v>15.84</v>
       </c>
       <c r="G31" t="n">
-        <v>9.4</v>
+        <v>359.2</v>
       </c>
       <c r="H31" t="n">
-        <v>84.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>68.17</v>
+        <v>-16</v>
       </c>
       <c r="K31" t="n">
-        <v>58.88</v>
+        <v>-125.55</v>
       </c>
       <c r="L31" t="n">
-        <v>90.08</v>
+        <v>126.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:21:28</t>
+          <t>05:22:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.13</v>
+        <v>4.47</v>
       </c>
       <c r="F32" t="n">
-        <v>13.42</v>
+        <v>12.55</v>
       </c>
       <c r="G32" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
       <c r="H32" t="n">
-        <v>83.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-15.35</v>
+        <v>112.29</v>
       </c>
       <c r="K32" t="n">
-        <v>-123.05</v>
+        <v>54.33</v>
       </c>
       <c r="L32" t="n">
-        <v>124</v>
+        <v>124.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:23:52</t>
+          <t>05:24:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.47</v>
+        <v>4.34</v>
       </c>
       <c r="F33" t="n">
-        <v>14.99</v>
+        <v>13.18</v>
       </c>
       <c r="G33" t="n">
-        <v>6.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>83.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>77.61</v>
+        <v>-75.33</v>
       </c>
       <c r="K33" t="n">
-        <v>32.59</v>
+        <v>31</v>
       </c>
       <c r="L33" t="n">
-        <v>84.17</v>
+        <v>81.45999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:26:06</t>
+          <t>05:26:42</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.74</v>
+        <v>3.81</v>
       </c>
       <c r="F34" t="n">
-        <v>13.95</v>
+        <v>6.54</v>
       </c>
       <c r="G34" t="n">
-        <v>13.3</v>
+        <v>14.7</v>
       </c>
       <c r="H34" t="n">
-        <v>88.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-66.63</v>
+        <v>-78.11</v>
       </c>
       <c r="K34" t="n">
-        <v>18.87</v>
+        <v>38.54</v>
       </c>
       <c r="L34" t="n">
-        <v>69.25</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:29:47</t>
+          <t>05:31:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.82</v>
+        <v>4.26</v>
       </c>
       <c r="F35" t="n">
-        <v>14.33</v>
+        <v>11.36</v>
       </c>
       <c r="G35" t="n">
-        <v>14.7</v>
+        <v>3.1</v>
       </c>
       <c r="H35" t="n">
-        <v>86.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I35" t="n">
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>102.07</v>
+        <v>21.7</v>
       </c>
       <c r="K35" t="n">
-        <v>19.86</v>
+        <v>-164.15</v>
       </c>
       <c r="L35" t="n">
-        <v>103.99</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:30:58</t>
+          <t>05:32:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.59</v>
+        <v>4.04</v>
       </c>
       <c r="F36" t="n">
-        <v>13.61</v>
+        <v>14.51</v>
       </c>
       <c r="G36" t="n">
-        <v>356.4</v>
+        <v>12.7</v>
       </c>
       <c r="H36" t="n">
-        <v>83.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I36" t="n">
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>18.38</v>
+        <v>-73.72</v>
       </c>
       <c r="K36" t="n">
-        <v>-173.09</v>
+        <v>-119.69</v>
       </c>
       <c r="L36" t="n">
-        <v>174.06</v>
+        <v>140.58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:33:22</t>
+          <t>05:34:41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.04</v>
+        <v>3.81</v>
       </c>
       <c r="F37" t="n">
-        <v>13.68</v>
+        <v>13.18</v>
       </c>
       <c r="G37" t="n">
-        <v>12.7</v>
+        <v>10.5</v>
       </c>
       <c r="H37" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-90.93000000000001</v>
+        <v>-6.09</v>
       </c>
       <c r="K37" t="n">
-        <v>-100.67</v>
+        <v>115.64</v>
       </c>
       <c r="L37" t="n">
-        <v>135.66</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:37:46</t>
+          <t>05:38:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="F38" t="n">
-        <v>13.98</v>
+        <v>13.18</v>
       </c>
       <c r="G38" t="n">
-        <v>1.5</v>
+        <v>13.6</v>
       </c>
       <c r="H38" t="n">
-        <v>81.8</v>
+        <v>84.2</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-20.92</v>
+        <v>152.54</v>
       </c>
       <c r="K38" t="n">
-        <v>131.49</v>
+        <v>-159.23</v>
       </c>
       <c r="L38" t="n">
-        <v>133.15</v>
+        <v>220.51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:39:35</t>
+          <t>05:40:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.84</v>
+        <v>4.24</v>
       </c>
       <c r="F39" t="n">
-        <v>14.39</v>
+        <v>13.52</v>
       </c>
       <c r="G39" t="n">
-        <v>13.6</v>
+        <v>3.9</v>
       </c>
       <c r="H39" t="n">
-        <v>84.2</v>
+        <v>78.2</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-181.34</v>
+        <v>-191.25</v>
       </c>
       <c r="K39" t="n">
-        <v>2.89</v>
+        <v>163.09</v>
       </c>
       <c r="L39" t="n">
-        <v>181.36</v>
+        <v>251.35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:40:43</t>
+          <t>05:42:20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.76</v>
+        <v>4.25</v>
       </c>
       <c r="F40" t="n">
-        <v>13.65</v>
+        <v>11.56</v>
       </c>
       <c r="G40" t="n">
-        <v>355.7</v>
+        <v>7.8</v>
       </c>
       <c r="H40" t="n">
-        <v>85.5</v>
+        <v>83.7</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-192.46</v>
+        <v>110.18</v>
       </c>
       <c r="K40" t="n">
-        <v>129.58</v>
+        <v>-168.77</v>
       </c>
       <c r="L40" t="n">
-        <v>232.01</v>
+        <v>201.55</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:45:04</t>
+          <t>05:46:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.26</v>
+        <v>3.66</v>
       </c>
       <c r="F41" t="n">
-        <v>14.47</v>
+        <v>11.11</v>
       </c>
       <c r="G41" t="n">
-        <v>7.8</v>
+        <v>23.1</v>
       </c>
       <c r="H41" t="n">
-        <v>83.7</v>
+        <v>91.7</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-252.89</v>
+        <v>227.72</v>
       </c>
       <c r="K41" t="n">
-        <v>-242.43</v>
+        <v>165.57</v>
       </c>
       <c r="L41" t="n">
-        <v>350.32</v>
+        <v>281.55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:45:57</t>
+          <t>05:48:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="F42" t="n">
-        <v>14.61</v>
+        <v>11.69</v>
       </c>
       <c r="G42" t="n">
-        <v>22.6</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>88.8</v>
+        <v>78.8</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>229.71</v>
+        <v>45.02</v>
       </c>
       <c r="K42" t="n">
-        <v>139.67</v>
+        <v>325.11</v>
       </c>
       <c r="L42" t="n">
-        <v>268.84</v>
+        <v>328.21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:48:11</t>
+          <t>05:49:31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.84</v>
+        <v>4.33</v>
       </c>
       <c r="F43" t="n">
-        <v>13.63</v>
+        <v>9.09</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="H43" t="n">
-        <v>78.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>271.67</v>
+        <v>-274.85</v>
       </c>
       <c r="K43" t="n">
-        <v>42.56</v>
+        <v>-67.77</v>
       </c>
       <c r="L43" t="n">
-        <v>274.98</v>
+        <v>283.08</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:00:11</t>
+          <t>05:59:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.13</v>
+        <v>4.26</v>
       </c>
       <c r="F44" t="n">
-        <v>13.68</v>
+        <v>13.77</v>
       </c>
       <c r="G44" t="n">
-        <v>9</v>
+        <v>17.2</v>
       </c>
       <c r="H44" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-72.64</v>
+        <v>-20.87</v>
       </c>
       <c r="K44" t="n">
-        <v>-40.1</v>
+        <v>-60.51</v>
       </c>
       <c r="L44" t="n">
-        <v>82.97</v>
+        <v>64.01000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:02:17</t>
+          <t>05:59:56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.27</v>
+        <v>4.57</v>
       </c>
       <c r="F45" t="n">
-        <v>14.1</v>
+        <v>13.78</v>
       </c>
       <c r="G45" t="n">
-        <v>17.2</v>
+        <v>11.3</v>
       </c>
       <c r="H45" t="n">
-        <v>86.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I45" t="n">
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-38.64</v>
+        <v>83.92</v>
       </c>
       <c r="K45" t="n">
-        <v>56.74</v>
+        <v>-64.67</v>
       </c>
       <c r="L45" t="n">
-        <v>68.65000000000001</v>
+        <v>105.95</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:03:09</t>
+          <t>06:01:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.3</v>
+        <v>5.19</v>
       </c>
       <c r="F46" t="n">
-        <v>14.02</v>
+        <v>15.98</v>
       </c>
       <c r="G46" t="n">
-        <v>9.9</v>
+        <v>21.2</v>
       </c>
       <c r="H46" t="n">
-        <v>86.8</v>
+        <v>84.8</v>
       </c>
       <c r="I46" t="n">
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>80.40000000000001</v>
+        <v>74.56</v>
       </c>
       <c r="K46" t="n">
-        <v>-63.8</v>
+        <v>-54.65</v>
       </c>
       <c r="L46" t="n">
-        <v>102.64</v>
+        <v>92.45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:08:17</t>
+          <t>06:05:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.21</v>
+        <v>4.57</v>
       </c>
       <c r="F47" t="n">
-        <v>13.83</v>
+        <v>13.77</v>
       </c>
       <c r="G47" t="n">
-        <v>21.2</v>
+        <v>3.4</v>
       </c>
       <c r="H47" t="n">
-        <v>84.8</v>
+        <v>88.3</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-79.20999999999999</v>
+        <v>-114.32</v>
       </c>
       <c r="K47" t="n">
-        <v>52.36</v>
+        <v>28.84</v>
       </c>
       <c r="L47" t="n">
-        <v>94.95</v>
+        <v>117.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:10:14</t>
+          <t>06:07:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.99</v>
+        <v>4.52</v>
       </c>
       <c r="F48" t="n">
-        <v>13.63</v>
+        <v>12.65</v>
       </c>
       <c r="G48" t="n">
-        <v>15.8</v>
+        <v>4.3</v>
       </c>
       <c r="H48" t="n">
-        <v>84.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-102.32</v>
+        <v>-89.20999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>20.95</v>
+        <v>-5.04</v>
       </c>
       <c r="L48" t="n">
-        <v>104.44</v>
+        <v>89.34999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:11:09</t>
+          <t>06:07:55</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.54</v>
+        <v>4.1</v>
       </c>
       <c r="F49" t="n">
-        <v>14.65</v>
+        <v>9.76</v>
       </c>
       <c r="G49" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="H49" t="n">
-        <v>85.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>-17.83</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-75.33</v>
+        <v>27.23</v>
       </c>
       <c r="L49" t="n">
-        <v>77.41</v>
+        <v>73.03</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:15:45</t>
+          <t>06:12:49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.07</v>
+        <v>4.43</v>
       </c>
       <c r="F50" t="n">
-        <v>13.58</v>
+        <v>14.17</v>
       </c>
       <c r="G50" t="n">
-        <v>3.4</v>
+        <v>9.4</v>
       </c>
       <c r="H50" t="n">
-        <v>87.5</v>
+        <v>82.2</v>
       </c>
       <c r="I50" t="n">
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>99.81999999999999</v>
+        <v>-146.17</v>
       </c>
       <c r="K50" t="n">
-        <v>39.14</v>
+        <v>204.3</v>
       </c>
       <c r="L50" t="n">
-        <v>107.22</v>
+        <v>251.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:16:52</t>
+          <t>06:15:02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.44</v>
+        <v>4.68</v>
       </c>
       <c r="F51" t="n">
-        <v>13.84</v>
+        <v>14.76</v>
       </c>
       <c r="G51" t="n">
-        <v>9.4</v>
+        <v>11.6</v>
       </c>
       <c r="H51" t="n">
-        <v>82.2</v>
+        <v>89.3</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>186.79</v>
+        <v>-60.63</v>
       </c>
       <c r="K51" t="n">
-        <v>62.3</v>
+        <v>-187.23</v>
       </c>
       <c r="L51" t="n">
-        <v>196.91</v>
+        <v>196.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:18:51</t>
+          <t>06:17:11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.52</v>
+        <v>4.27</v>
       </c>
       <c r="F52" t="n">
-        <v>14.04</v>
+        <v>14.08</v>
       </c>
       <c r="G52" t="n">
-        <v>17.9</v>
+        <v>4.7</v>
       </c>
       <c r="H52" t="n">
-        <v>93</v>
+        <v>87.3</v>
       </c>
       <c r="I52" t="n">
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-56.91</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-187.09</v>
+        <v>-197.35</v>
       </c>
       <c r="L52" t="n">
-        <v>195.56</v>
+        <v>214.85</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:22:13</t>
+          <t>06:22:06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.29</v>
+        <v>4.59</v>
       </c>
       <c r="F53" t="n">
-        <v>14.12</v>
+        <v>13.38</v>
       </c>
       <c r="G53" t="n">
-        <v>4.7</v>
+        <v>354.3</v>
       </c>
       <c r="H53" t="n">
-        <v>87.3</v>
+        <v>81.5</v>
       </c>
       <c r="I53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-268.45</v>
+        <v>-179.33</v>
       </c>
       <c r="K53" t="n">
-        <v>56.05</v>
+        <v>188.57</v>
       </c>
       <c r="L53" t="n">
-        <v>274.24</v>
+        <v>260.22</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:23:03</t>
+          <t>06:23:26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.47</v>
+        <v>4.8</v>
       </c>
       <c r="F54" t="n">
-        <v>13.65</v>
+        <v>15.98</v>
       </c>
       <c r="G54" t="n">
-        <v>354.3</v>
+        <v>9.4</v>
       </c>
       <c r="H54" t="n">
-        <v>81.5</v>
+        <v>82.5</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>230.33</v>
+        <v>127.99</v>
       </c>
       <c r="K54" t="n">
-        <v>258.03</v>
+        <v>192.27</v>
       </c>
       <c r="L54" t="n">
-        <v>345.88</v>
+        <v>230.98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:25:16</t>
+          <t>06:25:38</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.61</v>
+        <v>4.12</v>
       </c>
       <c r="F55" t="n">
-        <v>14.13</v>
+        <v>10.67</v>
       </c>
       <c r="G55" t="n">
-        <v>26.4</v>
+        <v>16.1</v>
       </c>
       <c r="H55" t="n">
-        <v>85.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I55" t="n">
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-168.2</v>
+        <v>-179.9</v>
       </c>
       <c r="K55" t="n">
-        <v>-64.20999999999999</v>
+        <v>184.03</v>
       </c>
       <c r="L55" t="n">
-        <v>180.04</v>
+        <v>257.35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:30:31</t>
+          <t>06:29:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.03</v>
+        <v>4.36</v>
       </c>
       <c r="F56" t="n">
-        <v>14.13</v>
+        <v>13.95</v>
       </c>
       <c r="G56" t="n">
-        <v>16.1</v>
+        <v>7.2</v>
       </c>
       <c r="H56" t="n">
-        <v>78.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I56" t="n">
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>282.03</v>
+        <v>-230.85</v>
       </c>
       <c r="K56" t="n">
-        <v>-16.03</v>
+        <v>-220.42</v>
       </c>
       <c r="L56" t="n">
-        <v>282.48</v>
+        <v>319.18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:31:26</t>
+          <t>06:30:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.9</v>
+        <v>4.84</v>
       </c>
       <c r="F57" t="n">
-        <v>13.55</v>
+        <v>15.23</v>
       </c>
       <c r="G57" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="H57" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>222.57</v>
+        <v>387.44</v>
       </c>
       <c r="K57" t="n">
-        <v>141.33</v>
+        <v>287.48</v>
       </c>
       <c r="L57" t="n">
-        <v>263.65</v>
+        <v>482.44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:32:47</t>
+          <t>06:31:34</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.6</v>
+        <v>4.23</v>
       </c>
       <c r="F58" t="n">
-        <v>13.6</v>
+        <v>9.76</v>
       </c>
       <c r="G58" t="n">
-        <v>2.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>85</v>
+        <v>82.3</v>
       </c>
       <c r="I58" t="n">
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>294.46</v>
+        <v>73.97</v>
       </c>
       <c r="K58" t="n">
-        <v>-110.19</v>
+        <v>249.82</v>
       </c>
       <c r="L58" t="n">
-        <v>314.4</v>
+        <v>260.54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:44:22</t>
+          <t>06:41:43</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.86</v>
+        <v>4.06</v>
       </c>
       <c r="F59" t="n">
-        <v>13.96</v>
+        <v>12.08</v>
       </c>
       <c r="G59" t="n">
-        <v>9.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="H59" t="n">
-        <v>85.2</v>
+        <v>82.2</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-55.72</v>
+        <v>-59.32</v>
       </c>
       <c r="K59" t="n">
-        <v>82.8</v>
+        <v>-64.48999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>99.81</v>
+        <v>87.62</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:45:53</t>
+          <t>06:42:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.45</v>
+        <v>4.14</v>
       </c>
       <c r="F60" t="n">
-        <v>14.73</v>
+        <v>11.73</v>
       </c>
       <c r="G60" t="n">
-        <v>11.3</v>
+        <v>8.4</v>
       </c>
       <c r="H60" t="n">
-        <v>82.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-67.38</v>
+        <v>-23.13</v>
       </c>
       <c r="K60" t="n">
-        <v>-50.56</v>
+        <v>-7.12</v>
       </c>
       <c r="L60" t="n">
-        <v>84.23999999999999</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:47:57</t>
+          <t>06:44:25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.39</v>
+        <v>4.68</v>
       </c>
       <c r="F61" t="n">
-        <v>13.84</v>
+        <v>15.98</v>
       </c>
       <c r="G61" t="n">
-        <v>21.3</v>
+        <v>0.9</v>
       </c>
       <c r="H61" t="n">
-        <v>84.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I61" t="n">
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>32.99</v>
+        <v>-65.73</v>
       </c>
       <c r="K61" t="n">
-        <v>63.05</v>
+        <v>-63.52</v>
       </c>
       <c r="L61" t="n">
-        <v>71.16</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:52:02</t>
+          <t>06:49:42</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.17</v>
+        <v>4.63</v>
       </c>
       <c r="F62" t="n">
-        <v>14.2</v>
+        <v>15.58</v>
       </c>
       <c r="G62" t="n">
         <v>0.9</v>
       </c>
       <c r="H62" t="n">
-        <v>84.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-88.02</v>
+        <v>-12.83</v>
       </c>
       <c r="K62" t="n">
-        <v>25.84</v>
+        <v>-40.89</v>
       </c>
       <c r="L62" t="n">
-        <v>91.73</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:53:25</t>
+          <t>06:50:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="F63" t="n">
-        <v>13.88</v>
+        <v>13.39</v>
       </c>
       <c r="G63" t="n">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="H63" t="n">
-        <v>80.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>71.23999999999999</v>
+        <v>-83.84999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.76</v>
+        <v>-83.79000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>85.76000000000001</v>
+        <v>118.54</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:54:29</t>
+          <t>06:53:16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.23</v>
+        <v>4.99</v>
       </c>
       <c r="F64" t="n">
-        <v>13.64</v>
+        <v>13.87</v>
       </c>
       <c r="G64" t="n">
-        <v>3.5</v>
+        <v>11.3</v>
       </c>
       <c r="H64" t="n">
-        <v>86.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-86.92</v>
+        <v>-97.93000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>72.03</v>
+        <v>37.8</v>
       </c>
       <c r="L64" t="n">
-        <v>112.89</v>
+        <v>104.97</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06:58:45</t>
+          <t>06:56:55</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.88</v>
+        <v>5.4</v>
       </c>
       <c r="F65" t="n">
-        <v>13.41</v>
+        <v>15.98</v>
       </c>
       <c r="G65" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="H65" t="n">
-        <v>86</v>
+        <v>88.5</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>190.51</v>
+        <v>-136.92</v>
       </c>
       <c r="K65" t="n">
-        <v>13.59</v>
+        <v>93.25</v>
       </c>
       <c r="L65" t="n">
-        <v>191</v>
+        <v>165.66</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:00:28</t>
+          <t>06:58:39</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.03</v>
+        <v>5.06</v>
       </c>
       <c r="F66" t="n">
-        <v>12.94</v>
+        <v>15.69</v>
       </c>
       <c r="G66" t="n">
-        <v>7.6</v>
+        <v>21.3</v>
       </c>
       <c r="H66" t="n">
-        <v>88.5</v>
+        <v>82.5</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>18.9</v>
+        <v>-73.45999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>153.23</v>
+        <v>-159.97</v>
       </c>
       <c r="L66" t="n">
-        <v>154.39</v>
+        <v>176.03</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:01:25</t>
+          <t>06:59:57</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.52</v>
+        <v>3.78</v>
       </c>
       <c r="F67" t="n">
-        <v>13.63</v>
+        <v>11.94</v>
       </c>
       <c r="G67" t="n">
-        <v>20.8</v>
+        <v>359</v>
       </c>
       <c r="H67" t="n">
-        <v>91</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-167.89</v>
+        <v>-53.74</v>
       </c>
       <c r="K67" t="n">
-        <v>67.19</v>
+        <v>-118.08</v>
       </c>
       <c r="L67" t="n">
-        <v>180.83</v>
+        <v>129.74</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:07:37</t>
+          <t>07:04:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.67</v>
+        <v>4.44</v>
       </c>
       <c r="F68" t="n">
-        <v>14.22</v>
+        <v>14.44</v>
       </c>
       <c r="G68" t="n">
-        <v>359</v>
+        <v>17.7</v>
       </c>
       <c r="H68" t="n">
-        <v>85.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-198.71</v>
+        <v>-30.63</v>
       </c>
       <c r="K68" t="n">
-        <v>-35.66</v>
+        <v>-87.61</v>
       </c>
       <c r="L68" t="n">
-        <v>201.88</v>
+        <v>92.81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:08:37</t>
+          <t>07:07:18</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.43</v>
+        <v>3.82</v>
       </c>
       <c r="F69" t="n">
-        <v>13.83</v>
+        <v>10.29</v>
       </c>
       <c r="G69" t="n">
-        <v>10.1</v>
+        <v>14.8</v>
       </c>
       <c r="H69" t="n">
-        <v>89.3</v>
+        <v>84</v>
       </c>
       <c r="I69" t="n">
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-227.5</v>
+        <v>-91.95999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>18.55</v>
+        <v>158.64</v>
       </c>
       <c r="L69" t="n">
-        <v>228.26</v>
+        <v>183.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:10:21</t>
+          <t>07:09:53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.24</v>
+        <v>4.74</v>
       </c>
       <c r="F70" t="n">
-        <v>13.71</v>
+        <v>14.56</v>
       </c>
       <c r="G70" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="H70" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>136.45</v>
+        <v>-27.35</v>
       </c>
       <c r="K70" t="n">
-        <v>90.78</v>
+        <v>238.78</v>
       </c>
       <c r="L70" t="n">
-        <v>163.89</v>
+        <v>240.34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:14:31</t>
+          <t>07:13:06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.49</v>
+        <v>4.18</v>
       </c>
       <c r="F71" t="n">
-        <v>14.31</v>
+        <v>12.76</v>
       </c>
       <c r="G71" t="n">
-        <v>6.7</v>
+        <v>19.1</v>
       </c>
       <c r="H71" t="n">
-        <v>76.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-479.06</v>
+        <v>-349.95</v>
       </c>
       <c r="K71" t="n">
-        <v>31.54</v>
+        <v>-1.17</v>
       </c>
       <c r="L71" t="n">
-        <v>480.1</v>
+        <v>349.95</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:16:46</t>
+          <t>07:15:11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.87</v>
+        <v>3.62</v>
       </c>
       <c r="F72" t="n">
-        <v>13.13</v>
+        <v>11.01</v>
       </c>
       <c r="G72" t="n">
-        <v>23.5</v>
+        <v>5</v>
       </c>
       <c r="H72" t="n">
-        <v>90</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-423.87</v>
+        <v>-234.66</v>
       </c>
       <c r="K72" t="n">
-        <v>170.78</v>
+        <v>-214.26</v>
       </c>
       <c r="L72" t="n">
-        <v>456.98</v>
+        <v>317.76</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:19:29</t>
+          <t>07:17:33</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.35</v>
+        <v>3.63</v>
       </c>
       <c r="F73" t="n">
-        <v>12.99</v>
+        <v>13.24</v>
       </c>
       <c r="G73" t="n">
-        <v>356.2</v>
+        <v>15.5</v>
       </c>
       <c r="H73" t="n">
-        <v>79.5</v>
+        <v>79.7</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>259.18</v>
+        <v>-39.63</v>
       </c>
       <c r="K73" t="n">
-        <v>-20.3</v>
+        <v>-251.55</v>
       </c>
       <c r="L73" t="n">
-        <v>259.97</v>
+        <v>254.66</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:29:21</t>
+          <t>07:29:51</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.11</v>
+        <v>5.24</v>
       </c>
       <c r="F74" t="n">
-        <v>13.42</v>
+        <v>15.77</v>
       </c>
       <c r="G74" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="H74" t="n">
-        <v>95.8</v>
+        <v>74.2</v>
       </c>
       <c r="I74" t="n">
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-78.27</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>-23.34</v>
+        <v>-59.58</v>
       </c>
       <c r="L74" t="n">
-        <v>81.68000000000001</v>
+        <v>102.16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:30:36</t>
+          <t>07:30:40</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.51</v>
+        <v>5.03</v>
       </c>
       <c r="F75" t="n">
-        <v>14.21</v>
+        <v>15.98</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="H75" t="n">
-        <v>89.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>12.71</v>
+        <v>29.6</v>
       </c>
       <c r="K75" t="n">
-        <v>55.37</v>
+        <v>-106.01</v>
       </c>
       <c r="L75" t="n">
-        <v>56.81</v>
+        <v>110.06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:31:43</t>
+          <t>07:32:23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.67</v>
+        <v>6.37</v>
       </c>
       <c r="F76" t="n">
-        <v>13.14</v>
+        <v>15.98</v>
       </c>
       <c r="G76" t="n">
-        <v>12.9</v>
+        <v>7.4</v>
       </c>
       <c r="H76" t="n">
-        <v>81.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I76" t="n">
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>24.35</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-53.01</v>
+        <v>0.54</v>
       </c>
       <c r="L76" t="n">
-        <v>58.34</v>
+        <v>73.93000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:36:46</t>
+          <t>07:38:03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.82</v>
+        <v>4.79</v>
       </c>
       <c r="F77" t="n">
-        <v>13.87</v>
+        <v>13.61</v>
       </c>
       <c r="G77" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="H77" t="n">
-        <v>80.3</v>
+        <v>78.2</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>95.48999999999999</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-47.65</v>
+        <v>27</v>
       </c>
       <c r="L77" t="n">
-        <v>106.72</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:39:09</t>
+          <t>07:39:10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="F78" t="n">
-        <v>13.91</v>
+        <v>15.98</v>
       </c>
       <c r="G78" t="n">
-        <v>8.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="H78" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>-30.76</v>
+        <v>102.17</v>
       </c>
       <c r="K78" t="n">
-        <v>137.86</v>
+        <v>-1.09</v>
       </c>
       <c r="L78" t="n">
-        <v>141.24</v>
+        <v>102.18</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:39:58</t>
+          <t>07:41:33</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.73</v>
+        <v>4.92</v>
       </c>
       <c r="F79" t="n">
-        <v>14.08</v>
+        <v>15.33</v>
       </c>
       <c r="G79" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="H79" t="n">
-        <v>88.3</v>
+        <v>75.5</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>-12.46</v>
+        <v>-76.68000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-80.34999999999999</v>
+        <v>106.83</v>
       </c>
       <c r="L79" t="n">
-        <v>81.31</v>
+        <v>131.51</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:44:20</t>
+          <t>07:45:56</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.69</v>
+        <v>5.17</v>
       </c>
       <c r="F80" t="n">
-        <v>14.48</v>
+        <v>15.98</v>
       </c>
       <c r="G80" t="n">
-        <v>359.7</v>
+        <v>11.7</v>
       </c>
       <c r="H80" t="n">
-        <v>82.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I80" t="n">
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-162.89</v>
+        <v>-67.72</v>
       </c>
       <c r="K80" t="n">
-        <v>21.76</v>
+        <v>181.9</v>
       </c>
       <c r="L80" t="n">
-        <v>164.33</v>
+        <v>194.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:46:43</t>
+          <t>07:47:28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="F81" t="n">
-        <v>14.5</v>
+        <v>15.73</v>
       </c>
       <c r="G81" t="n">
-        <v>15.4</v>
+        <v>16.2</v>
       </c>
       <c r="H81" t="n">
-        <v>88.7</v>
+        <v>88.5</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-149.46</v>
+        <v>-113.06</v>
       </c>
       <c r="K81" t="n">
-        <v>109.5</v>
+        <v>-132.57</v>
       </c>
       <c r="L81" t="n">
-        <v>185.27</v>
+        <v>174.23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:47:50</t>
+          <t>07:48:59</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.15</v>
+        <v>4.98</v>
       </c>
       <c r="F82" t="n">
-        <v>14.11</v>
+        <v>15.19</v>
       </c>
       <c r="G82" t="n">
-        <v>0.2</v>
+        <v>25.8</v>
       </c>
       <c r="H82" t="n">
-        <v>81.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I82" t="n">
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-26.06</v>
+        <v>-112.01</v>
       </c>
       <c r="K82" t="n">
-        <v>257.01</v>
+        <v>-94.55</v>
       </c>
       <c r="L82" t="n">
-        <v>258.33</v>
+        <v>146.58</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:52:39</t>
+          <t>07:54:07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.7</v>
+        <v>5.08</v>
       </c>
       <c r="F83" t="n">
-        <v>14.5</v>
+        <v>15.17</v>
       </c>
       <c r="G83" t="n">
-        <v>14.5</v>
+        <v>357.7</v>
       </c>
       <c r="H83" t="n">
-        <v>81.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-150.26</v>
+        <v>-216.18</v>
       </c>
       <c r="K83" t="n">
-        <v>108.38</v>
+        <v>171.51</v>
       </c>
       <c r="L83" t="n">
-        <v>185.27</v>
+        <v>275.96</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:54:33</t>
+          <t>07:56:32</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.14</v>
+        <v>4.89</v>
       </c>
       <c r="F84" t="n">
-        <v>14.01</v>
+        <v>12.33</v>
       </c>
       <c r="G84" t="n">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="H84" t="n">
-        <v>80.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="I84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-193.65</v>
+        <v>-114.66</v>
       </c>
       <c r="K84" t="n">
-        <v>-155.63</v>
+        <v>225.51</v>
       </c>
       <c r="L84" t="n">
-        <v>248.44</v>
+        <v>252.99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:56:05</t>
+          <t>07:58:25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.97</v>
+        <v>4.53</v>
       </c>
       <c r="F85" t="n">
-        <v>13.73</v>
+        <v>13.93</v>
       </c>
       <c r="G85" t="n">
-        <v>4.4</v>
+        <v>359.1</v>
       </c>
       <c r="H85" t="n">
-        <v>88.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-38.94</v>
+        <v>133.45</v>
       </c>
       <c r="K85" t="n">
-        <v>192.76</v>
+        <v>292.36</v>
       </c>
       <c r="L85" t="n">
-        <v>196.66</v>
+        <v>321.38</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07:59:55</t>
+          <t>08:02:09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="F86" t="n">
-        <v>13.36</v>
+        <v>12.95</v>
       </c>
       <c r="G86" t="n">
-        <v>25.9</v>
+        <v>2.5</v>
       </c>
       <c r="H86" t="n">
-        <v>89.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-48.49</v>
+        <v>117.46</v>
       </c>
       <c r="K86" t="n">
-        <v>43.61</v>
+        <v>475.47</v>
       </c>
       <c r="L86" t="n">
-        <v>65.20999999999999</v>
+        <v>489.76</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:01:56</t>
+          <t>08:04:33</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.43</v>
+        <v>4.2</v>
       </c>
       <c r="F87" t="n">
-        <v>13.2</v>
+        <v>15.98</v>
       </c>
       <c r="G87" t="n">
-        <v>358.2</v>
+        <v>10.3</v>
       </c>
       <c r="H87" t="n">
-        <v>94.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-250.29</v>
+        <v>222.23</v>
       </c>
       <c r="K87" t="n">
-        <v>55.25</v>
+        <v>155.62</v>
       </c>
       <c r="L87" t="n">
-        <v>256.31</v>
+        <v>271.3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:04:21</t>
+          <t>08:05:23</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.59</v>
+        <v>5.27</v>
       </c>
       <c r="F88" t="n">
-        <v>13.87</v>
+        <v>15.98</v>
       </c>
       <c r="G88" t="n">
-        <v>11.8</v>
+        <v>21.6</v>
       </c>
       <c r="H88" t="n">
-        <v>79.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>210.97</v>
+        <v>-231.33</v>
       </c>
       <c r="K88" t="n">
-        <v>271.3</v>
+        <v>-262.17</v>
       </c>
       <c r="L88" t="n">
-        <v>343.67</v>
+        <v>349.64</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>19.53</v>
+        <v>21.24</v>
       </c>
       <c r="K14" t="n">
-        <v>-74.67</v>
+        <v>-81.2</v>
       </c>
       <c r="L14" t="n">
-        <v>77.19</v>
+        <v>83.93000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>66.11</v>
+        <v>73.03</v>
       </c>
       <c r="K15" t="n">
-        <v>-59.87</v>
+        <v>-66.14</v>
       </c>
       <c r="L15" t="n">
-        <v>89.2</v>
+        <v>98.53</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="K16" t="n">
-        <v>-72.2</v>
+        <v>-79.73</v>
       </c>
       <c r="L16" t="n">
-        <v>72.2</v>
+        <v>79.73</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-26.3</v>
+        <v>-28.97</v>
       </c>
       <c r="K17" t="n">
-        <v>93.92</v>
+        <v>103.48</v>
       </c>
       <c r="L17" t="n">
-        <v>97.53</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>14.05</v>
+        <v>15.25</v>
       </c>
       <c r="K18" t="n">
-        <v>86.77</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>87.90000000000001</v>
+        <v>95.44</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>13.83</v>
+        <v>15.64</v>
       </c>
       <c r="K19" t="n">
-        <v>89.01000000000001</v>
+        <v>100.66</v>
       </c>
       <c r="L19" t="n">
-        <v>90.08</v>
+        <v>101.87</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>26.78</v>
+        <v>30.02</v>
       </c>
       <c r="K20" t="n">
-        <v>-123.19</v>
+        <v>-138.07</v>
       </c>
       <c r="L20" t="n">
-        <v>126.06</v>
+        <v>141.3</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>147.83</v>
+        <v>168.22</v>
       </c>
       <c r="K21" t="n">
-        <v>82.67</v>
+        <v>94.08</v>
       </c>
       <c r="L21" t="n">
-        <v>169.38</v>
+        <v>192.74</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-85.72</v>
+        <v>-93.36</v>
       </c>
       <c r="K22" t="n">
-        <v>-176.11</v>
+        <v>-191.81</v>
       </c>
       <c r="L22" t="n">
-        <v>195.86</v>
+        <v>213.32</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-11.5</v>
+        <v>-13.1</v>
       </c>
       <c r="K23" t="n">
-        <v>179.32</v>
+        <v>204.34</v>
       </c>
       <c r="L23" t="n">
-        <v>179.69</v>
+        <v>204.76</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>152.03</v>
+        <v>170.81</v>
       </c>
       <c r="K24" t="n">
-        <v>61.69</v>
+        <v>69.31</v>
       </c>
       <c r="L24" t="n">
-        <v>164.07</v>
+        <v>184.33</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-111.86</v>
+        <v>-127.44</v>
       </c>
       <c r="K25" t="n">
-        <v>143.37</v>
+        <v>163.35</v>
       </c>
       <c r="L25" t="n">
-        <v>181.85</v>
+        <v>207.18</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>-86.20999999999999</v>
+        <v>-100</v>
       </c>
       <c r="K26" t="n">
-        <v>644.37</v>
+        <v>747.5</v>
       </c>
       <c r="L26" t="n">
-        <v>650.11</v>
+        <v>754.16</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-271.14</v>
+        <v>-313.1</v>
       </c>
       <c r="K27" t="n">
-        <v>-296.13</v>
+        <v>-341.96</v>
       </c>
       <c r="L27" t="n">
-        <v>401.52</v>
+        <v>463.65</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-76.27</v>
+        <v>-87.95</v>
       </c>
       <c r="K28" t="n">
-        <v>324.27</v>
+        <v>373.97</v>
       </c>
       <c r="L28" t="n">
-        <v>333.12</v>
+        <v>384.17</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>20.61</v>
+        <v>23.34</v>
       </c>
       <c r="K29" t="n">
-        <v>111.99</v>
+        <v>126.85</v>
       </c>
       <c r="L29" t="n">
-        <v>113.87</v>
+        <v>128.98</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>11.79</v>
+        <v>12.86</v>
       </c>
       <c r="K30" t="n">
-        <v>76.84999999999999</v>
+        <v>83.84</v>
       </c>
       <c r="L30" t="n">
-        <v>77.75</v>
+        <v>84.81999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-16</v>
+        <v>-18.08</v>
       </c>
       <c r="K31" t="n">
-        <v>-125.55</v>
+        <v>-141.88</v>
       </c>
       <c r="L31" t="n">
-        <v>126.57</v>
+        <v>143.03</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>112.29</v>
+        <v>125.36</v>
       </c>
       <c r="K32" t="n">
-        <v>54.33</v>
+        <v>60.66</v>
       </c>
       <c r="L32" t="n">
-        <v>124.75</v>
+        <v>139.27</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-75.33</v>
+        <v>-84.14</v>
       </c>
       <c r="K33" t="n">
-        <v>31</v>
+        <v>34.63</v>
       </c>
       <c r="L33" t="n">
-        <v>81.45999999999999</v>
+        <v>90.98999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-78.11</v>
+        <v>-84.98</v>
       </c>
       <c r="K34" t="n">
-        <v>38.54</v>
+        <v>41.93</v>
       </c>
       <c r="L34" t="n">
-        <v>87.09999999999999</v>
+        <v>94.76000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>21.7</v>
+        <v>24.66</v>
       </c>
       <c r="K35" t="n">
-        <v>-164.15</v>
+        <v>-186.48</v>
       </c>
       <c r="L35" t="n">
-        <v>165.58</v>
+        <v>188.11</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-73.72</v>
+        <v>-83.78</v>
       </c>
       <c r="K36" t="n">
-        <v>-119.69</v>
+        <v>-136.02</v>
       </c>
       <c r="L36" t="n">
-        <v>140.58</v>
+        <v>159.75</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-6.09</v>
+        <v>-6.64</v>
       </c>
       <c r="K37" t="n">
-        <v>115.64</v>
+        <v>126.03</v>
       </c>
       <c r="L37" t="n">
-        <v>115.8</v>
+        <v>126.2</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>152.54</v>
+        <v>173.71</v>
       </c>
       <c r="K38" t="n">
-        <v>-159.23</v>
+        <v>-181.32</v>
       </c>
       <c r="L38" t="n">
-        <v>220.51</v>
+        <v>251.1</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-191.25</v>
+        <v>-217.88</v>
       </c>
       <c r="K39" t="n">
-        <v>163.09</v>
+        <v>185.79</v>
       </c>
       <c r="L39" t="n">
-        <v>251.35</v>
+        <v>286.34</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>110.18</v>
+        <v>125.53</v>
       </c>
       <c r="K40" t="n">
-        <v>-168.77</v>
+        <v>-192.27</v>
       </c>
       <c r="L40" t="n">
-        <v>201.55</v>
+        <v>229.61</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>227.72</v>
+        <v>249.27</v>
       </c>
       <c r="K41" t="n">
-        <v>165.57</v>
+        <v>181.23</v>
       </c>
       <c r="L41" t="n">
-        <v>281.55</v>
+        <v>308.19</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>45.02</v>
+        <v>50.79</v>
       </c>
       <c r="K42" t="n">
-        <v>325.11</v>
+        <v>366.76</v>
       </c>
       <c r="L42" t="n">
-        <v>328.21</v>
+        <v>370.26</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-274.85</v>
+        <v>-303.93</v>
       </c>
       <c r="K43" t="n">
-        <v>-67.77</v>
+        <v>-74.94</v>
       </c>
       <c r="L43" t="n">
-        <v>283.08</v>
+        <v>313.03</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-20.87</v>
+        <v>-22.66</v>
       </c>
       <c r="K44" t="n">
-        <v>-60.51</v>
+        <v>-65.69</v>
       </c>
       <c r="L44" t="n">
-        <v>64.01000000000001</v>
+        <v>69.48999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>83.92</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-64.67</v>
+        <v>-73.13</v>
       </c>
       <c r="L45" t="n">
-        <v>105.95</v>
+        <v>119.81</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>74.56</v>
+        <v>84.09</v>
       </c>
       <c r="K46" t="n">
-        <v>-54.65</v>
+        <v>-61.64</v>
       </c>
       <c r="L46" t="n">
-        <v>92.45</v>
+        <v>104.26</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-114.32</v>
+        <v>-129.29</v>
       </c>
       <c r="K47" t="n">
-        <v>28.84</v>
+        <v>32.62</v>
       </c>
       <c r="L47" t="n">
-        <v>117.9</v>
+        <v>133.34</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-89.20999999999999</v>
+        <v>-100.91</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.04</v>
+        <v>-5.7</v>
       </c>
       <c r="L48" t="n">
-        <v>89.34999999999999</v>
+        <v>101.07</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>67.76000000000001</v>
+        <v>75.77</v>
       </c>
       <c r="K49" t="n">
-        <v>27.23</v>
+        <v>30.45</v>
       </c>
       <c r="L49" t="n">
-        <v>73.03</v>
+        <v>81.66</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-146.17</v>
+        <v>-166.01</v>
       </c>
       <c r="K50" t="n">
-        <v>204.3</v>
+        <v>232.03</v>
       </c>
       <c r="L50" t="n">
-        <v>251.2</v>
+        <v>285.31</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-60.63</v>
+        <v>-68.84</v>
       </c>
       <c r="K51" t="n">
-        <v>-187.23</v>
+        <v>-212.58</v>
       </c>
       <c r="L51" t="n">
-        <v>196.8</v>
+        <v>223.45</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>84.93000000000001</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-197.35</v>
+        <v>-224.19</v>
       </c>
       <c r="L52" t="n">
-        <v>214.85</v>
+        <v>244.07</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-179.33</v>
+        <v>-205.64</v>
       </c>
       <c r="K53" t="n">
-        <v>188.57</v>
+        <v>216.23</v>
       </c>
       <c r="L53" t="n">
-        <v>260.22</v>
+        <v>298.4</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>127.99</v>
+        <v>142.9</v>
       </c>
       <c r="K54" t="n">
-        <v>192.27</v>
+        <v>214.67</v>
       </c>
       <c r="L54" t="n">
-        <v>230.98</v>
+        <v>257.88</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-179.9</v>
+        <v>-204.92</v>
       </c>
       <c r="K55" t="n">
-        <v>184.03</v>
+        <v>209.63</v>
       </c>
       <c r="L55" t="n">
-        <v>257.35</v>
+        <v>293.15</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-230.85</v>
+        <v>-259.13</v>
       </c>
       <c r="K56" t="n">
-        <v>-220.42</v>
+        <v>-247.43</v>
       </c>
       <c r="L56" t="n">
-        <v>319.18</v>
+        <v>358.29</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>387.44</v>
+        <v>436.41</v>
       </c>
       <c r="K57" t="n">
-        <v>287.48</v>
+        <v>323.82</v>
       </c>
       <c r="L57" t="n">
-        <v>482.44</v>
+        <v>543.4299999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>73.97</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>249.82</v>
+        <v>286.35</v>
       </c>
       <c r="L58" t="n">
-        <v>260.54</v>
+        <v>298.64</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-59.32</v>
+        <v>-64.45999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-64.48999999999999</v>
+        <v>-70.06999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>87.62</v>
+        <v>95.20999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-23.13</v>
+        <v>-26.21</v>
       </c>
       <c r="K60" t="n">
-        <v>-7.12</v>
+        <v>-8.07</v>
       </c>
       <c r="L60" t="n">
-        <v>24.2</v>
+        <v>27.42</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-65.73</v>
+        <v>-74.29000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-63.52</v>
+        <v>-71.8</v>
       </c>
       <c r="L61" t="n">
-        <v>91.41</v>
+        <v>103.32</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-12.83</v>
+        <v>-14.51</v>
       </c>
       <c r="K62" t="n">
-        <v>-40.89</v>
+        <v>-46.23</v>
       </c>
       <c r="L62" t="n">
-        <v>42.85</v>
+        <v>48.45</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-83.84999999999999</v>
+        <v>-94.73999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-83.79000000000001</v>
+        <v>-94.67</v>
       </c>
       <c r="L63" t="n">
-        <v>118.54</v>
+        <v>133.93</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-97.93000000000001</v>
+        <v>-105.99</v>
       </c>
       <c r="K64" t="n">
-        <v>37.8</v>
+        <v>40.91</v>
       </c>
       <c r="L64" t="n">
-        <v>104.97</v>
+        <v>113.61</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-136.92</v>
+        <v>-155.19</v>
       </c>
       <c r="K65" t="n">
-        <v>93.25</v>
+        <v>105.7</v>
       </c>
       <c r="L65" t="n">
-        <v>165.66</v>
+        <v>187.77</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-73.45999999999999</v>
+        <v>-79.86</v>
       </c>
       <c r="K66" t="n">
-        <v>-159.97</v>
+        <v>-173.9</v>
       </c>
       <c r="L66" t="n">
-        <v>176.03</v>
+        <v>191.36</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-53.74</v>
+        <v>-58.58</v>
       </c>
       <c r="K67" t="n">
-        <v>-118.08</v>
+        <v>-128.69</v>
       </c>
       <c r="L67" t="n">
-        <v>129.74</v>
+        <v>141.4</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-30.63</v>
+        <v>-34.44</v>
       </c>
       <c r="K68" t="n">
-        <v>-87.61</v>
+        <v>-98.51000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>92.81</v>
+        <v>104.35</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-91.95999999999999</v>
+        <v>-101.88</v>
       </c>
       <c r="K69" t="n">
-        <v>158.64</v>
+        <v>175.76</v>
       </c>
       <c r="L69" t="n">
-        <v>183.37</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-27.35</v>
+        <v>-31.38</v>
       </c>
       <c r="K70" t="n">
-        <v>238.78</v>
+        <v>273.95</v>
       </c>
       <c r="L70" t="n">
-        <v>240.34</v>
+        <v>275.74</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-349.95</v>
+        <v>-390.15</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.17</v>
+        <v>-1.31</v>
       </c>
       <c r="L71" t="n">
-        <v>349.95</v>
+        <v>390.15</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-234.66</v>
+        <v>-267.85</v>
       </c>
       <c r="K72" t="n">
-        <v>-214.26</v>
+        <v>-244.57</v>
       </c>
       <c r="L72" t="n">
-        <v>317.76</v>
+        <v>362.71</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-39.63</v>
+        <v>-45.24</v>
       </c>
       <c r="K73" t="n">
-        <v>-251.55</v>
+        <v>-287.16</v>
       </c>
       <c r="L73" t="n">
-        <v>254.66</v>
+        <v>290.7</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>82.98999999999999</v>
+        <v>93.58</v>
       </c>
       <c r="K74" t="n">
-        <v>-59.58</v>
+        <v>-67.18000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>102.16</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>29.6</v>
+        <v>32.51</v>
       </c>
       <c r="K75" t="n">
-        <v>-106.01</v>
+        <v>-116.4</v>
       </c>
       <c r="L75" t="n">
-        <v>110.06</v>
+        <v>120.85</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>73.93000000000001</v>
+        <v>80.22</v>
       </c>
       <c r="K76" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="L76" t="n">
-        <v>73.93000000000001</v>
+        <v>80.22</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-8.630000000000001</v>
+        <v>-9.75</v>
       </c>
       <c r="K77" t="n">
-        <v>27</v>
+        <v>30.5</v>
       </c>
       <c r="L77" t="n">
-        <v>28.34</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>102.17</v>
+        <v>113.98</v>
       </c>
       <c r="K78" t="n">
-        <v>-1.09</v>
+        <v>-1.22</v>
       </c>
       <c r="L78" t="n">
-        <v>102.18</v>
+        <v>113.99</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>-76.68000000000001</v>
+        <v>-84.26000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>106.83</v>
+        <v>117.38</v>
       </c>
       <c r="L79" t="n">
-        <v>131.51</v>
+        <v>144.49</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-67.72</v>
+        <v>-76.78</v>
       </c>
       <c r="K80" t="n">
-        <v>181.9</v>
+        <v>206.24</v>
       </c>
       <c r="L80" t="n">
-        <v>194.1</v>
+        <v>220.07</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-113.06</v>
+        <v>-128.2</v>
       </c>
       <c r="K81" t="n">
-        <v>-132.57</v>
+        <v>-150.32</v>
       </c>
       <c r="L81" t="n">
-        <v>174.23</v>
+        <v>197.56</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-112.01</v>
+        <v>-121.79</v>
       </c>
       <c r="K82" t="n">
-        <v>-94.55</v>
+        <v>-102.8</v>
       </c>
       <c r="L82" t="n">
-        <v>146.58</v>
+        <v>159.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-216.18</v>
+        <v>-248.29</v>
       </c>
       <c r="K83" t="n">
-        <v>171.51</v>
+        <v>196.98</v>
       </c>
       <c r="L83" t="n">
-        <v>275.96</v>
+        <v>316.94</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-114.66</v>
+        <v>-131.61</v>
       </c>
       <c r="K84" t="n">
-        <v>225.51</v>
+        <v>258.86</v>
       </c>
       <c r="L84" t="n">
-        <v>252.99</v>
+        <v>290.4</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>133.45</v>
+        <v>153</v>
       </c>
       <c r="K85" t="n">
-        <v>292.36</v>
+        <v>335.19</v>
       </c>
       <c r="L85" t="n">
-        <v>321.38</v>
+        <v>368.46</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>117.46</v>
+        <v>134.59</v>
       </c>
       <c r="K86" t="n">
-        <v>475.47</v>
+        <v>544.84</v>
       </c>
       <c r="L86" t="n">
-        <v>489.76</v>
+        <v>561.21</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>222.23</v>
+        <v>254.68</v>
       </c>
       <c r="K87" t="n">
-        <v>155.62</v>
+        <v>178.35</v>
       </c>
       <c r="L87" t="n">
-        <v>271.3</v>
+        <v>310.92</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-231.33</v>
+        <v>-268.47</v>
       </c>
       <c r="K88" t="n">
-        <v>-262.17</v>
+        <v>-304.26</v>
       </c>
       <c r="L88" t="n">
-        <v>349.64</v>
+        <v>405.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="F14" t="n">
-        <v>12.24</v>
+        <v>12.76</v>
       </c>
       <c r="G14" t="n">
-        <v>23.1</v>
+        <v>11.4</v>
       </c>
       <c r="H14" t="n">
-        <v>86.40000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>21.24</v>
+        <v>43.33</v>
       </c>
       <c r="K14" t="n">
-        <v>-81.2</v>
+        <v>43.05</v>
       </c>
       <c r="L14" t="n">
-        <v>83.93000000000001</v>
+        <v>61.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:29:32</t>
+          <t>04:30:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.71</v>
+        <v>4.19</v>
       </c>
       <c r="F15" t="n">
-        <v>10.8</v>
+        <v>12.16</v>
       </c>
       <c r="G15" t="n">
-        <v>10.9</v>
+        <v>13.6</v>
       </c>
       <c r="H15" t="n">
-        <v>88.40000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>73.03</v>
+        <v>47.42</v>
       </c>
       <c r="K15" t="n">
-        <v>-66.14</v>
+        <v>-40.22</v>
       </c>
       <c r="L15" t="n">
-        <v>98.53</v>
+        <v>62.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:30:29</t>
+          <t>04:31:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="F16" t="n">
-        <v>9.449999999999999</v>
+        <v>6.65</v>
       </c>
       <c r="G16" t="n">
-        <v>11.2</v>
+        <v>9.5</v>
       </c>
       <c r="H16" t="n">
-        <v>83.8</v>
+        <v>72.2</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>0.87</v>
+        <v>18.1</v>
       </c>
       <c r="K16" t="n">
-        <v>-79.73</v>
+        <v>55.67</v>
       </c>
       <c r="L16" t="n">
-        <v>79.73</v>
+        <v>58.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:35:24</t>
+          <t>04:36:10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.26</v>
+        <v>4.43</v>
       </c>
       <c r="F17" t="n">
-        <v>10.72</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>22.8</v>
+        <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>89.7</v>
+        <v>60</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-28.97</v>
+        <v>54.55</v>
       </c>
       <c r="K17" t="n">
-        <v>103.48</v>
+        <v>65.66</v>
       </c>
       <c r="L17" t="n">
-        <v>107.46</v>
+        <v>85.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:37:14</t>
+          <t>04:38:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.25</v>
+        <v>4.73</v>
       </c>
       <c r="F18" t="n">
-        <v>13.89</v>
+        <v>11.98</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>13.7</v>
       </c>
       <c r="H18" t="n">
-        <v>81.59999999999999</v>
+        <v>56.1</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>15.25</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>94.20999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="L18" t="n">
-        <v>95.44</v>
+        <v>119.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:38:04</t>
+          <t>04:39:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.58</v>
+        <v>4.98</v>
       </c>
       <c r="F19" t="n">
-        <v>13.13</v>
+        <v>14.82</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H19" t="n">
-        <v>82.40000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>15.64</v>
+        <v>-12.53</v>
       </c>
       <c r="K19" t="n">
-        <v>100.66</v>
+        <v>124.94</v>
       </c>
       <c r="L19" t="n">
-        <v>101.87</v>
+        <v>125.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:42:46</t>
+          <t>04:44:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="F20" t="n">
-        <v>12.37</v>
+        <v>10.85</v>
       </c>
       <c r="G20" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="H20" t="n">
-        <v>85.7</v>
+        <v>40.8</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>30.02</v>
+        <v>-113.19</v>
       </c>
       <c r="K20" t="n">
-        <v>-138.07</v>
+        <v>116.25</v>
       </c>
       <c r="L20" t="n">
-        <v>141.3</v>
+        <v>162.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:43:36</t>
+          <t>04:46:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.24</v>
+        <v>3.67</v>
       </c>
       <c r="F21" t="n">
-        <v>9.529999999999999</v>
+        <v>11.28</v>
       </c>
       <c r="G21" t="n">
-        <v>13.8</v>
+        <v>21.5</v>
       </c>
       <c r="H21" t="n">
-        <v>82.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>168.22</v>
+        <v>92.36</v>
       </c>
       <c r="K21" t="n">
-        <v>94.08</v>
+        <v>72.27</v>
       </c>
       <c r="L21" t="n">
-        <v>192.74</v>
+        <v>117.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:45:46</t>
+          <t>04:48:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.25</v>
+        <v>3.66</v>
       </c>
       <c r="F22" t="n">
-        <v>11.98</v>
+        <v>7.49</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>359.8</v>
       </c>
       <c r="H22" t="n">
-        <v>79.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-93.36</v>
+        <v>68.2</v>
       </c>
       <c r="K22" t="n">
-        <v>-191.81</v>
+        <v>113.16</v>
       </c>
       <c r="L22" t="n">
-        <v>213.32</v>
+        <v>132.12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:50:33</t>
+          <t>04:52:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.46</v>
+        <v>4.24</v>
       </c>
       <c r="F23" t="n">
-        <v>14.23</v>
+        <v>11.46</v>
       </c>
       <c r="G23" t="n">
-        <v>18.4</v>
+        <v>355.4</v>
       </c>
       <c r="H23" t="n">
-        <v>83.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-13.1</v>
+        <v>234.83</v>
       </c>
       <c r="K23" t="n">
-        <v>204.34</v>
+        <v>4.15</v>
       </c>
       <c r="L23" t="n">
-        <v>204.76</v>
+        <v>234.87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:52:48</t>
+          <t>04:55:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.79</v>
+        <v>4.16</v>
       </c>
       <c r="F24" t="n">
-        <v>10.94</v>
+        <v>13.69</v>
       </c>
       <c r="G24" t="n">
-        <v>23.5</v>
+        <v>1.7</v>
       </c>
       <c r="H24" t="n">
-        <v>86.90000000000001</v>
+        <v>59.1</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>170.81</v>
+        <v>-97.37</v>
       </c>
       <c r="K24" t="n">
-        <v>69.31</v>
+        <v>-162.05</v>
       </c>
       <c r="L24" t="n">
-        <v>184.33</v>
+        <v>189.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:54:29</t>
+          <t>04:56:06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="F25" t="n">
-        <v>9.49</v>
+        <v>15.98</v>
       </c>
       <c r="G25" t="n">
-        <v>357.1</v>
+        <v>13.9</v>
       </c>
       <c r="H25" t="n">
-        <v>89.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-127.44</v>
+        <v>159.66</v>
       </c>
       <c r="K25" t="n">
-        <v>163.35</v>
+        <v>145.69</v>
       </c>
       <c r="L25" t="n">
-        <v>207.18</v>
+        <v>216.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>04:59:06</t>
+          <t>05:01:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.19</v>
+        <v>4.4</v>
       </c>
       <c r="F26" t="n">
-        <v>15.16</v>
+        <v>13.07</v>
       </c>
       <c r="G26" t="n">
-        <v>6.4</v>
+        <v>355.3</v>
       </c>
       <c r="H26" t="n">
-        <v>84.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-100</v>
+        <v>252.26</v>
       </c>
       <c r="K26" t="n">
-        <v>747.5</v>
+        <v>-17.76</v>
       </c>
       <c r="L26" t="n">
-        <v>754.16</v>
+        <v>252.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>04:59:55</t>
+          <t>05:02:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="F27" t="n">
-        <v>15.1</v>
+        <v>15.61</v>
       </c>
       <c r="G27" t="n">
-        <v>7.3</v>
+        <v>14.1</v>
       </c>
       <c r="H27" t="n">
-        <v>85</v>
+        <v>39.9</v>
       </c>
       <c r="I27" t="n">
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-313.1</v>
+        <v>-253.78</v>
       </c>
       <c r="K27" t="n">
-        <v>-341.96</v>
+        <v>132.23</v>
       </c>
       <c r="L27" t="n">
-        <v>463.65</v>
+        <v>286.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:01:09</t>
+          <t>05:04:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.31</v>
+        <v>4.23</v>
       </c>
       <c r="F28" t="n">
-        <v>14.08</v>
+        <v>9.25</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="H28" t="n">
-        <v>81.2</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-87.95</v>
+        <v>-141.14</v>
       </c>
       <c r="K28" t="n">
-        <v>373.97</v>
+        <v>132.23</v>
       </c>
       <c r="L28" t="n">
-        <v>384.17</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:14:32</t>
+          <t>05:16:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.21</v>
+        <v>3.36</v>
       </c>
       <c r="F29" t="n">
-        <v>13.67</v>
+        <v>8.24</v>
       </c>
       <c r="G29" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
-        <v>88</v>
+        <v>59.5</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>23.34</v>
+        <v>1.06</v>
       </c>
       <c r="K29" t="n">
-        <v>126.85</v>
+        <v>53.67</v>
       </c>
       <c r="L29" t="n">
-        <v>128.98</v>
+        <v>53.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:16:46</t>
+          <t>05:17:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.18</v>
+        <v>4.63</v>
       </c>
       <c r="F30" t="n">
-        <v>6.46</v>
+        <v>15.98</v>
       </c>
       <c r="G30" t="n">
-        <v>9.4</v>
+        <v>13.3</v>
       </c>
       <c r="H30" t="n">
-        <v>84.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>12.86</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>83.84</v>
+        <v>11.69</v>
       </c>
       <c r="L30" t="n">
-        <v>84.81999999999999</v>
+        <v>74.73999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:17:59</t>
+          <t>05:20:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.73</v>
+        <v>3.72</v>
       </c>
       <c r="F31" t="n">
-        <v>15.84</v>
+        <v>11.52</v>
       </c>
       <c r="G31" t="n">
-        <v>359.2</v>
+        <v>14.7</v>
       </c>
       <c r="H31" t="n">
-        <v>82.90000000000001</v>
+        <v>40.7</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.08</v>
+        <v>47.63</v>
       </c>
       <c r="K31" t="n">
-        <v>-141.88</v>
+        <v>34.26</v>
       </c>
       <c r="L31" t="n">
-        <v>143.03</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:22:16</t>
+          <t>05:24:37</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.47</v>
+        <v>3.67</v>
       </c>
       <c r="F32" t="n">
-        <v>12.55</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>6.1</v>
+        <v>19.3</v>
       </c>
       <c r="H32" t="n">
-        <v>83.90000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>125.36</v>
+        <v>30.57</v>
       </c>
       <c r="K32" t="n">
-        <v>60.66</v>
+        <v>59.16</v>
       </c>
       <c r="L32" t="n">
-        <v>139.27</v>
+        <v>66.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:24:40</t>
+          <t>05:25:31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.34</v>
+        <v>4.4</v>
       </c>
       <c r="F33" t="n">
-        <v>13.18</v>
+        <v>11.73</v>
       </c>
       <c r="G33" t="n">
-        <v>9.800000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="H33" t="n">
-        <v>87</v>
+        <v>66.2</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-84.14</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>34.63</v>
+        <v>45</v>
       </c>
       <c r="L33" t="n">
-        <v>90.98999999999999</v>
+        <v>103.53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:26:42</t>
+          <t>05:27:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.81</v>
+        <v>4.4</v>
       </c>
       <c r="F34" t="n">
-        <v>6.54</v>
+        <v>12.49</v>
       </c>
       <c r="G34" t="n">
-        <v>14.7</v>
+        <v>3.8</v>
       </c>
       <c r="H34" t="n">
-        <v>86.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-84.98</v>
+        <v>109.17</v>
       </c>
       <c r="K34" t="n">
-        <v>41.93</v>
+        <v>-77.51000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>94.76000000000001</v>
+        <v>133.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:31:51</t>
+          <t>05:32:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.26</v>
+        <v>5.09</v>
       </c>
       <c r="F35" t="n">
-        <v>11.36</v>
+        <v>15.17</v>
       </c>
       <c r="G35" t="n">
-        <v>3.1</v>
+        <v>29.9</v>
       </c>
       <c r="H35" t="n">
-        <v>78.59999999999999</v>
+        <v>36.1</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>24.66</v>
+        <v>-49.83</v>
       </c>
       <c r="K35" t="n">
-        <v>-186.48</v>
+        <v>216.9</v>
       </c>
       <c r="L35" t="n">
-        <v>188.11</v>
+        <v>222.55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:32:59</t>
+          <t>05:34:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.04</v>
+        <v>4.25</v>
       </c>
       <c r="F36" t="n">
-        <v>14.51</v>
+        <v>13.11</v>
       </c>
       <c r="G36" t="n">
-        <v>12.7</v>
+        <v>347.6</v>
       </c>
       <c r="H36" t="n">
-        <v>81.40000000000001</v>
+        <v>50.3</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-83.78</v>
+        <v>140.18</v>
       </c>
       <c r="K36" t="n">
-        <v>-136.02</v>
+        <v>-22.98</v>
       </c>
       <c r="L36" t="n">
-        <v>159.75</v>
+        <v>142.05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:34:41</t>
+          <t>05:34:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.81</v>
+        <v>5.06</v>
       </c>
       <c r="F37" t="n">
-        <v>13.18</v>
+        <v>15.98</v>
       </c>
       <c r="G37" t="n">
-        <v>10.5</v>
+        <v>0.8</v>
       </c>
       <c r="H37" t="n">
-        <v>81.2</v>
+        <v>52.9</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-6.64</v>
+        <v>49.25</v>
       </c>
       <c r="K37" t="n">
-        <v>126.03</v>
+        <v>179.47</v>
       </c>
       <c r="L37" t="n">
-        <v>126.2</v>
+        <v>186.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:38:14</t>
+          <t>05:38:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.84</v>
+        <v>3.39</v>
       </c>
       <c r="F38" t="n">
-        <v>13.18</v>
+        <v>8.33</v>
       </c>
       <c r="G38" t="n">
-        <v>13.6</v>
+        <v>5.4</v>
       </c>
       <c r="H38" t="n">
-        <v>84.2</v>
+        <v>45.8</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>173.71</v>
+        <v>138.67</v>
       </c>
       <c r="K38" t="n">
-        <v>-181.32</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>251.1</v>
+        <v>157.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:40:28</t>
+          <t>05:41:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.24</v>
+        <v>4.29</v>
       </c>
       <c r="F39" t="n">
-        <v>13.52</v>
+        <v>10.9</v>
       </c>
       <c r="G39" t="n">
-        <v>3.9</v>
+        <v>13.3</v>
       </c>
       <c r="H39" t="n">
-        <v>78.2</v>
+        <v>63.1</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-217.88</v>
+        <v>125.81</v>
       </c>
       <c r="K39" t="n">
-        <v>185.79</v>
+        <v>200.33</v>
       </c>
       <c r="L39" t="n">
-        <v>286.34</v>
+        <v>236.55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:42:20</t>
+          <t>05:42:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="F40" t="n">
-        <v>11.56</v>
+        <v>10.95</v>
       </c>
       <c r="G40" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="H40" t="n">
-        <v>83.7</v>
+        <v>57.6</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>125.53</v>
+        <v>210.18</v>
       </c>
       <c r="K40" t="n">
-        <v>-192.27</v>
+        <v>-25.24</v>
       </c>
       <c r="L40" t="n">
-        <v>229.61</v>
+        <v>211.69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:46:38</t>
+          <t>05:48:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.66</v>
+        <v>3.98</v>
       </c>
       <c r="F41" t="n">
-        <v>11.11</v>
+        <v>12.49</v>
       </c>
       <c r="G41" t="n">
-        <v>23.1</v>
+        <v>2.3</v>
       </c>
       <c r="H41" t="n">
-        <v>91.7</v>
+        <v>55.7</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>249.27</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>181.23</v>
+        <v>278.97</v>
       </c>
       <c r="L41" t="n">
-        <v>308.19</v>
+        <v>289.96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:48:19</t>
+          <t>05:50:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.84</v>
+        <v>4.62</v>
       </c>
       <c r="F42" t="n">
-        <v>11.69</v>
+        <v>15.1</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>25.5</v>
       </c>
       <c r="H42" t="n">
-        <v>78.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>50.79</v>
+        <v>78.75</v>
       </c>
       <c r="K42" t="n">
-        <v>366.76</v>
+        <v>290.67</v>
       </c>
       <c r="L42" t="n">
-        <v>370.26</v>
+        <v>301.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:49:31</t>
+          <t>05:52:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.33</v>
+        <v>4.42</v>
       </c>
       <c r="F43" t="n">
-        <v>9.09</v>
+        <v>13.51</v>
       </c>
       <c r="G43" t="n">
-        <v>4.4</v>
+        <v>15.2</v>
       </c>
       <c r="H43" t="n">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-303.93</v>
+        <v>-181.76</v>
       </c>
       <c r="K43" t="n">
-        <v>-74.94</v>
+        <v>245.52</v>
       </c>
       <c r="L43" t="n">
-        <v>313.03</v>
+        <v>305.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05:59:00</t>
+          <t>06:02:03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.26</v>
+        <v>4.53</v>
       </c>
       <c r="F44" t="n">
-        <v>13.77</v>
+        <v>14.01</v>
       </c>
       <c r="G44" t="n">
-        <v>17.2</v>
+        <v>3.4</v>
       </c>
       <c r="H44" t="n">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-22.66</v>
+        <v>101.11</v>
       </c>
       <c r="K44" t="n">
-        <v>-65.69</v>
+        <v>-15.86</v>
       </c>
       <c r="L44" t="n">
-        <v>69.48999999999999</v>
+        <v>102.35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05:59:56</t>
+          <t>06:03:54</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.57</v>
+        <v>4.7</v>
       </c>
       <c r="F45" t="n">
-        <v>13.78</v>
+        <v>14.95</v>
       </c>
       <c r="G45" t="n">
-        <v>11.3</v>
+        <v>6</v>
       </c>
       <c r="H45" t="n">
-        <v>85.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>94.90000000000001</v>
+        <v>1.71</v>
       </c>
       <c r="K45" t="n">
-        <v>-73.13</v>
+        <v>36.24</v>
       </c>
       <c r="L45" t="n">
-        <v>119.81</v>
+        <v>36.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:01:27</t>
+          <t>06:05:50</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.19</v>
+        <v>4.72</v>
       </c>
       <c r="F46" t="n">
-        <v>15.98</v>
+        <v>14.69</v>
       </c>
       <c r="G46" t="n">
-        <v>21.2</v>
+        <v>356.3</v>
       </c>
       <c r="H46" t="n">
-        <v>84.8</v>
+        <v>22.6</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>84.09</v>
+        <v>-52.57</v>
       </c>
       <c r="K46" t="n">
-        <v>-61.64</v>
+        <v>115.81</v>
       </c>
       <c r="L46" t="n">
-        <v>104.26</v>
+        <v>127.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:05:12</t>
+          <t>06:09:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.57</v>
+        <v>4.68</v>
       </c>
       <c r="F47" t="n">
-        <v>13.77</v>
+        <v>14.92</v>
       </c>
       <c r="G47" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="H47" t="n">
-        <v>88.3</v>
+        <v>67.7</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-129.29</v>
+        <v>120.97</v>
       </c>
       <c r="K47" t="n">
-        <v>32.62</v>
+        <v>21.6</v>
       </c>
       <c r="L47" t="n">
-        <v>133.34</v>
+        <v>122.88</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:07:11</t>
+          <t>06:12:01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.52</v>
+        <v>5</v>
       </c>
       <c r="F48" t="n">
-        <v>12.65</v>
+        <v>15.05</v>
       </c>
       <c r="G48" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="H48" t="n">
-        <v>85.8</v>
+        <v>48.5</v>
       </c>
       <c r="I48" t="n">
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-100.91</v>
+        <v>-8.56</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.7</v>
+        <v>97.38</v>
       </c>
       <c r="L48" t="n">
-        <v>101.07</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:07:55</t>
+          <t>06:14:21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.1</v>
+        <v>5.02</v>
       </c>
       <c r="F49" t="n">
-        <v>9.76</v>
+        <v>15.64</v>
       </c>
       <c r="G49" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>82.09999999999999</v>
+        <v>34.4</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>75.77</v>
+        <v>-48.75</v>
       </c>
       <c r="K49" t="n">
-        <v>30.45</v>
+        <v>112.55</v>
       </c>
       <c r="L49" t="n">
-        <v>81.66</v>
+        <v>122.66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:12:49</t>
+          <t>06:19:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="F50" t="n">
-        <v>14.17</v>
+        <v>11.05</v>
       </c>
       <c r="G50" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="H50" t="n">
-        <v>82.2</v>
+        <v>61.4</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>-166.01</v>
+        <v>138.19</v>
       </c>
       <c r="K50" t="n">
-        <v>232.03</v>
+        <v>90.2</v>
       </c>
       <c r="L50" t="n">
-        <v>285.31</v>
+        <v>165.02</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:15:02</t>
+          <t>06:20:57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.68</v>
+        <v>5.16</v>
       </c>
       <c r="F51" t="n">
-        <v>14.76</v>
+        <v>14.86</v>
       </c>
       <c r="G51" t="n">
-        <v>11.6</v>
+        <v>5.8</v>
       </c>
       <c r="H51" t="n">
-        <v>89.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I51" t="n">
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-68.84</v>
+        <v>78.72</v>
       </c>
       <c r="K51" t="n">
-        <v>-212.58</v>
+        <v>168.93</v>
       </c>
       <c r="L51" t="n">
-        <v>223.45</v>
+        <v>186.37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:17:11</t>
+          <t>06:22:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.27</v>
+        <v>4.05</v>
       </c>
       <c r="F52" t="n">
-        <v>14.08</v>
+        <v>15.98</v>
       </c>
       <c r="G52" t="n">
-        <v>4.7</v>
+        <v>13.6</v>
       </c>
       <c r="H52" t="n">
-        <v>87.3</v>
+        <v>66.3</v>
       </c>
       <c r="I52" t="n">
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>96.48999999999999</v>
+        <v>-84.12</v>
       </c>
       <c r="K52" t="n">
-        <v>-224.19</v>
+        <v>119</v>
       </c>
       <c r="L52" t="n">
-        <v>244.07</v>
+        <v>145.73</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:22:06</t>
+          <t>06:25:32</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.59</v>
+        <v>4.31</v>
       </c>
       <c r="F53" t="n">
-        <v>13.38</v>
+        <v>13.25</v>
       </c>
       <c r="G53" t="n">
-        <v>354.3</v>
+        <v>3.4</v>
       </c>
       <c r="H53" t="n">
-        <v>81.5</v>
+        <v>79.7</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-205.64</v>
+        <v>-140.62</v>
       </c>
       <c r="K53" t="n">
-        <v>216.23</v>
+        <v>117.25</v>
       </c>
       <c r="L53" t="n">
-        <v>298.4</v>
+        <v>183.09</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:23:26</t>
+          <t>06:27:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="F54" t="n">
-        <v>15.98</v>
+        <v>12.79</v>
       </c>
       <c r="G54" t="n">
-        <v>9.4</v>
+        <v>18.5</v>
       </c>
       <c r="H54" t="n">
-        <v>82.5</v>
+        <v>40.7</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>142.9</v>
+        <v>151.79</v>
       </c>
       <c r="K54" t="n">
-        <v>214.67</v>
+        <v>115.17</v>
       </c>
       <c r="L54" t="n">
-        <v>257.88</v>
+        <v>190.54</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:25:38</t>
+          <t>06:29:39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.12</v>
+        <v>4.9</v>
       </c>
       <c r="F55" t="n">
-        <v>10.67</v>
+        <v>15.98</v>
       </c>
       <c r="G55" t="n">
-        <v>16.1</v>
+        <v>15.7</v>
       </c>
       <c r="H55" t="n">
-        <v>78.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="I55" t="n">
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-204.92</v>
+        <v>-206.62</v>
       </c>
       <c r="K55" t="n">
-        <v>209.63</v>
+        <v>127.74</v>
       </c>
       <c r="L55" t="n">
-        <v>293.15</v>
+        <v>242.92</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:29:45</t>
+          <t>06:34:18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.36</v>
+        <v>3.67</v>
       </c>
       <c r="F56" t="n">
-        <v>13.95</v>
+        <v>11.66</v>
       </c>
       <c r="G56" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="H56" t="n">
-        <v>81.5</v>
+        <v>64.8</v>
       </c>
       <c r="I56" t="n">
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-259.13</v>
+        <v>192.54</v>
       </c>
       <c r="K56" t="n">
-        <v>-247.43</v>
+        <v>-83.69</v>
       </c>
       <c r="L56" t="n">
-        <v>358.29</v>
+        <v>209.95</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:30:46</t>
+          <t>06:36:20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.84</v>
+        <v>5.17</v>
       </c>
       <c r="F57" t="n">
-        <v>15.23</v>
+        <v>13.51</v>
       </c>
       <c r="G57" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="H57" t="n">
-        <v>85</v>
+        <v>34.9</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>436.41</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>323.82</v>
+        <v>337.42</v>
       </c>
       <c r="L57" t="n">
-        <v>543.4299999999999</v>
+        <v>347.54</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:31:34</t>
+          <t>06:38:08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.23</v>
+        <v>4.88</v>
       </c>
       <c r="F58" t="n">
-        <v>9.76</v>
+        <v>13.73</v>
       </c>
       <c r="G58" t="n">
-        <v>9.699999999999999</v>
+        <v>4</v>
       </c>
       <c r="H58" t="n">
-        <v>82.3</v>
+        <v>29.2</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>84.79000000000001</v>
+        <v>236.43</v>
       </c>
       <c r="K58" t="n">
-        <v>286.35</v>
+        <v>-16.47</v>
       </c>
       <c r="L58" t="n">
-        <v>298.64</v>
+        <v>237.01</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:41:43</t>
+          <t>06:46:30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.06</v>
+        <v>5.24</v>
       </c>
       <c r="F59" t="n">
-        <v>12.08</v>
+        <v>15.98</v>
       </c>
       <c r="G59" t="n">
-        <v>11.3</v>
+        <v>15.9</v>
       </c>
       <c r="H59" t="n">
-        <v>82.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-64.45999999999999</v>
+        <v>72.28</v>
       </c>
       <c r="K59" t="n">
-        <v>-70.06999999999999</v>
+        <v>-49.16</v>
       </c>
       <c r="L59" t="n">
-        <v>95.20999999999999</v>
+        <v>87.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:42:48</t>
+          <t>06:48:13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.14</v>
+        <v>4.48</v>
       </c>
       <c r="F60" t="n">
-        <v>11.73</v>
+        <v>10.99</v>
       </c>
       <c r="G60" t="n">
-        <v>8.4</v>
+        <v>358.8</v>
       </c>
       <c r="H60" t="n">
-        <v>80.59999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="I60" t="n">
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-26.21</v>
+        <v>-52.6</v>
       </c>
       <c r="K60" t="n">
-        <v>-8.07</v>
+        <v>47.9</v>
       </c>
       <c r="L60" t="n">
-        <v>27.42</v>
+        <v>71.14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:44:25</t>
+          <t>06:50:05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.68</v>
+        <v>4.31</v>
       </c>
       <c r="F61" t="n">
-        <v>15.98</v>
+        <v>12.44</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9</v>
+        <v>14.7</v>
       </c>
       <c r="H61" t="n">
-        <v>84.8</v>
+        <v>54.9</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-74.29000000000001</v>
+        <v>22.07</v>
       </c>
       <c r="K61" t="n">
-        <v>-71.8</v>
+        <v>72.05</v>
       </c>
       <c r="L61" t="n">
-        <v>103.32</v>
+        <v>75.36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:49:42</t>
+          <t>06:54:07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.63</v>
+        <v>4.56</v>
       </c>
       <c r="F62" t="n">
-        <v>15.58</v>
+        <v>12.69</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9</v>
+        <v>19.9</v>
       </c>
       <c r="H62" t="n">
-        <v>84.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-14.51</v>
+        <v>87.08</v>
       </c>
       <c r="K62" t="n">
-        <v>-46.23</v>
+        <v>-46.42</v>
       </c>
       <c r="L62" t="n">
-        <v>48.45</v>
+        <v>98.68000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:50:39</t>
+          <t>06:56:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.8</v>
+        <v>5.13</v>
       </c>
       <c r="F63" t="n">
-        <v>13.39</v>
+        <v>15.98</v>
       </c>
       <c r="G63" t="n">
-        <v>3.5</v>
+        <v>16.9</v>
       </c>
       <c r="H63" t="n">
-        <v>86.3</v>
+        <v>43.3</v>
       </c>
       <c r="I63" t="n">
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-94.73999999999999</v>
+        <v>107.45</v>
       </c>
       <c r="K63" t="n">
-        <v>-94.67</v>
+        <v>114.22</v>
       </c>
       <c r="L63" t="n">
-        <v>133.93</v>
+        <v>156.82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:53:16</t>
+          <t>06:58:17</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.99</v>
+        <v>4.74</v>
       </c>
       <c r="F64" t="n">
-        <v>13.87</v>
+        <v>13.08</v>
       </c>
       <c r="G64" t="n">
-        <v>11.3</v>
+        <v>359.5</v>
       </c>
       <c r="H64" t="n">
-        <v>88.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-105.99</v>
+        <v>-133.23</v>
       </c>
       <c r="K64" t="n">
-        <v>40.91</v>
+        <v>-41.72</v>
       </c>
       <c r="L64" t="n">
-        <v>113.61</v>
+        <v>139.61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06:56:55</t>
+          <t>07:02:47</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="F65" t="n">
-        <v>15.98</v>
+        <v>10.17</v>
       </c>
       <c r="G65" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="H65" t="n">
-        <v>88.5</v>
+        <v>35.9</v>
       </c>
       <c r="I65" t="n">
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-155.19</v>
+        <v>28.62</v>
       </c>
       <c r="K65" t="n">
-        <v>105.7</v>
+        <v>-121.09</v>
       </c>
       <c r="L65" t="n">
-        <v>187.77</v>
+        <v>124.42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06:58:39</t>
+          <t>07:04:11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.06</v>
+        <v>4.18</v>
       </c>
       <c r="F66" t="n">
-        <v>15.69</v>
+        <v>15.72</v>
       </c>
       <c r="G66" t="n">
-        <v>21.3</v>
+        <v>358.4</v>
       </c>
       <c r="H66" t="n">
-        <v>82.5</v>
+        <v>85.5</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-79.86</v>
+        <v>-135.59</v>
       </c>
       <c r="K66" t="n">
-        <v>-173.9</v>
+        <v>-112.39</v>
       </c>
       <c r="L66" t="n">
-        <v>191.36</v>
+        <v>176.11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06:59:57</t>
+          <t>07:06:25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.78</v>
+        <v>4.53</v>
       </c>
       <c r="F67" t="n">
-        <v>11.94</v>
+        <v>15.87</v>
       </c>
       <c r="G67" t="n">
-        <v>359</v>
+        <v>342.9</v>
       </c>
       <c r="H67" t="n">
-        <v>85.90000000000001</v>
+        <v>54.2</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-58.58</v>
+        <v>135.73</v>
       </c>
       <c r="K67" t="n">
-        <v>-128.69</v>
+        <v>-79.45</v>
       </c>
       <c r="L67" t="n">
-        <v>141.4</v>
+        <v>157.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:04:35</t>
+          <t>07:11:16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.44</v>
+        <v>4.84</v>
       </c>
       <c r="F68" t="n">
-        <v>14.44</v>
+        <v>15.06</v>
       </c>
       <c r="G68" t="n">
-        <v>17.7</v>
+        <v>5.5</v>
       </c>
       <c r="H68" t="n">
-        <v>89.5</v>
+        <v>82.2</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-34.44</v>
+        <v>214.53</v>
       </c>
       <c r="K68" t="n">
-        <v>-98.51000000000001</v>
+        <v>-123.84</v>
       </c>
       <c r="L68" t="n">
-        <v>104.35</v>
+        <v>247.71</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:07:18</t>
+          <t>07:12:39</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.82</v>
+        <v>4.05</v>
       </c>
       <c r="F69" t="n">
-        <v>10.29</v>
+        <v>14.7</v>
       </c>
       <c r="G69" t="n">
-        <v>14.8</v>
+        <v>356</v>
       </c>
       <c r="H69" t="n">
-        <v>84</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-101.88</v>
+        <v>31.37</v>
       </c>
       <c r="K69" t="n">
-        <v>175.76</v>
+        <v>220.37</v>
       </c>
       <c r="L69" t="n">
-        <v>203.15</v>
+        <v>222.59</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:09:53</t>
+          <t>07:14:41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.74</v>
+        <v>5.04</v>
       </c>
       <c r="F70" t="n">
-        <v>14.56</v>
+        <v>15.86</v>
       </c>
       <c r="G70" t="n">
-        <v>14</v>
+        <v>6.3</v>
       </c>
       <c r="H70" t="n">
-        <v>88</v>
+        <v>18.8</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-31.38</v>
+        <v>41.6</v>
       </c>
       <c r="K70" t="n">
-        <v>273.95</v>
+        <v>295.08</v>
       </c>
       <c r="L70" t="n">
-        <v>275.74</v>
+        <v>298</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:13:06</t>
+          <t>07:19:43</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.18</v>
+        <v>4.64</v>
       </c>
       <c r="F71" t="n">
-        <v>12.76</v>
+        <v>13.39</v>
       </c>
       <c r="G71" t="n">
-        <v>19.1</v>
+        <v>2.7</v>
       </c>
       <c r="H71" t="n">
-        <v>83</v>
+        <v>25.5</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-390.15</v>
+        <v>62.83</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.31</v>
+        <v>383.82</v>
       </c>
       <c r="L71" t="n">
-        <v>390.15</v>
+        <v>388.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:15:11</t>
+          <t>07:21:26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.62</v>
+        <v>4.5</v>
       </c>
       <c r="F72" t="n">
-        <v>11.01</v>
+        <v>14.03</v>
       </c>
       <c r="G72" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="H72" t="n">
-        <v>82.09999999999999</v>
+        <v>25.1</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-267.85</v>
+        <v>-269.93</v>
       </c>
       <c r="K72" t="n">
-        <v>-244.57</v>
+        <v>169.37</v>
       </c>
       <c r="L72" t="n">
-        <v>362.71</v>
+        <v>318.67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:17:33</t>
+          <t>07:22:08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.63</v>
+        <v>4.46</v>
       </c>
       <c r="F73" t="n">
-        <v>13.24</v>
+        <v>11.93</v>
       </c>
       <c r="G73" t="n">
-        <v>15.5</v>
+        <v>7.1</v>
       </c>
       <c r="H73" t="n">
-        <v>79.7</v>
+        <v>69.7</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-45.24</v>
+        <v>-325.2</v>
       </c>
       <c r="K73" t="n">
-        <v>-287.16</v>
+        <v>131.7</v>
       </c>
       <c r="L73" t="n">
-        <v>290.7</v>
+        <v>350.86</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:29:51</t>
+          <t>07:32:14</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.24</v>
+        <v>4.92</v>
       </c>
       <c r="F74" t="n">
-        <v>15.77</v>
+        <v>15.98</v>
       </c>
       <c r="G74" t="n">
-        <v>6.4</v>
+        <v>24.3</v>
       </c>
       <c r="H74" t="n">
-        <v>74.2</v>
+        <v>77.7</v>
       </c>
       <c r="I74" t="n">
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>93.58</v>
+        <v>103.86</v>
       </c>
       <c r="K74" t="n">
-        <v>-67.18000000000001</v>
+        <v>16.56</v>
       </c>
       <c r="L74" t="n">
-        <v>115.2</v>
+        <v>105.18</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:30:40</t>
+          <t>07:34:30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.03</v>
+        <v>5.28</v>
       </c>
       <c r="F75" t="n">
         <v>15.98</v>
       </c>
       <c r="G75" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="H75" t="n">
-        <v>84.59999999999999</v>
+        <v>48.4</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>32.51</v>
+        <v>105.45</v>
       </c>
       <c r="K75" t="n">
-        <v>-116.4</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>120.85</v>
+        <v>139.87</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:32:23</t>
+          <t>07:36:25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.37</v>
+        <v>4.99</v>
       </c>
       <c r="F76" t="n">
-        <v>15.98</v>
+        <v>15.15</v>
       </c>
       <c r="G76" t="n">
-        <v>7.4</v>
+        <v>350.8</v>
       </c>
       <c r="H76" t="n">
-        <v>82.40000000000001</v>
+        <v>46.8</v>
       </c>
       <c r="I76" t="n">
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>80.22</v>
+        <v>35.76</v>
       </c>
       <c r="K76" t="n">
-        <v>0.58</v>
+        <v>66.67</v>
       </c>
       <c r="L76" t="n">
-        <v>80.22</v>
+        <v>75.65000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:38:03</t>
+          <t>07:41:01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.79</v>
+        <v>4.59</v>
       </c>
       <c r="F77" t="n">
-        <v>13.61</v>
+        <v>13.46</v>
       </c>
       <c r="G77" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="H77" t="n">
-        <v>78.2</v>
+        <v>35.9</v>
       </c>
       <c r="I77" t="n">
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-9.75</v>
+        <v>-51.12</v>
       </c>
       <c r="K77" t="n">
-        <v>30.5</v>
+        <v>72.09</v>
       </c>
       <c r="L77" t="n">
-        <v>32.02</v>
+        <v>88.38</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:39:10</t>
+          <t>07:42:11</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="F78" t="n">
-        <v>15.98</v>
+        <v>14.57</v>
       </c>
       <c r="G78" t="n">
-        <v>11.2</v>
+        <v>5.8</v>
       </c>
       <c r="H78" t="n">
-        <v>85</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>113.98</v>
+        <v>-97.33</v>
       </c>
       <c r="K78" t="n">
-        <v>-1.22</v>
+        <v>20.43</v>
       </c>
       <c r="L78" t="n">
-        <v>113.99</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:41:33</t>
+          <t>07:43:29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.92</v>
+        <v>4.52</v>
       </c>
       <c r="F79" t="n">
-        <v>15.33</v>
+        <v>14.77</v>
       </c>
       <c r="G79" t="n">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="H79" t="n">
-        <v>75.5</v>
+        <v>44.3</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-84.26000000000001</v>
+        <v>136.06</v>
       </c>
       <c r="K79" t="n">
-        <v>117.38</v>
+        <v>-1.55</v>
       </c>
       <c r="L79" t="n">
-        <v>144.49</v>
+        <v>136.07</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:45:56</t>
+          <t>07:47:32</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.17</v>
+        <v>4.88</v>
       </c>
       <c r="F80" t="n">
-        <v>15.98</v>
+        <v>15.7</v>
       </c>
       <c r="G80" t="n">
-        <v>11.7</v>
+        <v>22</v>
       </c>
       <c r="H80" t="n">
-        <v>81.5</v>
+        <v>47.7</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-76.78</v>
+        <v>40.7</v>
       </c>
       <c r="K80" t="n">
-        <v>206.24</v>
+        <v>-166.22</v>
       </c>
       <c r="L80" t="n">
-        <v>220.07</v>
+        <v>171.13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:47:28</t>
+          <t>07:49:15</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.1</v>
+        <v>4.88</v>
       </c>
       <c r="F81" t="n">
-        <v>15.73</v>
+        <v>15.98</v>
       </c>
       <c r="G81" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
       <c r="H81" t="n">
-        <v>88.5</v>
+        <v>62.1</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-128.2</v>
+        <v>161.63</v>
       </c>
       <c r="K81" t="n">
-        <v>-150.32</v>
+        <v>-59.22</v>
       </c>
       <c r="L81" t="n">
-        <v>197.56</v>
+        <v>172.14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:48:59</t>
+          <t>07:51:23</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.98</v>
+        <v>4.59</v>
       </c>
       <c r="F82" t="n">
-        <v>15.19</v>
+        <v>15.46</v>
       </c>
       <c r="G82" t="n">
-        <v>25.8</v>
+        <v>4.2</v>
       </c>
       <c r="H82" t="n">
-        <v>96.40000000000001</v>
+        <v>41.3</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-121.79</v>
+        <v>-92.17</v>
       </c>
       <c r="K82" t="n">
-        <v>-102.8</v>
+        <v>130.73</v>
       </c>
       <c r="L82" t="n">
-        <v>159.37</v>
+        <v>159.95</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:54:07</t>
+          <t>07:55:29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.08</v>
+        <v>5.3</v>
       </c>
       <c r="F83" t="n">
-        <v>15.17</v>
+        <v>15.98</v>
       </c>
       <c r="G83" t="n">
-        <v>357.7</v>
+        <v>3.1</v>
       </c>
       <c r="H83" t="n">
-        <v>85.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-248.29</v>
+        <v>-238.79</v>
       </c>
       <c r="K83" t="n">
-        <v>196.98</v>
+        <v>165.77</v>
       </c>
       <c r="L83" t="n">
-        <v>316.94</v>
+        <v>290.69</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:56:32</t>
+          <t>07:57:10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.89</v>
+        <v>4.77</v>
       </c>
       <c r="F84" t="n">
-        <v>12.33</v>
+        <v>15.98</v>
       </c>
       <c r="G84" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="H84" t="n">
-        <v>78.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I84" t="n">
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-131.61</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>258.86</v>
+        <v>464.28</v>
       </c>
       <c r="L84" t="n">
-        <v>290.4</v>
+        <v>469.87</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:58:25</t>
+          <t>07:59:43</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.53</v>
+        <v>4.93</v>
       </c>
       <c r="F85" t="n">
-        <v>13.93</v>
+        <v>15.98</v>
       </c>
       <c r="G85" t="n">
-        <v>359.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>87.5</v>
+        <v>33.8</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>153</v>
+        <v>15.96</v>
       </c>
       <c r="K85" t="n">
-        <v>335.19</v>
+        <v>252.08</v>
       </c>
       <c r="L85" t="n">
-        <v>368.46</v>
+        <v>252.59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:02:09</t>
+          <t>08:03:55</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.18</v>
+        <v>4.58</v>
       </c>
       <c r="F86" t="n">
-        <v>12.95</v>
+        <v>13.5</v>
       </c>
       <c r="G86" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="H86" t="n">
-        <v>84.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>134.59</v>
+        <v>277.28</v>
       </c>
       <c r="K86" t="n">
-        <v>544.84</v>
+        <v>-12.82</v>
       </c>
       <c r="L86" t="n">
-        <v>561.21</v>
+        <v>277.58</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:04:33</t>
+          <t>08:05:03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.2</v>
+        <v>4.73</v>
       </c>
       <c r="F87" t="n">
-        <v>15.98</v>
+        <v>13.66</v>
       </c>
       <c r="G87" t="n">
-        <v>10.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>254.68</v>
+        <v>-362.2</v>
       </c>
       <c r="K87" t="n">
-        <v>178.35</v>
+        <v>-58.71</v>
       </c>
       <c r="L87" t="n">
-        <v>310.92</v>
+        <v>366.93</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:05:23</t>
+          <t>08:06:33</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.27</v>
+        <v>4.31</v>
       </c>
       <c r="F88" t="n">
-        <v>15.98</v>
+        <v>12.28</v>
       </c>
       <c r="G88" t="n">
-        <v>21.6</v>
+        <v>11.1</v>
       </c>
       <c r="H88" t="n">
-        <v>85.59999999999999</v>
+        <v>40.6</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-268.47</v>
+        <v>-13.21</v>
       </c>
       <c r="K88" t="n">
-        <v>-304.26</v>
+        <v>331.17</v>
       </c>
       <c r="L88" t="n">
-        <v>405.77</v>
+        <v>331.43</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.67</v>
+        <v>3.77</v>
       </c>
       <c r="F14" t="n">
-        <v>12.76</v>
+        <v>12.03</v>
       </c>
       <c r="G14" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="H14" t="n">
-        <v>16.8</v>
+        <v>52</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>43.33</v>
+        <v>54.31</v>
       </c>
       <c r="K14" t="n">
-        <v>43.05</v>
+        <v>0.24</v>
       </c>
       <c r="L14" t="n">
-        <v>61.08</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:30:35</t>
+          <t>04:30:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.19</v>
+        <v>3.87</v>
       </c>
       <c r="F15" t="n">
-        <v>12.16</v>
+        <v>12.78</v>
       </c>
       <c r="G15" t="n">
-        <v>13.6</v>
+        <v>23.2</v>
       </c>
       <c r="H15" t="n">
-        <v>30.4</v>
+        <v>79.8</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>47.42</v>
+        <v>56.66</v>
       </c>
       <c r="K15" t="n">
-        <v>-40.22</v>
+        <v>0.76</v>
       </c>
       <c r="L15" t="n">
-        <v>62.18</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:31:45</t>
+          <t>04:31:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.87</v>
+        <v>3.06</v>
       </c>
       <c r="F16" t="n">
-        <v>6.65</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>9.5</v>
+        <v>25.4</v>
       </c>
       <c r="H16" t="n">
-        <v>72.2</v>
+        <v>53</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>18.1</v>
+        <v>-22.91</v>
       </c>
       <c r="K16" t="n">
-        <v>55.67</v>
+        <v>32.08</v>
       </c>
       <c r="L16" t="n">
-        <v>58.54</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:36:10</t>
+          <t>04:36:16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.43</v>
+        <v>3.7</v>
       </c>
       <c r="F17" t="n">
-        <v>9.220000000000001</v>
+        <v>10.88</v>
       </c>
       <c r="G17" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>39.6</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>54.55</v>
+        <v>7.88</v>
       </c>
       <c r="K17" t="n">
-        <v>65.66</v>
+        <v>78.33</v>
       </c>
       <c r="L17" t="n">
-        <v>85.36</v>
+        <v>78.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:38:27</t>
+          <t>04:37:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.73</v>
+        <v>4.13</v>
       </c>
       <c r="F18" t="n">
-        <v>11.98</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>13.7</v>
+        <v>4.1</v>
       </c>
       <c r="H18" t="n">
-        <v>56.1</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>97.01000000000001</v>
+        <v>-53</v>
       </c>
       <c r="K18" t="n">
-        <v>70.12</v>
+        <v>-86.72</v>
       </c>
       <c r="L18" t="n">
-        <v>119.7</v>
+        <v>101.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:39:44</t>
+          <t>04:39:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.98</v>
+        <v>3.83</v>
       </c>
       <c r="F19" t="n">
-        <v>14.82</v>
+        <v>10.24</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="H19" t="n">
-        <v>63.4</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-12.53</v>
+        <v>-71.31999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>124.94</v>
+        <v>-27.06</v>
       </c>
       <c r="L19" t="n">
-        <v>125.57</v>
+        <v>76.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:44:43</t>
+          <t>04:43:50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.38</v>
+        <v>3.74</v>
       </c>
       <c r="F20" t="n">
-        <v>10.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>7.3</v>
+        <v>359.6</v>
       </c>
       <c r="H20" t="n">
-        <v>40.8</v>
+        <v>29.4</v>
       </c>
       <c r="I20" t="n">
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-113.19</v>
+        <v>-82.59</v>
       </c>
       <c r="K20" t="n">
-        <v>116.25</v>
+        <v>45.04</v>
       </c>
       <c r="L20" t="n">
-        <v>162.25</v>
+        <v>94.06999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:46:31</t>
+          <t>04:45:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.67</v>
+        <v>4.61</v>
       </c>
       <c r="F21" t="n">
-        <v>11.28</v>
+        <v>11.68</v>
       </c>
       <c r="G21" t="n">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>65.59999999999999</v>
+        <v>52.5</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>92.36</v>
+        <v>-48.75</v>
       </c>
       <c r="K21" t="n">
-        <v>72.27</v>
+        <v>-130.46</v>
       </c>
       <c r="L21" t="n">
-        <v>117.28</v>
+        <v>139.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:48:20</t>
+          <t>04:47:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.66</v>
+        <v>4.19</v>
       </c>
       <c r="F22" t="n">
-        <v>7.49</v>
+        <v>14.1</v>
       </c>
       <c r="G22" t="n">
-        <v>359.8</v>
+        <v>359.2</v>
       </c>
       <c r="H22" t="n">
-        <v>68.90000000000001</v>
+        <v>36.5</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>68.2</v>
+        <v>78.64</v>
       </c>
       <c r="K22" t="n">
-        <v>113.16</v>
+        <v>-109.61</v>
       </c>
       <c r="L22" t="n">
-        <v>132.12</v>
+        <v>134.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:52:58</t>
+          <t>04:51:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.24</v>
+        <v>4.38</v>
       </c>
       <c r="F23" t="n">
-        <v>11.46</v>
+        <v>13.23</v>
       </c>
       <c r="G23" t="n">
-        <v>355.4</v>
+        <v>357.7</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>64.8</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>234.83</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>4.15</v>
+        <v>-149.17</v>
       </c>
       <c r="L23" t="n">
-        <v>234.87</v>
+        <v>149.39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:55:00</t>
+          <t>04:53:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.16</v>
+        <v>4.22</v>
       </c>
       <c r="F24" t="n">
-        <v>13.69</v>
+        <v>11.76</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7</v>
+        <v>9.6</v>
       </c>
       <c r="H24" t="n">
-        <v>59.1</v>
+        <v>15.5</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-97.37</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-162.05</v>
+        <v>-175.63</v>
       </c>
       <c r="L24" t="n">
-        <v>189.06</v>
+        <v>193.01</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:56:06</t>
+          <t>04:54:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="F25" t="n">
-        <v>15.98</v>
+        <v>12.99</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9</v>
+        <v>353.2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>159.66</v>
+        <v>226.41</v>
       </c>
       <c r="K25" t="n">
-        <v>145.69</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>216.14</v>
+        <v>226.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:01:55</t>
+          <t>05:00:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.4</v>
+        <v>4.84</v>
       </c>
       <c r="F26" t="n">
-        <v>13.07</v>
+        <v>13.21</v>
       </c>
       <c r="G26" t="n">
-        <v>355.3</v>
+        <v>15.5</v>
       </c>
       <c r="H26" t="n">
-        <v>67.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>252.26</v>
+        <v>201.92</v>
       </c>
       <c r="K26" t="n">
-        <v>-17.76</v>
+        <v>59.74</v>
       </c>
       <c r="L26" t="n">
-        <v>252.89</v>
+        <v>210.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:02:52</t>
+          <t>05:02:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.55</v>
+        <v>4.31</v>
       </c>
       <c r="F27" t="n">
-        <v>15.61</v>
+        <v>11.67</v>
       </c>
       <c r="G27" t="n">
-        <v>14.1</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>39.9</v>
+        <v>36.3</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-253.78</v>
+        <v>183.93</v>
       </c>
       <c r="K27" t="n">
-        <v>132.23</v>
+        <v>-185.66</v>
       </c>
       <c r="L27" t="n">
-        <v>286.16</v>
+        <v>261.34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:04:17</t>
+          <t>05:04:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.23</v>
+        <v>3.93</v>
       </c>
       <c r="F28" t="n">
-        <v>9.25</v>
+        <v>13.62</v>
       </c>
       <c r="G28" t="n">
-        <v>9.4</v>
+        <v>2.8</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>45.9</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-141.14</v>
+        <v>-102.8</v>
       </c>
       <c r="K28" t="n">
-        <v>132.23</v>
+        <v>-237.93</v>
       </c>
       <c r="L28" t="n">
-        <v>193.4</v>
+        <v>259.19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:16:39</t>
+          <t>05:13:31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.36</v>
+        <v>4.25</v>
       </c>
       <c r="F29" t="n">
-        <v>8.24</v>
+        <v>14.68</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>26.5</v>
       </c>
       <c r="H29" t="n">
-        <v>59.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>1.06</v>
+        <v>-13.3</v>
       </c>
       <c r="K29" t="n">
-        <v>53.67</v>
+        <v>-55.38</v>
       </c>
       <c r="L29" t="n">
-        <v>53.68</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:17:54</t>
+          <t>05:14:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.63</v>
+        <v>3.99</v>
       </c>
       <c r="F30" t="n">
-        <v>15.98</v>
+        <v>11.44</v>
       </c>
       <c r="G30" t="n">
-        <v>13.3</v>
+        <v>11.5</v>
       </c>
       <c r="H30" t="n">
-        <v>74.09999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>73.81999999999999</v>
+        <v>-43.3</v>
       </c>
       <c r="K30" t="n">
-        <v>11.69</v>
+        <v>50.04</v>
       </c>
       <c r="L30" t="n">
-        <v>74.73999999999999</v>
+        <v>66.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:20:00</t>
+          <t>05:16:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.72</v>
+        <v>4.53</v>
       </c>
       <c r="F31" t="n">
-        <v>11.52</v>
+        <v>14.36</v>
       </c>
       <c r="G31" t="n">
-        <v>14.7</v>
+        <v>10.4</v>
       </c>
       <c r="H31" t="n">
-        <v>40.7</v>
+        <v>70.5</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>47.63</v>
+        <v>-55.4</v>
       </c>
       <c r="K31" t="n">
-        <v>34.26</v>
+        <v>33.58</v>
       </c>
       <c r="L31" t="n">
-        <v>58.68</v>
+        <v>64.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:24:37</t>
+          <t>05:20:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.67</v>
+        <v>5.37</v>
       </c>
       <c r="F32" t="n">
-        <v>8.869999999999999</v>
+        <v>14.36</v>
       </c>
       <c r="G32" t="n">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="H32" t="n">
-        <v>20.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>30.57</v>
+        <v>-78.59999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>59.16</v>
+        <v>-71.91</v>
       </c>
       <c r="L32" t="n">
-        <v>66.59</v>
+        <v>106.53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:25:31</t>
+          <t>05:21:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="F33" t="n">
-        <v>11.73</v>
+        <v>13.51</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>66.2</v>
+        <v>61.1</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>93.23999999999999</v>
+        <v>-50.67</v>
       </c>
       <c r="K33" t="n">
-        <v>45</v>
+        <v>53.71</v>
       </c>
       <c r="L33" t="n">
-        <v>103.53</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:27:32</t>
+          <t>05:22:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F34" t="n">
-        <v>12.49</v>
+        <v>12.24</v>
       </c>
       <c r="G34" t="n">
-        <v>3.8</v>
+        <v>12.2</v>
       </c>
       <c r="H34" t="n">
-        <v>58.6</v>
+        <v>43.3</v>
       </c>
       <c r="I34" t="n">
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>109.17</v>
+        <v>4.37</v>
       </c>
       <c r="K34" t="n">
-        <v>-77.51000000000001</v>
+        <v>-78.36</v>
       </c>
       <c r="L34" t="n">
-        <v>133.89</v>
+        <v>78.48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:32:00</t>
+          <t>05:26:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.09</v>
+        <v>4.55</v>
       </c>
       <c r="F35" t="n">
-        <v>15.17</v>
+        <v>15.98</v>
       </c>
       <c r="G35" t="n">
-        <v>29.9</v>
+        <v>18.6</v>
       </c>
       <c r="H35" t="n">
-        <v>36.1</v>
+        <v>87</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-49.83</v>
+        <v>138.35</v>
       </c>
       <c r="K35" t="n">
-        <v>216.9</v>
+        <v>42.26</v>
       </c>
       <c r="L35" t="n">
-        <v>222.55</v>
+        <v>144.66</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:34:01</t>
+          <t>05:28:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.25</v>
+        <v>4.13</v>
       </c>
       <c r="F36" t="n">
-        <v>13.11</v>
+        <v>13.29</v>
       </c>
       <c r="G36" t="n">
-        <v>347.6</v>
+        <v>359</v>
       </c>
       <c r="H36" t="n">
-        <v>50.3</v>
+        <v>77.8</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>140.18</v>
+        <v>-102.61</v>
       </c>
       <c r="K36" t="n">
-        <v>-22.98</v>
+        <v>-66.63</v>
       </c>
       <c r="L36" t="n">
-        <v>142.05</v>
+        <v>122.35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:34:57</t>
+          <t>05:30:24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.06</v>
+        <v>4.13</v>
       </c>
       <c r="F37" t="n">
-        <v>15.98</v>
+        <v>15.9</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8</v>
+        <v>360</v>
       </c>
       <c r="H37" t="n">
-        <v>52.9</v>
+        <v>53.9</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>49.25</v>
+        <v>119.13</v>
       </c>
       <c r="K37" t="n">
-        <v>179.47</v>
+        <v>82.14</v>
       </c>
       <c r="L37" t="n">
-        <v>186.1</v>
+        <v>144.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:38:41</t>
+          <t>05:34:31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="F38" t="n">
-        <v>8.33</v>
+        <v>10.34</v>
       </c>
       <c r="G38" t="n">
-        <v>5.4</v>
+        <v>9.5</v>
       </c>
       <c r="H38" t="n">
-        <v>45.8</v>
+        <v>41.4</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>138.67</v>
+        <v>-139.56</v>
       </c>
       <c r="K38" t="n">
-        <v>75.70999999999999</v>
+        <v>69.59</v>
       </c>
       <c r="L38" t="n">
-        <v>157.99</v>
+        <v>155.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:41:07</t>
+          <t>05:36:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.29</v>
+        <v>3.52</v>
       </c>
       <c r="F39" t="n">
-        <v>10.9</v>
+        <v>8.66</v>
       </c>
       <c r="G39" t="n">
-        <v>13.3</v>
+        <v>15.2</v>
       </c>
       <c r="H39" t="n">
-        <v>63.1</v>
+        <v>82.3</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>125.81</v>
+        <v>80.77</v>
       </c>
       <c r="K39" t="n">
-        <v>200.33</v>
+        <v>144</v>
       </c>
       <c r="L39" t="n">
-        <v>236.55</v>
+        <v>165.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:42:26</t>
+          <t>05:38:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.08</v>
+        <v>4.42</v>
       </c>
       <c r="F40" t="n">
-        <v>10.95</v>
+        <v>11.64</v>
       </c>
       <c r="G40" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="H40" t="n">
-        <v>57.6</v>
+        <v>60.1</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>210.18</v>
+        <v>-149.82</v>
       </c>
       <c r="K40" t="n">
-        <v>-25.24</v>
+        <v>101.44</v>
       </c>
       <c r="L40" t="n">
-        <v>211.69</v>
+        <v>180.93</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:48:17</t>
+          <t>05:42:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="F41" t="n">
-        <v>12.49</v>
+        <v>12.32</v>
       </c>
       <c r="G41" t="n">
-        <v>2.3</v>
+        <v>13.7</v>
       </c>
       <c r="H41" t="n">
-        <v>55.7</v>
+        <v>61.6</v>
       </c>
       <c r="I41" t="n">
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>79.06999999999999</v>
+        <v>-27.46</v>
       </c>
       <c r="K41" t="n">
-        <v>278.97</v>
+        <v>-239.03</v>
       </c>
       <c r="L41" t="n">
-        <v>289.96</v>
+        <v>240.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:50:23</t>
+          <t>05:44:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.62</v>
+        <v>4.46</v>
       </c>
       <c r="F42" t="n">
-        <v>15.1</v>
+        <v>12.59</v>
       </c>
       <c r="G42" t="n">
-        <v>25.5</v>
+        <v>349.9</v>
       </c>
       <c r="H42" t="n">
-        <v>65.09999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>78.75</v>
+        <v>3.45</v>
       </c>
       <c r="K42" t="n">
-        <v>290.67</v>
+        <v>269.47</v>
       </c>
       <c r="L42" t="n">
-        <v>301.15</v>
+        <v>269.49</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:52:23</t>
+          <t>05:46:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.42</v>
+        <v>4.7</v>
       </c>
       <c r="F43" t="n">
-        <v>13.51</v>
+        <v>10.58</v>
       </c>
       <c r="G43" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="H43" t="n">
-        <v>85.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="I43" t="n">
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-181.76</v>
+        <v>180.28</v>
       </c>
       <c r="K43" t="n">
-        <v>245.52</v>
+        <v>167.22</v>
       </c>
       <c r="L43" t="n">
-        <v>305.48</v>
+        <v>245.89</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:02:03</t>
+          <t>05:57:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.53</v>
+        <v>5.04</v>
       </c>
       <c r="F44" t="n">
-        <v>14.01</v>
+        <v>13.56</v>
       </c>
       <c r="G44" t="n">
-        <v>3.4</v>
+        <v>13.7</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>56.1</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>101.11</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>-15.86</v>
+        <v>37.26</v>
       </c>
       <c r="L44" t="n">
-        <v>102.35</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:03:54</t>
+          <t>05:58:20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.7</v>
+        <v>5.28</v>
       </c>
       <c r="F45" t="n">
-        <v>14.95</v>
+        <v>15.98</v>
       </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="H45" t="n">
-        <v>64.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>1.71</v>
+        <v>-14.99</v>
       </c>
       <c r="K45" t="n">
-        <v>36.24</v>
+        <v>94.16</v>
       </c>
       <c r="L45" t="n">
-        <v>36.28</v>
+        <v>95.34999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:05:50</t>
+          <t>06:00:17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.72</v>
+        <v>4.67</v>
       </c>
       <c r="F46" t="n">
-        <v>14.69</v>
+        <v>12.3</v>
       </c>
       <c r="G46" t="n">
-        <v>356.3</v>
+        <v>7.3</v>
       </c>
       <c r="H46" t="n">
-        <v>22.6</v>
+        <v>40.8</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-52.57</v>
+        <v>-76.41</v>
       </c>
       <c r="K46" t="n">
-        <v>115.81</v>
+        <v>48.05</v>
       </c>
       <c r="L46" t="n">
-        <v>127.18</v>
+        <v>90.26000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:09:27</t>
+          <t>06:04:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.68</v>
+        <v>3.98</v>
       </c>
       <c r="F47" t="n">
-        <v>14.92</v>
+        <v>12.72</v>
       </c>
       <c r="G47" t="n">
-        <v>6.5</v>
+        <v>21.5</v>
       </c>
       <c r="H47" t="n">
-        <v>67.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>120.97</v>
+        <v>69.78</v>
       </c>
       <c r="K47" t="n">
-        <v>21.6</v>
+        <v>40.3</v>
       </c>
       <c r="L47" t="n">
-        <v>122.88</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:12:01</t>
+          <t>06:06:50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="F48" t="n">
-        <v>15.05</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>5.1</v>
+        <v>359.8</v>
       </c>
       <c r="H48" t="n">
-        <v>48.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.56</v>
+        <v>56.96</v>
       </c>
       <c r="K48" t="n">
-        <v>97.38</v>
+        <v>69.58</v>
       </c>
       <c r="L48" t="n">
-        <v>97.75</v>
+        <v>89.92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:14:21</t>
+          <t>06:08:35</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.02</v>
+        <v>4.53</v>
       </c>
       <c r="F49" t="n">
-        <v>15.64</v>
+        <v>12.89</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>355.4</v>
       </c>
       <c r="H49" t="n">
-        <v>34.4</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-48.75</v>
+        <v>46.78</v>
       </c>
       <c r="K49" t="n">
-        <v>112.55</v>
+        <v>104.12</v>
       </c>
       <c r="L49" t="n">
-        <v>122.66</v>
+        <v>114.15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:19:20</t>
+          <t>06:12:48</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.41</v>
+        <v>3.95</v>
       </c>
       <c r="F50" t="n">
-        <v>11.05</v>
+        <v>12.09</v>
       </c>
       <c r="G50" t="n">
-        <v>10.2</v>
+        <v>16.2</v>
       </c>
       <c r="H50" t="n">
-        <v>61.4</v>
+        <v>37.2</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>138.19</v>
+        <v>40.63</v>
       </c>
       <c r="K50" t="n">
-        <v>90.2</v>
+        <v>-88.2</v>
       </c>
       <c r="L50" t="n">
-        <v>165.02</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:20:57</t>
+          <t>06:13:55</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.16</v>
+        <v>4.42</v>
       </c>
       <c r="F51" t="n">
-        <v>14.86</v>
+        <v>14.72</v>
       </c>
       <c r="G51" t="n">
-        <v>5.8</v>
+        <v>353.6</v>
       </c>
       <c r="H51" t="n">
-        <v>83.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>78.72</v>
+        <v>-111.61</v>
       </c>
       <c r="K51" t="n">
-        <v>168.93</v>
+        <v>31.64</v>
       </c>
       <c r="L51" t="n">
-        <v>186.37</v>
+        <v>116.01</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:22:46</t>
+          <t>06:15:52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.05</v>
+        <v>3.86</v>
       </c>
       <c r="F52" t="n">
-        <v>15.98</v>
+        <v>12.71</v>
       </c>
       <c r="G52" t="n">
-        <v>13.6</v>
+        <v>10.3</v>
       </c>
       <c r="H52" t="n">
-        <v>66.3</v>
+        <v>62.2</v>
       </c>
       <c r="I52" t="n">
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-84.12</v>
+        <v>85.14</v>
       </c>
       <c r="K52" t="n">
-        <v>119</v>
+        <v>64.69</v>
       </c>
       <c r="L52" t="n">
-        <v>145.73</v>
+        <v>106.93</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:25:32</t>
+          <t>06:20:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.31</v>
+        <v>4.11</v>
       </c>
       <c r="F53" t="n">
-        <v>13.25</v>
+        <v>14.13</v>
       </c>
       <c r="G53" t="n">
-        <v>3.4</v>
+        <v>356.3</v>
       </c>
       <c r="H53" t="n">
-        <v>79.7</v>
+        <v>85.2</v>
       </c>
       <c r="I53" t="n">
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-140.62</v>
+        <v>206.09</v>
       </c>
       <c r="K53" t="n">
-        <v>117.25</v>
+        <v>-105.31</v>
       </c>
       <c r="L53" t="n">
-        <v>183.09</v>
+        <v>231.44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:27:36</t>
+          <t>06:22:16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="F54" t="n">
-        <v>12.79</v>
+        <v>14.2</v>
       </c>
       <c r="G54" t="n">
-        <v>18.5</v>
+        <v>355.7</v>
       </c>
       <c r="H54" t="n">
-        <v>40.7</v>
+        <v>34.5</v>
       </c>
       <c r="I54" t="n">
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>151.79</v>
+        <v>-279.87</v>
       </c>
       <c r="K54" t="n">
-        <v>115.17</v>
+        <v>-50.87</v>
       </c>
       <c r="L54" t="n">
-        <v>190.54</v>
+        <v>284.46</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:29:39</t>
+          <t>06:23:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.9</v>
+        <v>3.88</v>
       </c>
       <c r="F55" t="n">
-        <v>15.98</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>15.7</v>
+        <v>4.4</v>
       </c>
       <c r="H55" t="n">
-        <v>62.8</v>
+        <v>41.6</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>-206.62</v>
+        <v>-162.31</v>
       </c>
       <c r="K55" t="n">
-        <v>127.74</v>
+        <v>92.11</v>
       </c>
       <c r="L55" t="n">
-        <v>242.92</v>
+        <v>186.63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:34:18</t>
+          <t>06:29:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.67</v>
+        <v>4.63</v>
       </c>
       <c r="F56" t="n">
-        <v>11.66</v>
+        <v>15.85</v>
       </c>
       <c r="G56" t="n">
-        <v>7.5</v>
+        <v>21.2</v>
       </c>
       <c r="H56" t="n">
-        <v>64.8</v>
+        <v>34.7</v>
       </c>
       <c r="I56" t="n">
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>192.54</v>
+        <v>181.92</v>
       </c>
       <c r="K56" t="n">
-        <v>-83.69</v>
+        <v>228.98</v>
       </c>
       <c r="L56" t="n">
-        <v>209.95</v>
+        <v>292.45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:36:20</t>
+          <t>06:30:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.17</v>
+        <v>5.26</v>
       </c>
       <c r="F57" t="n">
-        <v>13.51</v>
+        <v>13.97</v>
       </c>
       <c r="G57" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="H57" t="n">
-        <v>34.9</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>83.26000000000001</v>
+        <v>-185.96</v>
       </c>
       <c r="K57" t="n">
-        <v>337.42</v>
+        <v>-299.49</v>
       </c>
       <c r="L57" t="n">
-        <v>347.54</v>
+        <v>352.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:38:08</t>
+          <t>06:32:08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.88</v>
+        <v>4.7</v>
       </c>
       <c r="F58" t="n">
-        <v>13.73</v>
+        <v>11.99</v>
       </c>
       <c r="G58" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="H58" t="n">
-        <v>29.2</v>
+        <v>81.2</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>236.43</v>
+        <v>-374.56</v>
       </c>
       <c r="K58" t="n">
-        <v>-16.47</v>
+        <v>-21.62</v>
       </c>
       <c r="L58" t="n">
-        <v>237.01</v>
+        <v>375.18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:46:30</t>
+          <t>06:44:25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.24</v>
+        <v>4.04</v>
       </c>
       <c r="F59" t="n">
         <v>15.98</v>
       </c>
       <c r="G59" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="H59" t="n">
-        <v>84.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>72.28</v>
+        <v>-39.08</v>
       </c>
       <c r="K59" t="n">
-        <v>-49.16</v>
+        <v>-53.49</v>
       </c>
       <c r="L59" t="n">
-        <v>87.41</v>
+        <v>66.23999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:48:13</t>
+          <t>06:46:07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="F60" t="n">
-        <v>10.99</v>
+        <v>12.92</v>
       </c>
       <c r="G60" t="n">
-        <v>358.8</v>
+        <v>11.5</v>
       </c>
       <c r="H60" t="n">
-        <v>59.3</v>
+        <v>99.3</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-52.6</v>
+        <v>62.82</v>
       </c>
       <c r="K60" t="n">
-        <v>47.9</v>
+        <v>48.53</v>
       </c>
       <c r="L60" t="n">
-        <v>71.14</v>
+        <v>79.38</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:50:05</t>
+          <t>06:48:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.31</v>
+        <v>5.41</v>
       </c>
       <c r="F61" t="n">
-        <v>12.44</v>
+        <v>15.98</v>
       </c>
       <c r="G61" t="n">
-        <v>14.7</v>
+        <v>357.2</v>
       </c>
       <c r="H61" t="n">
-        <v>54.9</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>22.07</v>
+        <v>-79.09</v>
       </c>
       <c r="K61" t="n">
-        <v>72.05</v>
+        <v>-48.33</v>
       </c>
       <c r="L61" t="n">
-        <v>75.36</v>
+        <v>92.69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:54:07</t>
+          <t>06:53:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.56</v>
+        <v>5.31</v>
       </c>
       <c r="F62" t="n">
-        <v>12.69</v>
+        <v>15.98</v>
       </c>
       <c r="G62" t="n">
-        <v>19.9</v>
+        <v>8.4</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>51.8</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>87.08</v>
+        <v>-89.69</v>
       </c>
       <c r="K62" t="n">
-        <v>-46.42</v>
+        <v>98.37</v>
       </c>
       <c r="L62" t="n">
-        <v>98.68000000000001</v>
+        <v>133.12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:56:22</t>
+          <t>06:54:33</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.13</v>
+        <v>4.65</v>
       </c>
       <c r="F63" t="n">
-        <v>15.98</v>
+        <v>12.75</v>
       </c>
       <c r="G63" t="n">
-        <v>16.9</v>
+        <v>8.5</v>
       </c>
       <c r="H63" t="n">
-        <v>43.3</v>
+        <v>94</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>107.45</v>
+        <v>-15.8</v>
       </c>
       <c r="K63" t="n">
-        <v>114.22</v>
+        <v>-106.17</v>
       </c>
       <c r="L63" t="n">
-        <v>156.82</v>
+        <v>107.34</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:58:17</t>
+          <t>06:56:01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.74</v>
+        <v>5.15</v>
       </c>
       <c r="F64" t="n">
-        <v>13.08</v>
+        <v>15.98</v>
       </c>
       <c r="G64" t="n">
-        <v>359.5</v>
+        <v>11</v>
       </c>
       <c r="H64" t="n">
-        <v>70</v>
+        <v>65.5</v>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-133.23</v>
+        <v>55.14</v>
       </c>
       <c r="K64" t="n">
-        <v>-41.72</v>
+        <v>124.81</v>
       </c>
       <c r="L64" t="n">
-        <v>139.61</v>
+        <v>136.45</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:02:47</t>
+          <t>07:00:03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.4</v>
+        <v>4.12</v>
       </c>
       <c r="F65" t="n">
-        <v>10.17</v>
+        <v>12.74</v>
       </c>
       <c r="G65" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="H65" t="n">
-        <v>35.9</v>
+        <v>48.6</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>28.62</v>
+        <v>108.95</v>
       </c>
       <c r="K65" t="n">
-        <v>-121.09</v>
+        <v>13.09</v>
       </c>
       <c r="L65" t="n">
-        <v>124.42</v>
+        <v>109.73</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:04:11</t>
+          <t>07:01:16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.18</v>
+        <v>4.84</v>
       </c>
       <c r="F66" t="n">
-        <v>15.72</v>
+        <v>15.98</v>
       </c>
       <c r="G66" t="n">
-        <v>358.4</v>
+        <v>14.4</v>
       </c>
       <c r="H66" t="n">
-        <v>85.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-135.59</v>
+        <v>57.75</v>
       </c>
       <c r="K66" t="n">
-        <v>-112.39</v>
+        <v>139.91</v>
       </c>
       <c r="L66" t="n">
-        <v>176.11</v>
+        <v>151.36</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:06:25</t>
+          <t>07:03:07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.53</v>
+        <v>4.8</v>
       </c>
       <c r="F67" t="n">
-        <v>15.87</v>
+        <v>15.98</v>
       </c>
       <c r="G67" t="n">
-        <v>342.9</v>
+        <v>6.2</v>
       </c>
       <c r="H67" t="n">
-        <v>54.2</v>
+        <v>59.8</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>135.73</v>
+        <v>36.91</v>
       </c>
       <c r="K67" t="n">
-        <v>-79.45</v>
+        <v>-176.14</v>
       </c>
       <c r="L67" t="n">
-        <v>157.27</v>
+        <v>179.97</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:11:16</t>
+          <t>07:06:59</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.84</v>
+        <v>5.29</v>
       </c>
       <c r="F68" t="n">
-        <v>15.06</v>
+        <v>14.93</v>
       </c>
       <c r="G68" t="n">
-        <v>5.5</v>
+        <v>352.8</v>
       </c>
       <c r="H68" t="n">
-        <v>82.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>214.53</v>
+        <v>40.01</v>
       </c>
       <c r="K68" t="n">
-        <v>-123.84</v>
+        <v>240.61</v>
       </c>
       <c r="L68" t="n">
-        <v>247.71</v>
+        <v>243.91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:12:39</t>
+          <t>07:08:32</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.05</v>
+        <v>4.91</v>
       </c>
       <c r="F69" t="n">
-        <v>14.7</v>
+        <v>15.98</v>
       </c>
       <c r="G69" t="n">
-        <v>356</v>
+        <v>2.1</v>
       </c>
       <c r="H69" t="n">
-        <v>64.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>31.37</v>
+        <v>250.64</v>
       </c>
       <c r="K69" t="n">
-        <v>220.37</v>
+        <v>-191.15</v>
       </c>
       <c r="L69" t="n">
-        <v>222.59</v>
+        <v>315.21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:14:41</t>
+          <t>07:10:54</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.04</v>
+        <v>4.17</v>
       </c>
       <c r="F70" t="n">
-        <v>15.86</v>
+        <v>12.24</v>
       </c>
       <c r="G70" t="n">
-        <v>6.3</v>
+        <v>15.2</v>
       </c>
       <c r="H70" t="n">
-        <v>18.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>41.6</v>
+        <v>-188.25</v>
       </c>
       <c r="K70" t="n">
-        <v>295.08</v>
+        <v>148.4</v>
       </c>
       <c r="L70" t="n">
-        <v>298</v>
+        <v>239.72</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:19:43</t>
+          <t>07:15:53</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.64</v>
+        <v>4.79</v>
       </c>
       <c r="F71" t="n">
-        <v>13.39</v>
+        <v>15.36</v>
       </c>
       <c r="G71" t="n">
-        <v>2.7</v>
+        <v>14.7</v>
       </c>
       <c r="H71" t="n">
-        <v>25.5</v>
+        <v>45.2</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>62.83</v>
+        <v>-334.13</v>
       </c>
       <c r="K71" t="n">
-        <v>383.82</v>
+        <v>155.36</v>
       </c>
       <c r="L71" t="n">
-        <v>388.93</v>
+        <v>368.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:21:26</t>
+          <t>07:17:28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="F72" t="n">
-        <v>14.03</v>
+        <v>10.67</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="H72" t="n">
-        <v>25.1</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I72" t="n">
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-269.93</v>
+        <v>-42.65</v>
       </c>
       <c r="K72" t="n">
-        <v>169.37</v>
+        <v>102.25</v>
       </c>
       <c r="L72" t="n">
-        <v>318.67</v>
+        <v>110.79</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:22:08</t>
+          <t>07:18:54</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.46</v>
+        <v>4.98</v>
       </c>
       <c r="F73" t="n">
-        <v>11.93</v>
+        <v>15.98</v>
       </c>
       <c r="G73" t="n">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="H73" t="n">
-        <v>69.7</v>
+        <v>27.5</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-325.2</v>
+        <v>107.08</v>
       </c>
       <c r="K73" t="n">
-        <v>131.7</v>
+        <v>-325.1</v>
       </c>
       <c r="L73" t="n">
-        <v>350.86</v>
+        <v>342.28</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:32:14</t>
+          <t>07:29:18</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.92</v>
+        <v>4.23</v>
       </c>
       <c r="F74" t="n">
-        <v>15.98</v>
+        <v>10.43</v>
       </c>
       <c r="G74" t="n">
-        <v>24.3</v>
+        <v>6.5</v>
       </c>
       <c r="H74" t="n">
-        <v>77.7</v>
+        <v>67.7</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>103.86</v>
+        <v>66.7</v>
       </c>
       <c r="K74" t="n">
-        <v>16.56</v>
+        <v>-10.07</v>
       </c>
       <c r="L74" t="n">
-        <v>105.18</v>
+        <v>67.45999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:34:30</t>
+          <t>07:31:44</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3193,28 +3193,28 @@
         <v>15.98</v>
       </c>
       <c r="G75" t="n">
-        <v>10.5</v>
+        <v>12.4</v>
       </c>
       <c r="H75" t="n">
-        <v>48.4</v>
+        <v>49.4</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>105.45</v>
+        <v>-108.27</v>
       </c>
       <c r="K75" t="n">
-        <v>91.90000000000001</v>
+        <v>31.37</v>
       </c>
       <c r="L75" t="n">
-        <v>139.87</v>
+        <v>112.72</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:36:25</t>
+          <t>07:32:46</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.99</v>
+        <v>4.78</v>
       </c>
       <c r="F76" t="n">
-        <v>15.15</v>
+        <v>15.98</v>
       </c>
       <c r="G76" t="n">
-        <v>350.8</v>
+        <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>46.8</v>
+        <v>34.4</v>
       </c>
       <c r="I76" t="n">
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>35.76</v>
+        <v>-42.3</v>
       </c>
       <c r="K76" t="n">
-        <v>66.67</v>
+        <v>62.41</v>
       </c>
       <c r="L76" t="n">
-        <v>75.65000000000001</v>
+        <v>75.39</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:41:01</t>
+          <t>07:37:07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.59</v>
+        <v>4.68</v>
       </c>
       <c r="F77" t="n">
-        <v>13.46</v>
+        <v>12.43</v>
       </c>
       <c r="G77" t="n">
-        <v>11.4</v>
+        <v>9</v>
       </c>
       <c r="H77" t="n">
-        <v>35.9</v>
+        <v>62.1</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-51.12</v>
+        <v>-104.25</v>
       </c>
       <c r="K77" t="n">
-        <v>72.09</v>
+        <v>35.53</v>
       </c>
       <c r="L77" t="n">
-        <v>88.38</v>
+        <v>110.13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:42:11</t>
+          <t>07:38:35</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.63</v>
+        <v>4.26</v>
       </c>
       <c r="F78" t="n">
-        <v>14.57</v>
+        <v>12.8</v>
       </c>
       <c r="G78" t="n">
         <v>5.8</v>
       </c>
       <c r="H78" t="n">
-        <v>64.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-97.33</v>
+        <v>48.87</v>
       </c>
       <c r="K78" t="n">
-        <v>20.43</v>
+        <v>74.42</v>
       </c>
       <c r="L78" t="n">
-        <v>99.45</v>
+        <v>89.03</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:43:29</t>
+          <t>07:40:56</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.52</v>
+        <v>4.31</v>
       </c>
       <c r="F79" t="n">
-        <v>14.77</v>
+        <v>15.98</v>
       </c>
       <c r="G79" t="n">
-        <v>19.5</v>
+        <v>11.9</v>
       </c>
       <c r="H79" t="n">
-        <v>44.3</v>
+        <v>47.7</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>136.06</v>
+        <v>52.2</v>
       </c>
       <c r="K79" t="n">
-        <v>-1.55</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>136.07</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:47:32</t>
+          <t>07:46:10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.88</v>
+        <v>4.74</v>
       </c>
       <c r="F80" t="n">
-        <v>15.7</v>
+        <v>15.76</v>
       </c>
       <c r="G80" t="n">
-        <v>22</v>
+        <v>25.9</v>
       </c>
       <c r="H80" t="n">
-        <v>47.7</v>
+        <v>60.4</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>40.7</v>
+        <v>-96.79000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-166.22</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>171.13</v>
+        <v>121.71</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:49:15</t>
+          <t>07:47:22</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.88</v>
+        <v>4.31</v>
       </c>
       <c r="F81" t="n">
-        <v>15.98</v>
+        <v>13.05</v>
       </c>
       <c r="G81" t="n">
-        <v>17</v>
+        <v>1.6</v>
       </c>
       <c r="H81" t="n">
-        <v>62.1</v>
+        <v>54.6</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>161.63</v>
+        <v>-108.36</v>
       </c>
       <c r="K81" t="n">
-        <v>-59.22</v>
+        <v>40.24</v>
       </c>
       <c r="L81" t="n">
-        <v>172.14</v>
+        <v>115.59</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:51:23</t>
+          <t>07:49:54</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.59</v>
+        <v>5.21</v>
       </c>
       <c r="F82" t="n">
-        <v>15.46</v>
+        <v>15.42</v>
       </c>
       <c r="G82" t="n">
-        <v>4.2</v>
+        <v>13.7</v>
       </c>
       <c r="H82" t="n">
-        <v>41.3</v>
+        <v>86</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-92.17</v>
+        <v>-12.86</v>
       </c>
       <c r="K82" t="n">
-        <v>130.73</v>
+        <v>183.22</v>
       </c>
       <c r="L82" t="n">
-        <v>159.95</v>
+        <v>183.67</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:55:29</t>
+          <t>07:53:35</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.3</v>
+        <v>4.04</v>
       </c>
       <c r="F83" t="n">
         <v>15.98</v>
       </c>
       <c r="G83" t="n">
-        <v>3.1</v>
+        <v>16</v>
       </c>
       <c r="H83" t="n">
-        <v>69.09999999999999</v>
+        <v>21.7</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-238.79</v>
+        <v>-13.95</v>
       </c>
       <c r="K83" t="n">
-        <v>165.77</v>
+        <v>180.19</v>
       </c>
       <c r="L83" t="n">
-        <v>290.69</v>
+        <v>180.73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:57:10</t>
+          <t>07:55:33</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.77</v>
+        <v>5.44</v>
       </c>
       <c r="F84" t="n">
         <v>15.98</v>
       </c>
       <c r="G84" t="n">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="H84" t="n">
-        <v>86.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I84" t="n">
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-72.20999999999999</v>
+        <v>212.33</v>
       </c>
       <c r="K84" t="n">
-        <v>464.28</v>
+        <v>-10.23</v>
       </c>
       <c r="L84" t="n">
-        <v>469.87</v>
+        <v>212.58</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:59:43</t>
+          <t>07:56:33</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.93</v>
+        <v>5.07</v>
       </c>
       <c r="F85" t="n">
         <v>15.98</v>
       </c>
       <c r="G85" t="n">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="H85" t="n">
-        <v>33.8</v>
+        <v>53.5</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>15.96</v>
+        <v>-199.83</v>
       </c>
       <c r="K85" t="n">
-        <v>252.08</v>
+        <v>-92.78</v>
       </c>
       <c r="L85" t="n">
-        <v>252.59</v>
+        <v>220.32</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:03:55</t>
+          <t>08:01:06</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.58</v>
+        <v>4.28</v>
       </c>
       <c r="F86" t="n">
-        <v>13.5</v>
+        <v>15.42</v>
       </c>
       <c r="G86" t="n">
-        <v>5</v>
+        <v>358.3</v>
       </c>
       <c r="H86" t="n">
-        <v>92.3</v>
+        <v>38.7</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>277.28</v>
+        <v>112.67</v>
       </c>
       <c r="K86" t="n">
-        <v>-12.82</v>
+        <v>273.35</v>
       </c>
       <c r="L86" t="n">
-        <v>277.58</v>
+        <v>295.66</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:05:03</t>
+          <t>08:03:16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.73</v>
+        <v>4.63</v>
       </c>
       <c r="F87" t="n">
-        <v>13.66</v>
+        <v>12.38</v>
       </c>
       <c r="G87" t="n">
-        <v>8.199999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="H87" t="n">
-        <v>58</v>
+        <v>36.7</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-362.2</v>
+        <v>71.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-58.71</v>
+        <v>197.36</v>
       </c>
       <c r="L87" t="n">
-        <v>366.93</v>
+        <v>210.05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:06:33</t>
+          <t>08:05:48</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.31</v>
+        <v>5.21</v>
       </c>
       <c r="F88" t="n">
-        <v>12.28</v>
+        <v>15.98</v>
       </c>
       <c r="G88" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="H88" t="n">
-        <v>40.6</v>
+        <v>61.5</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-13.21</v>
+        <v>278.89</v>
       </c>
       <c r="K88" t="n">
-        <v>331.17</v>
+        <v>73.87</v>
       </c>
       <c r="L88" t="n">
-        <v>331.43</v>
+        <v>288.51</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.18</v>
+        <v>-3.51</v>
       </c>
       <c r="K14" t="n">
-        <v>-91.29000000000001</v>
+        <v>-100.73</v>
       </c>
       <c r="L14" t="n">
-        <v>91.34</v>
+        <v>100.79</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>17.1</v>
+        <v>19.85</v>
       </c>
       <c r="K15" t="n">
-        <v>-70.73999999999999</v>
+        <v>-82.15000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>72.78</v>
+        <v>84.51000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>58.3</v>
+        <v>64.34</v>
       </c>
       <c r="K16" t="n">
-        <v>60.61</v>
+        <v>66.89</v>
       </c>
       <c r="L16" t="n">
-        <v>84.09999999999999</v>
+        <v>92.81</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="K17" t="n">
-        <v>-84.62</v>
+        <v>-99.83</v>
       </c>
       <c r="L17" t="n">
-        <v>84.62</v>
+        <v>99.83</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>39.38</v>
+        <v>49.37</v>
       </c>
       <c r="K18" t="n">
-        <v>-52.15</v>
+        <v>-65.38</v>
       </c>
       <c r="L18" t="n">
-        <v>65.34999999999999</v>
+        <v>81.93000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>13.98</v>
+        <v>17.14</v>
       </c>
       <c r="K19" t="n">
-        <v>83.19</v>
+        <v>101.99</v>
       </c>
       <c r="L19" t="n">
-        <v>84.34999999999999</v>
+        <v>103.42</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-203.12</v>
+        <v>-233.77</v>
       </c>
       <c r="K20" t="n">
-        <v>19.01</v>
+        <v>21.88</v>
       </c>
       <c r="L20" t="n">
-        <v>204</v>
+        <v>234.79</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>15.65</v>
+        <v>19.91</v>
       </c>
       <c r="K21" t="n">
-        <v>-114.53</v>
+        <v>-145.69</v>
       </c>
       <c r="L21" t="n">
-        <v>115.6</v>
+        <v>147.04</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>77.20999999999999</v>
+        <v>86.44</v>
       </c>
       <c r="K22" t="n">
-        <v>135.89</v>
+        <v>152.13</v>
       </c>
       <c r="L22" t="n">
-        <v>156.3</v>
+        <v>174.98</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-115.83</v>
+        <v>-139.73</v>
       </c>
       <c r="K23" t="n">
-        <v>-244.82</v>
+        <v>-295.33</v>
       </c>
       <c r="L23" t="n">
-        <v>270.84</v>
+        <v>326.72</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-197.31</v>
+        <v>-254.78</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.63</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>197.31</v>
+        <v>254.78</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>148.24</v>
+        <v>201.09</v>
       </c>
       <c r="K25" t="n">
-        <v>12.51</v>
+        <v>16.97</v>
       </c>
       <c r="L25" t="n">
-        <v>148.77</v>
+        <v>201.81</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-249.19</v>
+        <v>-339.14</v>
       </c>
       <c r="K26" t="n">
-        <v>-96.98</v>
+        <v>-131.99</v>
       </c>
       <c r="L26" t="n">
-        <v>267.39</v>
+        <v>363.92</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-70.09999999999999</v>
+        <v>-86.31999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>478.85</v>
+        <v>589.64</v>
       </c>
       <c r="L27" t="n">
-        <v>483.95</v>
+        <v>595.9299999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-61.05</v>
+        <v>-84.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>-294.02</v>
+        <v>-408.93</v>
       </c>
       <c r="L28" t="n">
-        <v>300.29</v>
+        <v>417.65</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>66.59999999999999</v>
+        <v>77.56</v>
       </c>
       <c r="K29" t="n">
-        <v>4.79</v>
+        <v>5.58</v>
       </c>
       <c r="L29" t="n">
-        <v>66.77</v>
+        <v>77.76000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>18.22</v>
+        <v>19.71</v>
       </c>
       <c r="K30" t="n">
-        <v>97.22</v>
+        <v>105.15</v>
       </c>
       <c r="L30" t="n">
-        <v>98.91</v>
+        <v>106.98</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>68.17</v>
+        <v>73.59</v>
       </c>
       <c r="K31" t="n">
-        <v>58.88</v>
+        <v>63.56</v>
       </c>
       <c r="L31" t="n">
-        <v>90.08</v>
+        <v>97.23999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-15.35</v>
+        <v>-16.39</v>
       </c>
       <c r="K32" t="n">
-        <v>-123.05</v>
+        <v>-131.39</v>
       </c>
       <c r="L32" t="n">
-        <v>124</v>
+        <v>132.41</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>77.61</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>32.59</v>
+        <v>39.45</v>
       </c>
       <c r="L33" t="n">
-        <v>84.17</v>
+        <v>101.91</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-66.63</v>
+        <v>-84.23</v>
       </c>
       <c r="K34" t="n">
-        <v>18.87</v>
+        <v>23.86</v>
       </c>
       <c r="L34" t="n">
-        <v>69.25</v>
+        <v>87.54000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>102.07</v>
+        <v>133.71</v>
       </c>
       <c r="K35" t="n">
-        <v>19.86</v>
+        <v>26.02</v>
       </c>
       <c r="L35" t="n">
-        <v>103.99</v>
+        <v>136.21</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>18.38</v>
+        <v>21.94</v>
       </c>
       <c r="K36" t="n">
-        <v>-173.09</v>
+        <v>-206.61</v>
       </c>
       <c r="L36" t="n">
-        <v>174.06</v>
+        <v>207.77</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-90.93000000000001</v>
+        <v>-108.87</v>
       </c>
       <c r="K37" t="n">
-        <v>-100.67</v>
+        <v>-120.52</v>
       </c>
       <c r="L37" t="n">
-        <v>135.66</v>
+        <v>162.41</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-20.92</v>
+        <v>-28.47</v>
       </c>
       <c r="K38" t="n">
-        <v>131.49</v>
+        <v>178.97</v>
       </c>
       <c r="L38" t="n">
-        <v>133.15</v>
+        <v>181.22</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-181.34</v>
+        <v>-223.14</v>
       </c>
       <c r="K39" t="n">
-        <v>2.89</v>
+        <v>3.56</v>
       </c>
       <c r="L39" t="n">
-        <v>181.36</v>
+        <v>223.17</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-192.46</v>
+        <v>-245.74</v>
       </c>
       <c r="K40" t="n">
-        <v>129.58</v>
+        <v>165.45</v>
       </c>
       <c r="L40" t="n">
-        <v>232.01</v>
+        <v>296.25</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-252.89</v>
+        <v>-324.65</v>
       </c>
       <c r="K41" t="n">
-        <v>-242.43</v>
+        <v>-311.23</v>
       </c>
       <c r="L41" t="n">
-        <v>350.32</v>
+        <v>449.74</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>229.71</v>
+        <v>305.76</v>
       </c>
       <c r="K42" t="n">
-        <v>139.67</v>
+        <v>185.9</v>
       </c>
       <c r="L42" t="n">
-        <v>268.84</v>
+        <v>357.84</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>271.67</v>
+        <v>350.18</v>
       </c>
       <c r="K43" t="n">
-        <v>42.56</v>
+        <v>54.86</v>
       </c>
       <c r="L43" t="n">
-        <v>274.98</v>
+        <v>354.45</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-72.64</v>
+        <v>-81.38</v>
       </c>
       <c r="K44" t="n">
-        <v>-40.1</v>
+        <v>-44.92</v>
       </c>
       <c r="L44" t="n">
-        <v>82.97</v>
+        <v>92.95</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-38.64</v>
+        <v>-47.04</v>
       </c>
       <c r="K45" t="n">
-        <v>56.74</v>
+        <v>69.09</v>
       </c>
       <c r="L45" t="n">
-        <v>68.65000000000001</v>
+        <v>83.59</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>80.40000000000001</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-63.8</v>
+        <v>-70.34999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>102.64</v>
+        <v>113.18</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-79.20999999999999</v>
+        <v>-96.15000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>52.36</v>
+        <v>63.56</v>
       </c>
       <c r="L47" t="n">
-        <v>94.95</v>
+        <v>115.26</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-102.32</v>
+        <v>-116.19</v>
       </c>
       <c r="K48" t="n">
-        <v>20.95</v>
+        <v>23.79</v>
       </c>
       <c r="L48" t="n">
-        <v>104.44</v>
+        <v>118.6</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-17.83</v>
+        <v>-21.82</v>
       </c>
       <c r="K49" t="n">
-        <v>-75.33</v>
+        <v>-92.2</v>
       </c>
       <c r="L49" t="n">
-        <v>77.41</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>99.81999999999999</v>
+        <v>134.22</v>
       </c>
       <c r="K50" t="n">
-        <v>39.14</v>
+        <v>52.63</v>
       </c>
       <c r="L50" t="n">
-        <v>107.22</v>
+        <v>144.17</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>186.79</v>
+        <v>213.48</v>
       </c>
       <c r="K51" t="n">
-        <v>62.3</v>
+        <v>71.2</v>
       </c>
       <c r="L51" t="n">
-        <v>196.91</v>
+        <v>225.04</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-56.91</v>
+        <v>-67.7</v>
       </c>
       <c r="K52" t="n">
-        <v>-187.09</v>
+        <v>-222.56</v>
       </c>
       <c r="L52" t="n">
-        <v>195.56</v>
+        <v>232.63</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>-268.45</v>
+        <v>-317.4</v>
       </c>
       <c r="K53" t="n">
-        <v>56.05</v>
+        <v>66.27</v>
       </c>
       <c r="L53" t="n">
-        <v>274.24</v>
+        <v>324.24</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>230.33</v>
+        <v>314.22</v>
       </c>
       <c r="K54" t="n">
-        <v>258.03</v>
+        <v>352.01</v>
       </c>
       <c r="L54" t="n">
-        <v>345.88</v>
+        <v>471.85</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-168.2</v>
+        <v>-233.33</v>
       </c>
       <c r="K55" t="n">
-        <v>-64.20999999999999</v>
+        <v>-89.06999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>180.04</v>
+        <v>249.76</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>282.03</v>
+        <v>367.66</v>
       </c>
       <c r="K56" t="n">
-        <v>-16.03</v>
+        <v>-20.9</v>
       </c>
       <c r="L56" t="n">
-        <v>282.48</v>
+        <v>368.26</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>222.57</v>
+        <v>297.66</v>
       </c>
       <c r="K57" t="n">
-        <v>141.33</v>
+        <v>189.02</v>
       </c>
       <c r="L57" t="n">
-        <v>263.65</v>
+        <v>352.61</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>294.46</v>
+        <v>411.92</v>
       </c>
       <c r="K58" t="n">
-        <v>-110.19</v>
+        <v>-154.14</v>
       </c>
       <c r="L58" t="n">
-        <v>314.4</v>
+        <v>439.81</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-55.72</v>
+        <v>-60.69</v>
       </c>
       <c r="K59" t="n">
-        <v>82.8</v>
+        <v>90.19</v>
       </c>
       <c r="L59" t="n">
-        <v>99.81</v>
+        <v>108.71</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-67.38</v>
+        <v>-75.39</v>
       </c>
       <c r="K60" t="n">
-        <v>-50.56</v>
+        <v>-56.57</v>
       </c>
       <c r="L60" t="n">
-        <v>84.23999999999999</v>
+        <v>94.26000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>32.99</v>
+        <v>39.3</v>
       </c>
       <c r="K61" t="n">
-        <v>63.05</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>71.16</v>
+        <v>84.76000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-88.02</v>
+        <v>-105.47</v>
       </c>
       <c r="K62" t="n">
-        <v>25.84</v>
+        <v>30.97</v>
       </c>
       <c r="L62" t="n">
-        <v>91.73</v>
+        <v>109.93</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>71.23999999999999</v>
+        <v>87.97</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.76</v>
+        <v>-58.98</v>
       </c>
       <c r="L63" t="n">
-        <v>85.76000000000001</v>
+        <v>105.91</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-86.92</v>
+        <v>-98.03</v>
       </c>
       <c r="K64" t="n">
-        <v>72.03</v>
+        <v>81.23</v>
       </c>
       <c r="L64" t="n">
-        <v>112.89</v>
+        <v>127.31</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>190.51</v>
+        <v>226.22</v>
       </c>
       <c r="K65" t="n">
-        <v>13.59</v>
+        <v>16.14</v>
       </c>
       <c r="L65" t="n">
-        <v>191</v>
+        <v>226.79</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>18.9</v>
+        <v>23.53</v>
       </c>
       <c r="K66" t="n">
-        <v>153.23</v>
+        <v>190.8</v>
       </c>
       <c r="L66" t="n">
-        <v>154.39</v>
+        <v>192.25</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-167.89</v>
+        <v>-196.56</v>
       </c>
       <c r="K67" t="n">
-        <v>67.19</v>
+        <v>78.66</v>
       </c>
       <c r="L67" t="n">
-        <v>180.83</v>
+        <v>211.71</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-198.71</v>
+        <v>-266.78</v>
       </c>
       <c r="K68" t="n">
-        <v>-35.66</v>
+        <v>-47.87</v>
       </c>
       <c r="L68" t="n">
-        <v>201.88</v>
+        <v>271.04</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-227.5</v>
+        <v>-283.25</v>
       </c>
       <c r="K69" t="n">
-        <v>18.55</v>
+        <v>23.1</v>
       </c>
       <c r="L69" t="n">
-        <v>228.26</v>
+        <v>284.2</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>136.45</v>
+        <v>178.69</v>
       </c>
       <c r="K70" t="n">
-        <v>90.78</v>
+        <v>118.89</v>
       </c>
       <c r="L70" t="n">
-        <v>163.89</v>
+        <v>214.63</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-479.06</v>
+        <v>-643.8</v>
       </c>
       <c r="K71" t="n">
-        <v>31.54</v>
+        <v>42.39</v>
       </c>
       <c r="L71" t="n">
-        <v>480.1</v>
+        <v>645.1900000000001</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-423.87</v>
+        <v>-543.6900000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>170.78</v>
+        <v>219.06</v>
       </c>
       <c r="L72" t="n">
-        <v>456.98</v>
+        <v>586.16</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>259.18</v>
+        <v>352.06</v>
       </c>
       <c r="K73" t="n">
-        <v>-20.3</v>
+        <v>-27.57</v>
       </c>
       <c r="L73" t="n">
-        <v>259.97</v>
+        <v>353.14</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-78.27</v>
+        <v>-90.48999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>-23.34</v>
+        <v>-26.98</v>
       </c>
       <c r="L74" t="n">
-        <v>81.68000000000001</v>
+        <v>94.43000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>12.71</v>
+        <v>15.36</v>
       </c>
       <c r="K75" t="n">
-        <v>55.37</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>56.81</v>
+        <v>68.64</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>24.35</v>
+        <v>30.61</v>
       </c>
       <c r="K76" t="n">
-        <v>-53.01</v>
+        <v>-66.65000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>58.34</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>95.48999999999999</v>
+        <v>106.34</v>
       </c>
       <c r="K77" t="n">
-        <v>-47.65</v>
+        <v>-53.06</v>
       </c>
       <c r="L77" t="n">
-        <v>106.72</v>
+        <v>118.85</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-30.76</v>
+        <v>-32.94</v>
       </c>
       <c r="K78" t="n">
-        <v>137.86</v>
+        <v>147.66</v>
       </c>
       <c r="L78" t="n">
-        <v>141.24</v>
+        <v>151.29</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-12.46</v>
+        <v>-15.43</v>
       </c>
       <c r="K79" t="n">
-        <v>-80.34999999999999</v>
+        <v>-99.56</v>
       </c>
       <c r="L79" t="n">
-        <v>81.31</v>
+        <v>100.75</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-162.89</v>
+        <v>-187.53</v>
       </c>
       <c r="K80" t="n">
-        <v>21.76</v>
+        <v>25.06</v>
       </c>
       <c r="L80" t="n">
-        <v>164.33</v>
+        <v>189.2</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-149.46</v>
+        <v>-179.62</v>
       </c>
       <c r="K81" t="n">
-        <v>109.5</v>
+        <v>131.59</v>
       </c>
       <c r="L81" t="n">
-        <v>185.27</v>
+        <v>222.66</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-26.06</v>
+        <v>-29.41</v>
       </c>
       <c r="K82" t="n">
-        <v>257.01</v>
+        <v>290.05</v>
       </c>
       <c r="L82" t="n">
-        <v>258.33</v>
+        <v>291.54</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-150.26</v>
+        <v>-218.61</v>
       </c>
       <c r="K83" t="n">
-        <v>108.38</v>
+        <v>157.68</v>
       </c>
       <c r="L83" t="n">
-        <v>185.27</v>
+        <v>269.54</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-193.65</v>
+        <v>-227.5</v>
       </c>
       <c r="K84" t="n">
-        <v>-155.63</v>
+        <v>-182.84</v>
       </c>
       <c r="L84" t="n">
-        <v>248.44</v>
+        <v>291.87</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-38.94</v>
+        <v>-53.94</v>
       </c>
       <c r="K85" t="n">
-        <v>192.76</v>
+        <v>266.98</v>
       </c>
       <c r="L85" t="n">
-        <v>196.66</v>
+        <v>272.38</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-48.49</v>
+        <v>-70.84</v>
       </c>
       <c r="K86" t="n">
-        <v>43.61</v>
+        <v>63.71</v>
       </c>
       <c r="L86" t="n">
-        <v>65.20999999999999</v>
+        <v>95.28</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-250.29</v>
+        <v>-357.33</v>
       </c>
       <c r="K87" t="n">
-        <v>55.25</v>
+        <v>78.88</v>
       </c>
       <c r="L87" t="n">
-        <v>256.31</v>
+        <v>365.93</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>210.97</v>
+        <v>280.63</v>
       </c>
       <c r="K88" t="n">
-        <v>271.3</v>
+        <v>360.89</v>
       </c>
       <c r="L88" t="n">
-        <v>343.67</v>
+        <v>457.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-06-13.xlsx
+++ b/output/2025-06-13.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.51</v>
+        <v>-4.6</v>
       </c>
       <c r="K14" t="n">
-        <v>-100.73</v>
+        <v>-131.77</v>
       </c>
       <c r="L14" t="n">
-        <v>100.79</v>
+        <v>131.85</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>19.85</v>
+        <v>23.12</v>
       </c>
       <c r="K15" t="n">
-        <v>-82.15000000000001</v>
+        <v>-95.67</v>
       </c>
       <c r="L15" t="n">
-        <v>84.51000000000001</v>
+        <v>98.42</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>64.34</v>
+        <v>73.42</v>
       </c>
       <c r="K16" t="n">
-        <v>66.89</v>
+        <v>76.33</v>
       </c>
       <c r="L16" t="n">
-        <v>92.81</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="K17" t="n">
-        <v>-99.83</v>
+        <v>-107.62</v>
       </c>
       <c r="L17" t="n">
-        <v>99.83</v>
+        <v>107.63</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>49.37</v>
+        <v>59.13</v>
       </c>
       <c r="K18" t="n">
-        <v>-65.38</v>
+        <v>-78.31</v>
       </c>
       <c r="L18" t="n">
-        <v>81.93000000000001</v>
+        <v>98.13</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>17.14</v>
+        <v>21.34</v>
       </c>
       <c r="K19" t="n">
-        <v>101.99</v>
+        <v>126.97</v>
       </c>
       <c r="L19" t="n">
-        <v>103.42</v>
+        <v>128.75</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>77.56</v>
+        <v>89.95</v>
       </c>
       <c r="K29" t="n">
-        <v>5.58</v>
+        <v>6.48</v>
       </c>
       <c r="L29" t="n">
-        <v>77.76000000000001</v>
+        <v>90.19</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>19.71</v>
+        <v>29.25</v>
       </c>
       <c r="K30" t="n">
-        <v>105.15</v>
+        <v>156.06</v>
       </c>
       <c r="L30" t="n">
-        <v>106.98</v>
+        <v>158.78</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>73.59</v>
+        <v>75.66</v>
       </c>
       <c r="K31" t="n">
-        <v>63.56</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>97.23999999999999</v>
+        <v>99.97</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-16.39</v>
+        <v>-19.18</v>
       </c>
       <c r="K32" t="n">
-        <v>-131.39</v>
+        <v>-153.76</v>
       </c>
       <c r="L32" t="n">
-        <v>132.41</v>
+        <v>154.95</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>93.95999999999999</v>
+        <v>115.89</v>
       </c>
       <c r="K33" t="n">
-        <v>39.45</v>
+        <v>48.66</v>
       </c>
       <c r="L33" t="n">
-        <v>101.91</v>
+        <v>125.69</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-84.23</v>
+        <v>-108.3</v>
       </c>
       <c r="K34" t="n">
-        <v>23.86</v>
+        <v>30.68</v>
       </c>
       <c r="L34" t="n">
-        <v>87.54000000000001</v>
+        <v>112.56</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-81.38</v>
+        <v>-100.77</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.92</v>
+        <v>-55.63</v>
       </c>
       <c r="L44" t="n">
-        <v>92.95</v>
+        <v>115.11</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-47.04</v>
+        <v>-59.94</v>
       </c>
       <c r="K45" t="n">
-        <v>69.09</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>83.59</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>88.65000000000001</v>
+        <v>113.65</v>
       </c>
       <c r="K46" t="n">
-        <v>-70.34999999999999</v>
+        <v>-90.19</v>
       </c>
       <c r="L46" t="n">
-        <v>113.18</v>
+        <v>145.09</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-96.15000000000001</v>
+        <v>-132.75</v>
       </c>
       <c r="K47" t="n">
-        <v>63.56</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>115.26</v>
+        <v>159.14</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-116.19</v>
+        <v>-133.07</v>
       </c>
       <c r="K48" t="n">
-        <v>23.79</v>
+        <v>27.24</v>
       </c>
       <c r="L48" t="n">
-        <v>118.6</v>
+        <v>135.83</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-21.82</v>
+        <v>-27.21</v>
       </c>
       <c r="K49" t="n">
-        <v>-92.2</v>
+        <v>-114.95</v>
       </c>
       <c r="L49" t="n">
-        <v>94.73999999999999</v>
+        <v>118.13</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-60.69</v>
+        <v>-71.11</v>
       </c>
       <c r="K59" t="n">
-        <v>90.19</v>
+        <v>105.67</v>
       </c>
       <c r="L59" t="n">
-        <v>108.71</v>
+        <v>127.37</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-75.39</v>
+        <v>-99.63</v>
       </c>
       <c r="K60" t="n">
-        <v>-56.57</v>
+        <v>-74.76000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>94.26000000000001</v>
+        <v>124.56</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>39.3</v>
+        <v>51.31</v>
       </c>
       <c r="K61" t="n">
-        <v>75.09999999999999</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>84.76000000000001</v>
+        <v>110.66</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-105.47</v>
+        <v>-144.76</v>
       </c>
       <c r="K62" t="n">
-        <v>30.97</v>
+        <v>42.5</v>
       </c>
       <c r="L62" t="n">
-        <v>109.93</v>
+        <v>150.87</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>87.97</v>
+        <v>122.19</v>
       </c>
       <c r="K63" t="n">
-        <v>-58.98</v>
+        <v>-81.92</v>
       </c>
       <c r="L63" t="n">
-        <v>105.91</v>
+        <v>147.11</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-98.03</v>
+        <v>-116.5</v>
       </c>
       <c r="K64" t="n">
-        <v>81.23</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>127.31</v>
+        <v>151.3</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-90.48999999999999</v>
+        <v>-111.6</v>
       </c>
       <c r="K74" t="n">
-        <v>-26.98</v>
+        <v>-33.27</v>
       </c>
       <c r="L74" t="n">
-        <v>94.43000000000001</v>
+        <v>116.46</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>15.36</v>
+        <v>16.77</v>
       </c>
       <c r="K75" t="n">
-        <v>66.90000000000001</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>68.64</v>
+        <v>74.94</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>30.61</v>
+        <v>42.27</v>
       </c>
       <c r="K76" t="n">
-        <v>-66.65000000000001</v>
+        <v>-92.04000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>73.34999999999999</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>106.34</v>
+        <v>138.41</v>
       </c>
       <c r="K77" t="n">
-        <v>-53.06</v>
+        <v>-69.06999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>118.85</v>
+        <v>154.69</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-32.94</v>
+        <v>-41.84</v>
       </c>
       <c r="K78" t="n">
-        <v>147.66</v>
+        <v>187.54</v>
       </c>
       <c r="L78" t="n">
-        <v>151.29</v>
+        <v>192.15</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-15.43</v>
+        <v>-19.81</v>
       </c>
       <c r="K79" t="n">
-        <v>-99.56</v>
+        <v>-127.81</v>
       </c>
       <c r="L79" t="n">
-        <v>100.75</v>
+        <v>129.34</v>
       </c>
     </row>
     <row r="80">
